--- a/Tiếng Trung/Từ mới.xlsx
+++ b/Tiếng Trung/Từ mới.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C2C3869-A991-4C86-ADC2-812CE03C86F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84628EBA-E2DE-455D-8BAC-895879857AEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1890" uniqueCount="1847">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1938" uniqueCount="1891">
   <si>
     <t>带领</t>
   </si>
@@ -5572,6 +5572,138 @@
   </si>
   <si>
     <t>thêm, bù, bổ sung</t>
+  </si>
+  <si>
+    <t>在怪</t>
+  </si>
+  <si>
+    <t>zai` guai`</t>
+  </si>
+  <si>
+    <t>tại quái</t>
+  </si>
+  <si>
+    <t>đổ lỗi</t>
+  </si>
+  <si>
+    <t>阵阵</t>
+  </si>
+  <si>
+    <t>zhen` zhen`</t>
+  </si>
+  <si>
+    <t>trận trận</t>
+  </si>
+  <si>
+    <t>từng cơn, từng đợt</t>
+  </si>
+  <si>
+    <t>其实</t>
+  </si>
+  <si>
+    <t>qi' shi'</t>
+  </si>
+  <si>
+    <t>kì thực</t>
+  </si>
+  <si>
+    <t>thực ra, thật ra</t>
+  </si>
+  <si>
+    <t>家长</t>
+  </si>
+  <si>
+    <t>jia zhang?</t>
+  </si>
+  <si>
+    <t>gia trưởng</t>
+  </si>
+  <si>
+    <t>phụ huynh</t>
+  </si>
+  <si>
+    <t>甲骨文</t>
+  </si>
+  <si>
+    <t>jia? Gu? Wen'</t>
+  </si>
+  <si>
+    <t>giáp cốt văn</t>
+  </si>
+  <si>
+    <t>chữ giáp cốt</t>
+  </si>
+  <si>
+    <t>khoảng chừng, ước chừng, khoảng, hình như</t>
+  </si>
+  <si>
+    <t>产生</t>
+  </si>
+  <si>
+    <t>sản sinh</t>
+  </si>
+  <si>
+    <t>之际</t>
+  </si>
+  <si>
+    <t>zhi ji`</t>
+  </si>
+  <si>
+    <t>chi tế</t>
+  </si>
+  <si>
+    <t>lúc, vào lúc, vào dịp, tại thời điểm chuyển giao</t>
+  </si>
+  <si>
+    <t>最为</t>
+  </si>
+  <si>
+    <t>zui` wei'</t>
+  </si>
+  <si>
+    <t>tối vi</t>
+  </si>
+  <si>
+    <t>nhất, hơn cả</t>
+  </si>
+  <si>
+    <t>古老</t>
+  </si>
+  <si>
+    <t>gu? Lao?</t>
+  </si>
+  <si>
+    <t>cổ lão</t>
+  </si>
+  <si>
+    <t>cổ xưa, cổ kính</t>
+  </si>
+  <si>
+    <t>tạo ra, sinh ra, tạo thành, xuất hiện</t>
+  </si>
+  <si>
+    <t>专家</t>
+  </si>
+  <si>
+    <t>zhuan jia</t>
+  </si>
+  <si>
+    <t>chuyên gia</t>
+  </si>
+  <si>
+    <t>chan? Sheng</t>
+  </si>
+  <si>
+    <t>成熟</t>
+  </si>
+  <si>
+    <t>cheng' shu'</t>
+  </si>
+  <si>
+    <t>thành thục</t>
+  </si>
+  <si>
+    <t>hoàn thiện, chín chắn, chín muồi, kĩ càng</t>
   </si>
 </sst>
 </file>
@@ -5896,7 +6028,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:W528"/>
+  <dimension ref="A2:W540"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="30.6" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="3" width="9.109375" style="1"/>
@@ -12122,506 +12254,674 @@
     </row>
     <row r="493" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D493" s="1" t="s">
-        <v>1706</v>
+        <v>1851</v>
       </c>
       <c r="G493" s="1" t="s">
-        <v>1707</v>
+        <v>1852</v>
       </c>
       <c r="L493" s="1" t="s">
-        <v>1708</v>
+        <v>1853</v>
       </c>
       <c r="Q493" s="1" t="s">
-        <v>1709</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="494" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D494" s="1" t="s">
-        <v>1710</v>
+        <v>1706</v>
       </c>
       <c r="G494" s="1" t="s">
-        <v>1711</v>
+        <v>1707</v>
       </c>
       <c r="L494" s="1" t="s">
-        <v>1712</v>
+        <v>1708</v>
       </c>
       <c r="Q494" s="1" t="s">
-        <v>1713</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="495" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D495" s="1" t="s">
-        <v>1714</v>
+        <v>1710</v>
       </c>
       <c r="G495" s="1" t="s">
-        <v>1715</v>
+        <v>1711</v>
       </c>
       <c r="L495" s="1" t="s">
-        <v>1716</v>
+        <v>1712</v>
       </c>
       <c r="Q495" s="1" t="s">
-        <v>1717</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="496" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D496" s="1" t="s">
-        <v>1718</v>
+        <v>1714</v>
       </c>
       <c r="G496" s="1" t="s">
-        <v>1719</v>
+        <v>1715</v>
       </c>
       <c r="L496" s="1" t="s">
-        <v>1720</v>
+        <v>1716</v>
       </c>
       <c r="Q496" s="1" t="s">
-        <v>1721</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="497" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D497" s="1" t="s">
-        <v>1722</v>
+        <v>1718</v>
       </c>
       <c r="G497" s="1" t="s">
-        <v>1723</v>
+        <v>1719</v>
       </c>
       <c r="L497" s="1" t="s">
-        <v>1724</v>
+        <v>1720</v>
       </c>
       <c r="Q497" s="1" t="s">
-        <v>1725</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="498" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D498" s="1" t="s">
-        <v>1726</v>
+        <v>1722</v>
       </c>
       <c r="G498" s="1" t="s">
-        <v>1727</v>
+        <v>1723</v>
       </c>
       <c r="L498" s="1" t="s">
-        <v>1728</v>
+        <v>1724</v>
       </c>
       <c r="Q498" s="1" t="s">
-        <v>1729</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="499" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D499" s="1" t="s">
-        <v>1730</v>
+        <v>1726</v>
       </c>
       <c r="G499" s="1" t="s">
-        <v>1731</v>
+        <v>1727</v>
       </c>
       <c r="L499" s="1" t="s">
-        <v>1732</v>
+        <v>1728</v>
       </c>
       <c r="Q499" s="1" t="s">
-        <v>1733</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="500" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D500" s="1" t="s">
-        <v>1734</v>
+        <v>1730</v>
       </c>
       <c r="G500" s="1" t="s">
-        <v>1735</v>
+        <v>1731</v>
       </c>
       <c r="L500" s="1" t="s">
-        <v>1736</v>
+        <v>1732</v>
       </c>
       <c r="Q500" s="1" t="s">
-        <v>1737</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="501" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D501" s="1" t="s">
-        <v>1738</v>
+        <v>1734</v>
       </c>
       <c r="G501" s="1" t="s">
-        <v>1739</v>
+        <v>1735</v>
       </c>
       <c r="L501" s="1" t="s">
-        <v>1740</v>
+        <v>1736</v>
       </c>
       <c r="Q501" s="1" t="s">
-        <v>1741</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="502" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D502" s="1" t="s">
-        <v>1742</v>
+        <v>1847</v>
       </c>
       <c r="G502" s="1" t="s">
-        <v>1743</v>
+        <v>1848</v>
       </c>
       <c r="L502" s="1" t="s">
-        <v>1744</v>
+        <v>1849</v>
       </c>
       <c r="Q502" s="1" t="s">
-        <v>1745</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="503" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D503" s="1" t="s">
-        <v>1746</v>
+        <v>1738</v>
       </c>
       <c r="G503" s="1" t="s">
-        <v>1747</v>
+        <v>1739</v>
       </c>
       <c r="L503" s="1" t="s">
-        <v>1748</v>
+        <v>1740</v>
       </c>
       <c r="Q503" s="1" t="s">
-        <v>1749</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="504" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D504" s="1" t="s">
-        <v>1750</v>
+        <v>1742</v>
       </c>
       <c r="G504" s="1" t="s">
-        <v>1751</v>
+        <v>1743</v>
       </c>
       <c r="L504" s="1" t="s">
-        <v>1752</v>
+        <v>1744</v>
       </c>
       <c r="Q504" s="1" t="s">
-        <v>1752</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="505" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D505" s="1" t="s">
-        <v>1753</v>
+        <v>1746</v>
       </c>
       <c r="G505" s="1" t="s">
-        <v>1754</v>
+        <v>1747</v>
       </c>
       <c r="L505" s="1" t="s">
-        <v>1755</v>
+        <v>1748</v>
       </c>
       <c r="Q505" s="1" t="s">
-        <v>1755</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="506" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D506" s="1" t="s">
-        <v>1756</v>
+        <v>1750</v>
       </c>
       <c r="G506" s="1" t="s">
-        <v>1757</v>
+        <v>1751</v>
       </c>
       <c r="L506" s="1" t="s">
-        <v>1758</v>
+        <v>1752</v>
       </c>
       <c r="Q506" s="1" t="s">
-        <v>1759</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="507" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D507" s="1" t="s">
-        <v>1760</v>
+        <v>1753</v>
       </c>
       <c r="G507" s="1" t="s">
-        <v>1761</v>
+        <v>1754</v>
       </c>
       <c r="L507" s="1" t="s">
-        <v>1762</v>
+        <v>1755</v>
       </c>
       <c r="Q507" s="1" t="s">
-        <v>1763</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="508" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D508" s="1" t="s">
-        <v>1764</v>
+        <v>1756</v>
       </c>
       <c r="G508" s="1" t="s">
-        <v>1765</v>
+        <v>1757</v>
       </c>
       <c r="L508" s="1" t="s">
-        <v>1766</v>
+        <v>1758</v>
       </c>
       <c r="Q508" s="1" t="s">
-        <v>1767</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="509" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D509" s="1" t="s">
-        <v>1768</v>
+        <v>1760</v>
       </c>
       <c r="G509" s="1" t="s">
-        <v>1769</v>
+        <v>1761</v>
       </c>
       <c r="L509" s="1" t="s">
-        <v>1770</v>
+        <v>1762</v>
       </c>
       <c r="Q509" s="1" t="s">
-        <v>1771</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="510" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D510" s="1" t="s">
-        <v>1772</v>
+        <v>1764</v>
       </c>
       <c r="G510" s="1" t="s">
-        <v>1773</v>
+        <v>1765</v>
       </c>
       <c r="L510" s="1" t="s">
-        <v>1774</v>
+        <v>1766</v>
       </c>
       <c r="Q510" s="1" t="s">
-        <v>1775</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="511" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D511" s="1" t="s">
-        <v>1776</v>
+        <v>1768</v>
       </c>
       <c r="G511" s="1" t="s">
-        <v>1777</v>
+        <v>1769</v>
       </c>
       <c r="L511" s="1" t="s">
-        <v>1778</v>
+        <v>1770</v>
       </c>
       <c r="Q511" s="1" t="s">
-        <v>1779</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="512" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D512" s="1" t="s">
-        <v>1780</v>
+        <v>1772</v>
       </c>
       <c r="G512" s="1" t="s">
-        <v>1781</v>
+        <v>1773</v>
       </c>
       <c r="L512" s="1" t="s">
-        <v>1782</v>
+        <v>1774</v>
       </c>
       <c r="Q512" s="1" t="s">
-        <v>1783</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="513" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D513" s="1" t="s">
-        <v>1784</v>
+        <v>1776</v>
       </c>
       <c r="G513" s="1" t="s">
-        <v>1785</v>
+        <v>1777</v>
       </c>
       <c r="L513" s="1" t="s">
-        <v>1786</v>
+        <v>1778</v>
       </c>
       <c r="Q513" s="1" t="s">
-        <v>1787</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="514" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D514" s="1" t="s">
-        <v>1788</v>
+        <v>1780</v>
       </c>
       <c r="G514" s="1" t="s">
-        <v>1789</v>
+        <v>1781</v>
       </c>
       <c r="L514" s="1" t="s">
-        <v>1790</v>
+        <v>1782</v>
       </c>
       <c r="Q514" s="1" t="s">
-        <v>1791</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="515" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D515" s="1" t="s">
-        <v>1792</v>
+        <v>1784</v>
       </c>
       <c r="G515" s="1" t="s">
-        <v>1793</v>
+        <v>1785</v>
       </c>
       <c r="L515" s="1" t="s">
-        <v>1794</v>
+        <v>1786</v>
       </c>
       <c r="Q515" s="1" t="s">
-        <v>1795</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="516" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D516" s="1" t="s">
-        <v>1796</v>
+        <v>1788</v>
       </c>
       <c r="G516" s="1" t="s">
-        <v>1797</v>
+        <v>1789</v>
       </c>
       <c r="L516" s="1" t="s">
-        <v>1798</v>
+        <v>1790</v>
       </c>
       <c r="Q516" s="1" t="s">
-        <v>1799</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="517" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D517" s="1" t="s">
-        <v>1800</v>
+        <v>1792</v>
       </c>
       <c r="G517" s="1" t="s">
-        <v>1801</v>
+        <v>1793</v>
       </c>
       <c r="L517" s="1" t="s">
-        <v>1802</v>
+        <v>1794</v>
       </c>
       <c r="Q517" s="1" t="s">
-        <v>1803</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="518" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D518" s="1" t="s">
-        <v>1804</v>
+        <v>1796</v>
       </c>
       <c r="G518" s="1" t="s">
-        <v>1805</v>
+        <v>1797</v>
       </c>
       <c r="L518" s="1" t="s">
-        <v>1806</v>
+        <v>1798</v>
       </c>
       <c r="Q518" s="1" t="s">
-        <v>1807</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="519" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D519" s="1" t="s">
-        <v>1808</v>
+        <v>1800</v>
       </c>
       <c r="G519" s="1" t="s">
-        <v>1809</v>
+        <v>1801</v>
       </c>
       <c r="L519" s="1" t="s">
-        <v>1810</v>
+        <v>1802</v>
       </c>
       <c r="Q519" s="1" t="s">
-        <v>1810</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="520" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D520" s="1" t="s">
-        <v>1811</v>
+        <v>1804</v>
       </c>
       <c r="G520" s="1" t="s">
-        <v>1812</v>
+        <v>1805</v>
       </c>
       <c r="L520" s="1" t="s">
-        <v>1813</v>
+        <v>1806</v>
       </c>
       <c r="Q520" s="1" t="s">
-        <v>1814</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="521" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D521" s="1" t="s">
-        <v>1815</v>
+        <v>1808</v>
       </c>
       <c r="G521" s="1" t="s">
-        <v>1816</v>
+        <v>1809</v>
       </c>
       <c r="L521" s="1" t="s">
-        <v>1817</v>
+        <v>1810</v>
       </c>
       <c r="Q521" s="1" t="s">
-        <v>1818</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="522" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D522" s="1" t="s">
-        <v>1819</v>
+        <v>1811</v>
       </c>
       <c r="G522" s="1" t="s">
-        <v>1820</v>
+        <v>1812</v>
       </c>
       <c r="L522" s="1" t="s">
-        <v>1821</v>
+        <v>1813</v>
       </c>
       <c r="Q522" s="1" t="s">
-        <v>1822</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="523" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D523" s="1" t="s">
-        <v>1823</v>
+        <v>1815</v>
       </c>
       <c r="G523" s="1" t="s">
-        <v>1824</v>
+        <v>1816</v>
       </c>
       <c r="L523" s="1" t="s">
-        <v>1825</v>
+        <v>1817</v>
       </c>
       <c r="Q523" s="1" t="s">
-        <v>1826</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="524" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D524" s="1" t="s">
-        <v>1827</v>
+        <v>1819</v>
       </c>
       <c r="G524" s="1" t="s">
-        <v>1828</v>
+        <v>1820</v>
       </c>
       <c r="L524" s="1" t="s">
-        <v>1829</v>
+        <v>1821</v>
       </c>
       <c r="Q524" s="1" t="s">
-        <v>1830</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="525" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D525" s="1" t="s">
-        <v>1831</v>
+        <v>1823</v>
       </c>
       <c r="G525" s="1" t="s">
-        <v>1832</v>
+        <v>1824</v>
       </c>
       <c r="L525" s="1" t="s">
-        <v>1833</v>
+        <v>1825</v>
       </c>
       <c r="Q525" s="1" t="s">
-        <v>1834</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="526" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D526" s="1" t="s">
-        <v>1835</v>
+        <v>1827</v>
       </c>
       <c r="G526" s="1" t="s">
-        <v>1836</v>
+        <v>1828</v>
       </c>
       <c r="L526" s="1" t="s">
-        <v>1837</v>
+        <v>1829</v>
       </c>
       <c r="Q526" s="1" t="s">
-        <v>1838</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="527" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D527" s="1" t="s">
-        <v>1839</v>
+        <v>1831</v>
       </c>
       <c r="G527" s="1" t="s">
-        <v>1840</v>
+        <v>1832</v>
       </c>
       <c r="L527" s="1" t="s">
-        <v>1841</v>
+        <v>1833</v>
       </c>
       <c r="Q527" s="1" t="s">
-        <v>1842</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="528" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D528" s="1" t="s">
+        <v>1835</v>
+      </c>
+      <c r="G528" s="1" t="s">
+        <v>1836</v>
+      </c>
+      <c r="L528" s="1" t="s">
+        <v>1837</v>
+      </c>
+      <c r="Q528" s="1" t="s">
+        <v>1838</v>
+      </c>
+    </row>
+    <row r="529" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D529" s="1" t="s">
+        <v>1839</v>
+      </c>
+      <c r="G529" s="1" t="s">
+        <v>1840</v>
+      </c>
+      <c r="L529" s="1" t="s">
+        <v>1841</v>
+      </c>
+      <c r="Q529" s="1" t="s">
+        <v>1842</v>
+      </c>
+    </row>
+    <row r="530" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D530" s="1" t="s">
         <v>1843</v>
       </c>
-      <c r="G528" s="1" t="s">
+      <c r="G530" s="1" t="s">
         <v>1844</v>
       </c>
-      <c r="L528" s="1" t="s">
+      <c r="L530" s="1" t="s">
         <v>1845</v>
       </c>
-      <c r="Q528" s="1" t="s">
+      <c r="Q530" s="1" t="s">
         <v>1846</v>
+      </c>
+    </row>
+    <row r="531" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D531" s="1" t="s">
+        <v>1855</v>
+      </c>
+      <c r="G531" s="1" t="s">
+        <v>1856</v>
+      </c>
+      <c r="L531" s="1" t="s">
+        <v>1857</v>
+      </c>
+      <c r="Q531" s="1" t="s">
+        <v>1858</v>
+      </c>
+    </row>
+    <row r="532" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D532" s="1" t="s">
+        <v>1859</v>
+      </c>
+      <c r="G532" s="1" t="s">
+        <v>1860</v>
+      </c>
+      <c r="L532" s="1" t="s">
+        <v>1861</v>
+      </c>
+      <c r="Q532" s="1" t="s">
+        <v>1862</v>
+      </c>
+    </row>
+    <row r="533" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D533" s="1" t="s">
+        <v>1863</v>
+      </c>
+      <c r="G533" s="1" t="s">
+        <v>1864</v>
+      </c>
+      <c r="L533" s="1" t="s">
+        <v>1865</v>
+      </c>
+      <c r="Q533" s="1" t="s">
+        <v>1866</v>
+      </c>
+    </row>
+    <row r="534" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D534" s="1" t="s">
+        <v>1129</v>
+      </c>
+      <c r="G534" s="1" t="s">
+        <v>1130</v>
+      </c>
+      <c r="L534" s="1" t="s">
+        <v>1131</v>
+      </c>
+      <c r="Q534" s="1" t="s">
+        <v>1867</v>
+      </c>
+    </row>
+    <row r="535" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D535" s="1" t="s">
+        <v>1868</v>
+      </c>
+      <c r="G535" s="1" t="s">
+        <v>1886</v>
+      </c>
+      <c r="L535" s="1" t="s">
+        <v>1869</v>
+      </c>
+      <c r="Q535" s="1" t="s">
+        <v>1882</v>
+      </c>
+    </row>
+    <row r="536" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D536" s="1" t="s">
+        <v>1870</v>
+      </c>
+      <c r="G536" s="1" t="s">
+        <v>1871</v>
+      </c>
+      <c r="L536" s="1" t="s">
+        <v>1872</v>
+      </c>
+      <c r="Q536" s="1" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="537" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D537" s="1" t="s">
+        <v>1874</v>
+      </c>
+      <c r="G537" s="1" t="s">
+        <v>1875</v>
+      </c>
+      <c r="L537" s="1" t="s">
+        <v>1876</v>
+      </c>
+      <c r="Q537" s="1" t="s">
+        <v>1877</v>
+      </c>
+    </row>
+    <row r="538" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D538" s="1" t="s">
+        <v>1878</v>
+      </c>
+      <c r="G538" s="1" t="s">
+        <v>1879</v>
+      </c>
+      <c r="L538" s="1" t="s">
+        <v>1880</v>
+      </c>
+      <c r="Q538" s="1" t="s">
+        <v>1881</v>
+      </c>
+    </row>
+    <row r="539" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D539" s="1" t="s">
+        <v>1887</v>
+      </c>
+      <c r="G539" s="1" t="s">
+        <v>1888</v>
+      </c>
+      <c r="L539" s="1" t="s">
+        <v>1889</v>
+      </c>
+      <c r="Q539" s="1" t="s">
+        <v>1890</v>
+      </c>
+    </row>
+    <row r="540" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D540" s="1" t="s">
+        <v>1883</v>
+      </c>
+      <c r="G540" s="1" t="s">
+        <v>1884</v>
+      </c>
+      <c r="L540" s="1" t="s">
+        <v>1885</v>
+      </c>
+      <c r="Q540" s="1" t="s">
+        <v>1885</v>
       </c>
     </row>
   </sheetData>

--- a/Tiếng Trung/Từ mới.xlsx
+++ b/Tiếng Trung/Từ mới.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84628EBA-E2DE-455D-8BAC-895879857AEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E59E54A-F745-4319-B6C2-75470BEEC14C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1938" uniqueCount="1891">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2038" uniqueCount="1989">
   <si>
     <t>带领</t>
   </si>
@@ -5704,6 +5704,300 @@
   </si>
   <si>
     <t>hoàn thiện, chín chắn, chín muồi, kĩ càng</t>
+  </si>
+  <si>
+    <t>创造</t>
+  </si>
+  <si>
+    <t>chuang` zao`</t>
+  </si>
+  <si>
+    <t>sáng tạo</t>
+  </si>
+  <si>
+    <t>饮食</t>
+  </si>
+  <si>
+    <t>yin? Shi'</t>
+  </si>
+  <si>
+    <t>ẩm thực</t>
+  </si>
+  <si>
+    <t>鲁菜</t>
+  </si>
+  <si>
+    <t>lu? Cai`</t>
+  </si>
+  <si>
+    <t>Lỗ thái</t>
+  </si>
+  <si>
+    <t>món sơn đông</t>
+  </si>
+  <si>
+    <t>淮菜</t>
+  </si>
+  <si>
+    <t>huai' cai`</t>
+  </si>
+  <si>
+    <t>Hoài thái</t>
+  </si>
+  <si>
+    <t>món hoài dương</t>
+  </si>
+  <si>
+    <t>粤菜</t>
+  </si>
+  <si>
+    <t>yue` cai`</t>
+  </si>
+  <si>
+    <t>việt thái</t>
+  </si>
+  <si>
+    <t>món quảng đông</t>
+  </si>
+  <si>
+    <t>其中</t>
+  </si>
+  <si>
+    <t>qi' zhong</t>
+  </si>
+  <si>
+    <t>kì trung</t>
+  </si>
+  <si>
+    <t>trong đó, một trong những</t>
+  </si>
+  <si>
+    <t>突出</t>
+  </si>
+  <si>
+    <t>tu chu</t>
+  </si>
+  <si>
+    <t>đột xuất</t>
+  </si>
+  <si>
+    <t>nổi bật, xuất sắc, vượt chội</t>
+  </si>
+  <si>
+    <t>正宗</t>
+  </si>
+  <si>
+    <t>zheng` zong</t>
+  </si>
+  <si>
+    <t>chính tông</t>
+  </si>
+  <si>
+    <t>chính thống, chính cống, chính gốc</t>
+  </si>
+  <si>
+    <t>菜肴</t>
+  </si>
+  <si>
+    <t>cai` yao'</t>
+  </si>
+  <si>
+    <t>thái hào</t>
+  </si>
+  <si>
+    <t>đồ ăn, món ăn, thức ăn</t>
+  </si>
+  <si>
+    <t>如今</t>
+  </si>
+  <si>
+    <t>ru' jin</t>
+  </si>
+  <si>
+    <t>như kim</t>
+  </si>
+  <si>
+    <t>bây giờ, đến nay, hiện nay, ngày nay</t>
+  </si>
+  <si>
+    <t>遍布</t>
+  </si>
+  <si>
+    <t>bian` bu`</t>
+  </si>
+  <si>
+    <t>biến bố</t>
+  </si>
+  <si>
+    <t>phân bố, rải rác</t>
+  </si>
+  <si>
+    <t>各地</t>
+  </si>
+  <si>
+    <t>ge` di`</t>
+  </si>
+  <si>
+    <t>các địa</t>
+  </si>
+  <si>
+    <t>các nơi, mọi nơi</t>
+  </si>
+  <si>
+    <t>广泛</t>
+  </si>
+  <si>
+    <t>guang? Fan`</t>
+  </si>
+  <si>
+    <t>quảng phiếm</t>
+  </si>
+  <si>
+    <t>rộng rãi</t>
+  </si>
+  <si>
+    <t>清淡</t>
+  </si>
+  <si>
+    <t>qing dan`</t>
+  </si>
+  <si>
+    <t>thanh đạm</t>
+  </si>
+  <si>
+    <t>nhạt nhẽo</t>
+  </si>
+  <si>
+    <t>属于</t>
+  </si>
+  <si>
+    <t>shu? Yu'</t>
+  </si>
+  <si>
+    <t>thuộc vu</t>
+  </si>
+  <si>
+    <t>thuộc về</t>
+  </si>
+  <si>
+    <t>某人</t>
+  </si>
+  <si>
+    <t>mou? Ren'</t>
+  </si>
+  <si>
+    <t>mỗ nhân</t>
+  </si>
+  <si>
+    <t>ai đó, một ai đó, một người nào đó</t>
+  </si>
+  <si>
+    <t>财主</t>
+  </si>
+  <si>
+    <t>cai' zhu?</t>
+  </si>
+  <si>
+    <t>tài chủ</t>
+  </si>
+  <si>
+    <t>tài chủ, nhà giàu, phú ông</t>
+  </si>
+  <si>
+    <t>于是</t>
+  </si>
+  <si>
+    <t>yu' shi`</t>
+  </si>
+  <si>
+    <t>vu thị</t>
+  </si>
+  <si>
+    <t>thế là</t>
+  </si>
+  <si>
+    <t>派人</t>
+  </si>
+  <si>
+    <t>pai` ren'</t>
+  </si>
+  <si>
+    <t>phái nhân</t>
+  </si>
+  <si>
+    <t>gửi ai đó</t>
+  </si>
+  <si>
+    <t>封</t>
+  </si>
+  <si>
+    <t>feng</t>
+  </si>
+  <si>
+    <t>phong</t>
+  </si>
+  <si>
+    <t>phong, ban tước vị, đóng kín, bịt kín, niêm phong, phong, bức thư</t>
+  </si>
+  <si>
+    <t>识字</t>
+  </si>
+  <si>
+    <t>shi' zi`</t>
+  </si>
+  <si>
+    <t>thức tự</t>
+  </si>
+  <si>
+    <t>biết chữ</t>
+  </si>
+  <si>
+    <t>假装</t>
+  </si>
+  <si>
+    <t>jia? Zhuang</t>
+  </si>
+  <si>
+    <t>giả trang</t>
+  </si>
+  <si>
+    <t>giả vờ, đóng giả</t>
+  </si>
+  <si>
+    <t>便</t>
+  </si>
+  <si>
+    <t>bian`</t>
+  </si>
+  <si>
+    <t>tiện</t>
+  </si>
+  <si>
+    <t>liền, bèn</t>
+  </si>
+  <si>
+    <t>不住</t>
+  </si>
+  <si>
+    <t>bu' zhu`</t>
+  </si>
+  <si>
+    <t>bất trú</t>
+  </si>
+  <si>
+    <t>liên tục, không ngừng</t>
+  </si>
+  <si>
+    <t>亲自</t>
+  </si>
+  <si>
+    <t>qin` zi`</t>
+  </si>
+  <si>
+    <t>thân tự</t>
+  </si>
+  <si>
+    <t>tự mình, tự thân, đích thân</t>
   </si>
 </sst>
 </file>
@@ -6028,7 +6322,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:W540"/>
+  <dimension ref="A2:W565"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="30.6" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="3" width="9.109375" style="1"/>
@@ -12924,6 +13218,356 @@
         <v>1885</v>
       </c>
     </row>
+    <row r="541" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D541" s="1" t="s">
+        <v>1891</v>
+      </c>
+      <c r="G541" s="1" t="s">
+        <v>1892</v>
+      </c>
+      <c r="L541" s="1" t="s">
+        <v>1893</v>
+      </c>
+      <c r="Q541" s="1" t="s">
+        <v>1893</v>
+      </c>
+    </row>
+    <row r="542" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D542" s="1" t="s">
+        <v>1894</v>
+      </c>
+      <c r="G542" s="1" t="s">
+        <v>1895</v>
+      </c>
+      <c r="L542" s="1" t="s">
+        <v>1896</v>
+      </c>
+      <c r="Q542" s="1" t="s">
+        <v>1896</v>
+      </c>
+    </row>
+    <row r="543" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D543" s="1" t="s">
+        <v>1897</v>
+      </c>
+      <c r="G543" s="1" t="s">
+        <v>1898</v>
+      </c>
+      <c r="L543" s="1" t="s">
+        <v>1899</v>
+      </c>
+      <c r="Q543" s="1" t="s">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="544" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D544" s="1" t="s">
+        <v>1901</v>
+      </c>
+      <c r="G544" s="1" t="s">
+        <v>1902</v>
+      </c>
+      <c r="L544" s="1" t="s">
+        <v>1903</v>
+      </c>
+      <c r="Q544" s="1" t="s">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="545" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D545" s="1" t="s">
+        <v>1905</v>
+      </c>
+      <c r="G545" s="1" t="s">
+        <v>1906</v>
+      </c>
+      <c r="L545" s="1" t="s">
+        <v>1907</v>
+      </c>
+      <c r="Q545" s="1" t="s">
+        <v>1908</v>
+      </c>
+    </row>
+    <row r="546" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D546" s="1" t="s">
+        <v>1909</v>
+      </c>
+      <c r="G546" s="1" t="s">
+        <v>1910</v>
+      </c>
+      <c r="L546" s="1" t="s">
+        <v>1911</v>
+      </c>
+      <c r="Q546" s="1" t="s">
+        <v>1912</v>
+      </c>
+    </row>
+    <row r="547" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D547" s="1" t="s">
+        <v>1913</v>
+      </c>
+      <c r="G547" s="1" t="s">
+        <v>1914</v>
+      </c>
+      <c r="L547" s="1" t="s">
+        <v>1915</v>
+      </c>
+      <c r="Q547" s="1" t="s">
+        <v>1916</v>
+      </c>
+    </row>
+    <row r="548" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D548" s="1" t="s">
+        <v>1917</v>
+      </c>
+      <c r="G548" s="1" t="s">
+        <v>1918</v>
+      </c>
+      <c r="L548" s="1" t="s">
+        <v>1919</v>
+      </c>
+      <c r="Q548" s="1" t="s">
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="549" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D549" s="1" t="s">
+        <v>1921</v>
+      </c>
+      <c r="G549" s="1" t="s">
+        <v>1922</v>
+      </c>
+      <c r="L549" s="1" t="s">
+        <v>1923</v>
+      </c>
+      <c r="Q549" s="1" t="s">
+        <v>1924</v>
+      </c>
+    </row>
+    <row r="550" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D550" s="1" t="s">
+        <v>1925</v>
+      </c>
+      <c r="G550" s="1" t="s">
+        <v>1926</v>
+      </c>
+      <c r="L550" s="1" t="s">
+        <v>1927</v>
+      </c>
+      <c r="Q550" s="1" t="s">
+        <v>1928</v>
+      </c>
+    </row>
+    <row r="551" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D551" s="1" t="s">
+        <v>1929</v>
+      </c>
+      <c r="G551" s="1" t="s">
+        <v>1930</v>
+      </c>
+      <c r="L551" s="1" t="s">
+        <v>1931</v>
+      </c>
+      <c r="Q551" s="1" t="s">
+        <v>1932</v>
+      </c>
+    </row>
+    <row r="552" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D552" s="1" t="s">
+        <v>1933</v>
+      </c>
+      <c r="G552" s="1" t="s">
+        <v>1934</v>
+      </c>
+      <c r="L552" s="1" t="s">
+        <v>1935</v>
+      </c>
+      <c r="Q552" s="1" t="s">
+        <v>1936</v>
+      </c>
+    </row>
+    <row r="553" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D553" s="1" t="s">
+        <v>1937</v>
+      </c>
+      <c r="G553" s="1" t="s">
+        <v>1938</v>
+      </c>
+      <c r="L553" s="1" t="s">
+        <v>1939</v>
+      </c>
+      <c r="Q553" s="1" t="s">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="554" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D554" s="1" t="s">
+        <v>1941</v>
+      </c>
+      <c r="G554" s="1" t="s">
+        <v>1942</v>
+      </c>
+      <c r="L554" s="1" t="s">
+        <v>1943</v>
+      </c>
+      <c r="Q554" s="1" t="s">
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="555" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D555" s="1" t="s">
+        <v>1945</v>
+      </c>
+      <c r="G555" s="1" t="s">
+        <v>1946</v>
+      </c>
+      <c r="L555" s="1" t="s">
+        <v>1947</v>
+      </c>
+      <c r="Q555" s="1" t="s">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="556" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D556" s="1" t="s">
+        <v>1949</v>
+      </c>
+      <c r="G556" s="1" t="s">
+        <v>1950</v>
+      </c>
+      <c r="L556" s="1" t="s">
+        <v>1951</v>
+      </c>
+      <c r="Q556" s="1" t="s">
+        <v>1952</v>
+      </c>
+    </row>
+    <row r="557" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D557" s="1" t="s">
+        <v>1953</v>
+      </c>
+      <c r="G557" s="1" t="s">
+        <v>1954</v>
+      </c>
+      <c r="L557" s="1" t="s">
+        <v>1955</v>
+      </c>
+      <c r="Q557" s="1" t="s">
+        <v>1956</v>
+      </c>
+    </row>
+    <row r="558" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D558" s="1" t="s">
+        <v>1957</v>
+      </c>
+      <c r="G558" s="1" t="s">
+        <v>1958</v>
+      </c>
+      <c r="L558" s="1" t="s">
+        <v>1959</v>
+      </c>
+      <c r="Q558" s="1" t="s">
+        <v>1960</v>
+      </c>
+    </row>
+    <row r="559" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D559" s="1" t="s">
+        <v>1961</v>
+      </c>
+      <c r="G559" s="1" t="s">
+        <v>1962</v>
+      </c>
+      <c r="L559" s="1" t="s">
+        <v>1963</v>
+      </c>
+      <c r="Q559" s="1" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="560" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D560" s="1" t="s">
+        <v>1965</v>
+      </c>
+      <c r="G560" s="1" t="s">
+        <v>1966</v>
+      </c>
+      <c r="L560" s="1" t="s">
+        <v>1967</v>
+      </c>
+      <c r="Q560" s="1" t="s">
+        <v>1968</v>
+      </c>
+    </row>
+    <row r="561" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D561" s="1" t="s">
+        <v>1969</v>
+      </c>
+      <c r="G561" s="1" t="s">
+        <v>1970</v>
+      </c>
+      <c r="L561" s="1" t="s">
+        <v>1971</v>
+      </c>
+      <c r="Q561" s="1" t="s">
+        <v>1972</v>
+      </c>
+    </row>
+    <row r="562" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D562" s="1" t="s">
+        <v>1977</v>
+      </c>
+      <c r="G562" s="1" t="s">
+        <v>1978</v>
+      </c>
+      <c r="L562" s="1" t="s">
+        <v>1979</v>
+      </c>
+      <c r="Q562" s="1" t="s">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="563" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D563" s="1" t="s">
+        <v>1973</v>
+      </c>
+      <c r="G563" s="1" t="s">
+        <v>1974</v>
+      </c>
+      <c r="L563" s="1" t="s">
+        <v>1975</v>
+      </c>
+      <c r="Q563" s="1" t="s">
+        <v>1976</v>
+      </c>
+    </row>
+    <row r="564" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D564" s="1" t="s">
+        <v>1981</v>
+      </c>
+      <c r="G564" s="1" t="s">
+        <v>1982</v>
+      </c>
+      <c r="L564" s="1" t="s">
+        <v>1983</v>
+      </c>
+      <c r="Q564" s="1" t="s">
+        <v>1984</v>
+      </c>
+    </row>
+    <row r="565" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D565" s="1" t="s">
+        <v>1985</v>
+      </c>
+      <c r="G565" s="1" t="s">
+        <v>1986</v>
+      </c>
+      <c r="L565" s="1" t="s">
+        <v>1987</v>
+      </c>
+      <c r="Q565" s="1" t="s">
+        <v>1988</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Tiếng Trung/Từ mới.xlsx
+++ b/Tiếng Trung/Từ mới.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8017D86-D7A3-4911-8D8E-626B265D828C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E2739B0-1B69-4D93-A4BA-FAE72DFDABBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2263" uniqueCount="2206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2397" uniqueCount="2336">
   <si>
     <t>带领</t>
   </si>
@@ -6049,9 +6049,6 @@
     <t>đa thị</t>
   </si>
   <si>
-    <t>đa phần</t>
-  </si>
-  <si>
     <t>喜庆</t>
   </si>
   <si>
@@ -6118,9 +6115,6 @@
     <t>多在每年</t>
   </si>
   <si>
-    <t>chủ yếu hàng năm</t>
-  </si>
-  <si>
     <t>端午</t>
   </si>
   <si>
@@ -6650,6 +6644,402 @@
   </si>
   <si>
     <t>bút pháp</t>
+  </si>
+  <si>
+    <t>đa phần, đều là</t>
+  </si>
+  <si>
+    <t>chủ yếu hàng năm, đa phần hằng năm</t>
+  </si>
+  <si>
+    <t>著名</t>
+  </si>
+  <si>
+    <t>zhu` ming'</t>
+  </si>
+  <si>
+    <t>trước danh</t>
+  </si>
+  <si>
+    <t>nổi danh, nổi tiếng</t>
+  </si>
+  <si>
+    <t>作家</t>
+  </si>
+  <si>
+    <t>zuo` jia</t>
+  </si>
+  <si>
+    <t>tác gia</t>
+  </si>
+  <si>
+    <t>tác giả, nhà văn</t>
+  </si>
+  <si>
+    <t>摆</t>
+  </si>
+  <si>
+    <t>bai?</t>
+  </si>
+  <si>
+    <t>bài</t>
+  </si>
+  <si>
+    <t>đặt, bày, bố trí</t>
+  </si>
+  <si>
+    <t>迷惑</t>
+  </si>
+  <si>
+    <t>mi' huo`</t>
+  </si>
+  <si>
+    <t>mê hoặc</t>
+  </si>
+  <si>
+    <t>mê muội, khó hiểu, mơ hồ</t>
+  </si>
+  <si>
+    <t>不知所措</t>
+  </si>
+  <si>
+    <t>bu` zhi suo? Cuo`</t>
+  </si>
+  <si>
+    <t>bất tri sở thố</t>
+  </si>
+  <si>
+    <t>luống cuống, bối rối, lúng ta lúng túng</t>
+  </si>
+  <si>
+    <t>信口</t>
+  </si>
+  <si>
+    <t>xin` kou?</t>
+  </si>
+  <si>
+    <t>tín khẩu</t>
+  </si>
+  <si>
+    <t>幽默</t>
+  </si>
+  <si>
+    <t>you` mo`</t>
+  </si>
+  <si>
+    <t>u mặc</t>
+  </si>
+  <si>
+    <t>hài hước</t>
+  </si>
+  <si>
+    <t>闹了个</t>
+  </si>
+  <si>
+    <t>nao' le ge</t>
+  </si>
+  <si>
+    <t>gây ra, làm xảy ra</t>
+  </si>
+  <si>
+    <t>buột miệng, lỡ miệng</t>
+  </si>
+  <si>
+    <t>含有</t>
+  </si>
+  <si>
+    <t>han' you?</t>
+  </si>
+  <si>
+    <t>hàm hữu</t>
+  </si>
+  <si>
+    <t>chứa đựng</t>
+  </si>
+  <si>
+    <t>一直以来</t>
+  </si>
+  <si>
+    <t>从来</t>
+  </si>
+  <si>
+    <t>từ trước tới nay(khẳng định, nhấn mạnh sự duy trì)</t>
+  </si>
+  <si>
+    <t>từ trước tới nay(phủ định, nhấn mạnh không xảy ra)</t>
+  </si>
+  <si>
+    <t>随着</t>
+  </si>
+  <si>
+    <t>sui' zhe</t>
+  </si>
+  <si>
+    <t>tuỳ trước</t>
+  </si>
+  <si>
+    <t>cùng với, theo, theo sự</t>
+  </si>
+  <si>
+    <t>流逝</t>
+  </si>
+  <si>
+    <t>liu' shi`</t>
+  </si>
+  <si>
+    <t>lưu thệ</t>
+  </si>
+  <si>
+    <t>trôi qua</t>
+  </si>
+  <si>
+    <t>步入</t>
+  </si>
+  <si>
+    <t>bu` ru`</t>
+  </si>
+  <si>
+    <t>bộ nhập</t>
+  </si>
+  <si>
+    <t>第一批</t>
+  </si>
+  <si>
+    <t>di` yi pi</t>
+  </si>
+  <si>
+    <t>đệ nhất phê</t>
+  </si>
+  <si>
+    <t>lứa đầu tiên</t>
+  </si>
+  <si>
+    <t>bước vào, tiến vào, bước sang</t>
+  </si>
+  <si>
+    <t>进入</t>
+  </si>
+  <si>
+    <t>jin` ru`</t>
+  </si>
+  <si>
+    <t>tiến nhập</t>
+  </si>
+  <si>
+    <t>而立之年</t>
+  </si>
+  <si>
+    <t>er' li` zhi nian'</t>
+  </si>
+  <si>
+    <t>nhi lập chi niên</t>
+  </si>
+  <si>
+    <t>tuổi 30</t>
+  </si>
+  <si>
+    <t>三十而立</t>
+  </si>
+  <si>
+    <t>显示</t>
+  </si>
+  <si>
+    <t>xian? Shi`</t>
+  </si>
+  <si>
+    <t>hiển thị</t>
+  </si>
+  <si>
+    <t>hiển thị, thể hiện, khoe ra</t>
+  </si>
+  <si>
+    <t>集中</t>
+  </si>
+  <si>
+    <t>ji' zhong</t>
+  </si>
+  <si>
+    <t>tập trung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tập trung, </t>
+  </si>
+  <si>
+    <t>比例</t>
+  </si>
+  <si>
+    <t>bi? Li`</t>
+  </si>
+  <si>
+    <t>tỉ lệ</t>
+  </si>
+  <si>
+    <t>31.2%</t>
+  </si>
+  <si>
+    <t>bai? Fen zhi san shi' yi dian? Er</t>
+  </si>
+  <si>
+    <t>其次</t>
+  </si>
+  <si>
+    <t>qi' ci`</t>
+  </si>
+  <si>
+    <t>kỳ thứ</t>
+  </si>
+  <si>
+    <t>thứ nhì, tiếp theo</t>
+  </si>
+  <si>
+    <t>三成</t>
+  </si>
+  <si>
+    <t>san cheng'</t>
+  </si>
+  <si>
+    <t>tam thành</t>
+  </si>
+  <si>
+    <t>薪水</t>
+  </si>
+  <si>
+    <t>xin shui?</t>
+  </si>
+  <si>
+    <t>tân thuỷ</t>
+  </si>
+  <si>
+    <t>lương, tiền công, thù lao</t>
+  </si>
+  <si>
+    <t>福利</t>
+  </si>
+  <si>
+    <t>fu' li`</t>
+  </si>
+  <si>
+    <t>phúc lợi</t>
+  </si>
+  <si>
+    <t>phúc lợi, đãi ngộ</t>
+  </si>
+  <si>
+    <t>计较</t>
+  </si>
+  <si>
+    <t>ji` jiao</t>
+  </si>
+  <si>
+    <t>kế giảo</t>
+  </si>
+  <si>
+    <t>tính toán, so bì, tị nạnh</t>
+  </si>
+  <si>
+    <t>打转转</t>
+  </si>
+  <si>
+    <t>da? Zhuan` zhuan`</t>
+  </si>
+  <si>
+    <t>đả chuyển chuyển</t>
+  </si>
+  <si>
+    <t>xoay quanh, lởn vởn, đảo qua đảo lại</t>
+  </si>
+  <si>
+    <t>职场</t>
+  </si>
+  <si>
+    <t>zhi' chang?</t>
+  </si>
+  <si>
+    <t>chức trường</t>
+  </si>
+  <si>
+    <t>nơi công sở, môi trường công sở, nơi làm việc</t>
+  </si>
+  <si>
+    <t>收获</t>
+  </si>
+  <si>
+    <t>shou huo`</t>
+  </si>
+  <si>
+    <t>thu hoạch</t>
+  </si>
+  <si>
+    <t>gặt hái, thu hoạch</t>
+  </si>
+  <si>
+    <t>将近</t>
+  </si>
+  <si>
+    <t>jiang jin`</t>
+  </si>
+  <si>
+    <t>tương cận</t>
+  </si>
+  <si>
+    <t>gần, ngót, xấp xỉ</t>
+  </si>
+  <si>
+    <t>斤斤计较</t>
+  </si>
+  <si>
+    <t>jīnjīnjìjiào</t>
+  </si>
+  <si>
+    <t>cân cân kế giảo</t>
+  </si>
+  <si>
+    <t>tỵ nạnh; tính toán chi li; so đo từng tý</t>
+  </si>
+  <si>
+    <t>满足感</t>
+  </si>
+  <si>
+    <t>man? Zu' gan?</t>
+  </si>
+  <si>
+    <t>mãn túc cảm</t>
+  </si>
+  <si>
+    <t>cảm giác thoả mãn</t>
+  </si>
+  <si>
+    <t>婚姻</t>
+  </si>
+  <si>
+    <t>hun yin</t>
+  </si>
+  <si>
+    <t>hôn nhân</t>
+  </si>
+  <si>
+    <t>标题</t>
+  </si>
+  <si>
+    <t>biao ti'</t>
+  </si>
+  <si>
+    <t>tiêu đề</t>
+  </si>
+  <si>
+    <t>tiêu đề, đầu đề, đầu bài</t>
+  </si>
+  <si>
+    <t>无奈</t>
+  </si>
+  <si>
+    <t>wu' nai</t>
+  </si>
+  <si>
+    <t>vô nại</t>
+  </si>
+  <si>
+    <t>bất lực, bó tay, tiếc rằng, tiếc là</t>
   </si>
 </sst>
 </file>
@@ -6691,9 +7081,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6974,12 +7366,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:W624"/>
+  <dimension ref="A2:W660"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="30.75" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="3" width="9.140625" style="1"/>
     <col min="4" max="4" width="11.28515625" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="1"/>
+    <col min="5" max="16" width="9.140625" style="1"/>
+    <col min="17" max="17" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="4:17" x14ac:dyDescent="0.45">
@@ -7182,7 +7576,7 @@
         <v>46</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>2075</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="21" spans="4:17" x14ac:dyDescent="0.45">
@@ -10609,7 +11003,7 @@
         <v>1001</v>
       </c>
       <c r="Q301" s="1" t="s">
-        <v>2052</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="302" spans="4:17" x14ac:dyDescent="0.45">
@@ -14287,621 +14681,621 @@
         <v>2004</v>
       </c>
       <c r="Q570" s="1" t="s">
-        <v>2005</v>
+        <v>2204</v>
       </c>
     </row>
     <row r="571" spans="4:17" x14ac:dyDescent="0.45">
       <c r="D571" s="1" t="s">
+        <v>2005</v>
+      </c>
+      <c r="G571" s="1" t="s">
         <v>2006</v>
       </c>
-      <c r="G571" s="1" t="s">
+      <c r="L571" s="1" t="s">
         <v>2007</v>
       </c>
-      <c r="L571" s="1" t="s">
+      <c r="Q571" s="1" t="s">
         <v>2008</v>
-      </c>
-      <c r="Q571" s="1" t="s">
-        <v>2009</v>
       </c>
     </row>
     <row r="572" spans="4:17" x14ac:dyDescent="0.45">
       <c r="D572" s="1" t="s">
+        <v>2009</v>
+      </c>
+      <c r="G572" s="1" t="s">
         <v>2010</v>
       </c>
-      <c r="G572" s="1" t="s">
+      <c r="L572" s="1" t="s">
         <v>2011</v>
       </c>
-      <c r="L572" s="1" t="s">
-        <v>2012</v>
-      </c>
       <c r="Q572" s="1" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="573" spans="4:17" x14ac:dyDescent="0.45">
       <c r="D573" s="1" t="s">
+        <v>2012</v>
+      </c>
+      <c r="G573" s="1" t="s">
         <v>2013</v>
       </c>
-      <c r="G573" s="1" t="s">
+      <c r="L573" s="1" t="s">
         <v>2014</v>
       </c>
-      <c r="L573" s="1" t="s">
+      <c r="Q573" s="1" t="s">
         <v>2015</v>
-      </c>
-      <c r="Q573" s="1" t="s">
-        <v>2016</v>
       </c>
     </row>
     <row r="574" spans="4:17" x14ac:dyDescent="0.45">
       <c r="D574" s="1" t="s">
+        <v>2016</v>
+      </c>
+      <c r="G574" s="1" t="s">
         <v>2017</v>
       </c>
-      <c r="G574" s="1" t="s">
+      <c r="L574" s="1" t="s">
         <v>2018</v>
       </c>
-      <c r="L574" s="1" t="s">
+      <c r="Q574" s="1" t="s">
         <v>2019</v>
-      </c>
-      <c r="Q574" s="1" t="s">
-        <v>2020</v>
       </c>
     </row>
     <row r="575" spans="4:17" x14ac:dyDescent="0.45">
       <c r="D575" s="1" t="s">
+        <v>2020</v>
+      </c>
+      <c r="G575" s="1" t="s">
         <v>2021</v>
       </c>
-      <c r="G575" s="1" t="s">
+      <c r="Q575" s="1" t="s">
         <v>2022</v>
-      </c>
-      <c r="Q575" s="1" t="s">
-        <v>2023</v>
       </c>
     </row>
     <row r="576" spans="4:17" x14ac:dyDescent="0.45">
       <c r="D576" s="1" t="s">
+        <v>2023</v>
+      </c>
+      <c r="G576" s="1" t="s">
         <v>2024</v>
       </c>
-      <c r="G576" s="1" t="s">
+      <c r="Q576" s="1" t="s">
         <v>2025</v>
-      </c>
-      <c r="Q576" s="1" t="s">
-        <v>2026</v>
       </c>
     </row>
     <row r="577" spans="4:17" x14ac:dyDescent="0.45">
       <c r="D577" s="1" t="s">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="Q577" s="1" t="s">
-        <v>2028</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="578" spans="4:17" x14ac:dyDescent="0.45">
       <c r="D578" s="1" t="s">
+        <v>2027</v>
+      </c>
+      <c r="G578" s="1" t="s">
+        <v>2028</v>
+      </c>
+      <c r="L578" s="1" t="s">
         <v>2029</v>
       </c>
-      <c r="G578" s="1" t="s">
+      <c r="Q578" s="1" t="s">
         <v>2030</v>
-      </c>
-      <c r="L578" s="1" t="s">
-        <v>2031</v>
-      </c>
-      <c r="Q578" s="1" t="s">
-        <v>2032</v>
       </c>
     </row>
     <row r="579" spans="4:17" x14ac:dyDescent="0.45">
       <c r="D579" s="1" t="s">
+        <v>2031</v>
+      </c>
+      <c r="G579" s="1" t="s">
+        <v>2032</v>
+      </c>
+      <c r="L579" s="1" t="s">
         <v>2033</v>
       </c>
-      <c r="G579" s="1" t="s">
-        <v>2034</v>
-      </c>
-      <c r="L579" s="1" t="s">
-        <v>2035</v>
-      </c>
       <c r="Q579" s="1" t="s">
-        <v>2035</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="580" spans="4:17" x14ac:dyDescent="0.45">
       <c r="D580" s="1" t="s">
-        <v>2033</v>
+        <v>2031</v>
       </c>
       <c r="G580" s="1" t="s">
-        <v>2042</v>
+        <v>2040</v>
       </c>
       <c r="Q580" s="1" t="s">
-        <v>2043</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="581" spans="4:17" x14ac:dyDescent="0.45">
       <c r="D581" s="1" t="s">
+        <v>2034</v>
+      </c>
+      <c r="G581" s="1" t="s">
+        <v>2035</v>
+      </c>
+      <c r="Q581" s="1" t="s">
         <v>2036</v>
-      </c>
-      <c r="G581" s="1" t="s">
-        <v>2037</v>
-      </c>
-      <c r="Q581" s="1" t="s">
-        <v>2038</v>
       </c>
     </row>
     <row r="582" spans="4:17" x14ac:dyDescent="0.45">
       <c r="D582" s="1" t="s">
+        <v>2037</v>
+      </c>
+      <c r="G582" s="1" t="s">
+        <v>2038</v>
+      </c>
+      <c r="L582" s="1" t="s">
         <v>2039</v>
       </c>
-      <c r="G582" s="1" t="s">
-        <v>2040</v>
-      </c>
-      <c r="L582" s="1" t="s">
-        <v>2041</v>
-      </c>
       <c r="Q582" s="1" t="s">
-        <v>2041</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="583" spans="4:17" x14ac:dyDescent="0.45">
       <c r="D583" s="1" t="s">
+        <v>2042</v>
+      </c>
+      <c r="G583" s="1" t="s">
+        <v>2043</v>
+      </c>
+      <c r="L583" s="1" t="s">
         <v>2044</v>
       </c>
-      <c r="G583" s="1" t="s">
+      <c r="Q583" s="1" t="s">
         <v>2045</v>
-      </c>
-      <c r="L583" s="1" t="s">
-        <v>2046</v>
-      </c>
-      <c r="Q583" s="1" t="s">
-        <v>2047</v>
       </c>
     </row>
     <row r="584" spans="4:17" x14ac:dyDescent="0.45">
       <c r="D584" s="1" t="s">
+        <v>2046</v>
+      </c>
+      <c r="G584" s="1" t="s">
+        <v>2047</v>
+      </c>
+      <c r="L584" s="1" t="s">
         <v>2048</v>
       </c>
-      <c r="G584" s="1" t="s">
+      <c r="Q584" s="1" t="s">
         <v>2049</v>
-      </c>
-      <c r="L584" s="1" t="s">
-        <v>2050</v>
-      </c>
-      <c r="Q584" s="1" t="s">
-        <v>2051</v>
       </c>
     </row>
     <row r="585" spans="4:17" x14ac:dyDescent="0.45">
       <c r="D585" s="1" t="s">
+        <v>2051</v>
+      </c>
+      <c r="G585" s="1" t="s">
+        <v>2052</v>
+      </c>
+      <c r="Q585" s="1" t="s">
         <v>2053</v>
-      </c>
-      <c r="G585" s="1" t="s">
-        <v>2054</v>
-      </c>
-      <c r="Q585" s="1" t="s">
-        <v>2055</v>
       </c>
     </row>
     <row r="586" spans="4:17" x14ac:dyDescent="0.45">
       <c r="D586" s="1" t="s">
+        <v>2094</v>
+      </c>
+      <c r="G586" s="1" t="s">
+        <v>2095</v>
+      </c>
+      <c r="L586" s="1" t="s">
         <v>2096</v>
       </c>
-      <c r="G586" s="1" t="s">
+      <c r="Q586" s="1" t="s">
         <v>2097</v>
-      </c>
-      <c r="L586" s="1" t="s">
-        <v>2098</v>
-      </c>
-      <c r="Q586" s="1" t="s">
-        <v>2099</v>
       </c>
     </row>
     <row r="587" spans="4:17" x14ac:dyDescent="0.45">
       <c r="D587" s="1" t="s">
+        <v>2054</v>
+      </c>
+      <c r="G587" s="1" t="s">
+        <v>2055</v>
+      </c>
+      <c r="L587" s="1" t="s">
         <v>2056</v>
       </c>
-      <c r="G587" s="1" t="s">
+      <c r="Q587" s="1" t="s">
         <v>2057</v>
-      </c>
-      <c r="L587" s="1" t="s">
-        <v>2058</v>
-      </c>
-      <c r="Q587" s="1" t="s">
-        <v>2059</v>
       </c>
     </row>
     <row r="588" spans="4:17" x14ac:dyDescent="0.45">
       <c r="D588" s="1" t="s">
+        <v>2058</v>
+      </c>
+      <c r="G588" s="1" t="s">
+        <v>2059</v>
+      </c>
+      <c r="L588" s="1" t="s">
         <v>2060</v>
       </c>
-      <c r="G588" s="1" t="s">
+      <c r="Q588" s="1" t="s">
         <v>2061</v>
-      </c>
-      <c r="L588" s="1" t="s">
-        <v>2062</v>
-      </c>
-      <c r="Q588" s="1" t="s">
-        <v>2063</v>
       </c>
     </row>
     <row r="589" spans="4:17" x14ac:dyDescent="0.45">
       <c r="D589" s="1" t="s">
+        <v>2062</v>
+      </c>
+      <c r="G589" s="1" t="s">
+        <v>2063</v>
+      </c>
+      <c r="L589" s="1" t="s">
         <v>2064</v>
       </c>
-      <c r="G589" s="1" t="s">
+      <c r="Q589" s="1" t="s">
         <v>2065</v>
-      </c>
-      <c r="L589" s="1" t="s">
-        <v>2066</v>
-      </c>
-      <c r="Q589" s="1" t="s">
-        <v>2067</v>
       </c>
     </row>
     <row r="590" spans="4:17" x14ac:dyDescent="0.45">
       <c r="D590" s="1" t="s">
+        <v>2066</v>
+      </c>
+      <c r="G590" s="1" t="s">
+        <v>2067</v>
+      </c>
+      <c r="L590" s="1" t="s">
         <v>2068</v>
       </c>
-      <c r="G590" s="1" t="s">
+      <c r="Q590" s="1" t="s">
         <v>2069</v>
-      </c>
-      <c r="L590" s="1" t="s">
-        <v>2070</v>
-      </c>
-      <c r="Q590" s="1" t="s">
-        <v>2071</v>
       </c>
     </row>
     <row r="591" spans="4:17" x14ac:dyDescent="0.45">
       <c r="D591" s="1" t="s">
+        <v>2070</v>
+      </c>
+      <c r="G591" s="1" t="s">
+        <v>2071</v>
+      </c>
+      <c r="L591" s="1" t="s">
         <v>2072</v>
       </c>
-      <c r="G591" s="1" t="s">
-        <v>2073</v>
-      </c>
-      <c r="L591" s="1" t="s">
-        <v>2074</v>
-      </c>
       <c r="Q591" s="1" t="s">
-        <v>2100</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="592" spans="4:17" x14ac:dyDescent="0.45">
       <c r="D592" s="1" t="s">
+        <v>2074</v>
+      </c>
+      <c r="G592" s="1" t="s">
+        <v>2075</v>
+      </c>
+      <c r="L592" s="1" t="s">
         <v>2076</v>
       </c>
-      <c r="G592" s="1" t="s">
+      <c r="Q592" s="1" t="s">
         <v>2077</v>
-      </c>
-      <c r="L592" s="1" t="s">
-        <v>2078</v>
-      </c>
-      <c r="Q592" s="1" t="s">
-        <v>2079</v>
       </c>
     </row>
     <row r="593" spans="4:17" x14ac:dyDescent="0.45">
       <c r="D593" s="1" t="s">
+        <v>2078</v>
+      </c>
+      <c r="G593" s="1" t="s">
+        <v>2079</v>
+      </c>
+      <c r="L593" s="1" t="s">
         <v>2080</v>
       </c>
-      <c r="G593" s="1" t="s">
+      <c r="Q593" s="1" t="s">
         <v>2081</v>
-      </c>
-      <c r="L593" s="1" t="s">
-        <v>2082</v>
-      </c>
-      <c r="Q593" s="1" t="s">
-        <v>2083</v>
       </c>
     </row>
     <row r="594" spans="4:17" x14ac:dyDescent="0.45">
       <c r="D594" s="1" t="s">
+        <v>2082</v>
+      </c>
+      <c r="G594" s="1" t="s">
+        <v>2083</v>
+      </c>
+      <c r="L594" s="1" t="s">
         <v>2084</v>
       </c>
-      <c r="G594" s="1" t="s">
+      <c r="Q594" s="1" t="s">
         <v>2085</v>
-      </c>
-      <c r="L594" s="1" t="s">
-        <v>2086</v>
-      </c>
-      <c r="Q594" s="1" t="s">
-        <v>2087</v>
       </c>
     </row>
     <row r="595" spans="4:17" x14ac:dyDescent="0.45">
       <c r="D595" s="1" t="s">
+        <v>2086</v>
+      </c>
+      <c r="G595" s="1" t="s">
+        <v>2087</v>
+      </c>
+      <c r="L595" s="1" t="s">
         <v>2088</v>
       </c>
-      <c r="G595" s="1" t="s">
+      <c r="Q595" s="1" t="s">
         <v>2089</v>
-      </c>
-      <c r="L595" s="1" t="s">
-        <v>2090</v>
-      </c>
-      <c r="Q595" s="1" t="s">
-        <v>2091</v>
       </c>
     </row>
     <row r="596" spans="4:17" x14ac:dyDescent="0.45">
       <c r="D596" s="1" t="s">
+        <v>2090</v>
+      </c>
+      <c r="G596" s="1" t="s">
+        <v>2091</v>
+      </c>
+      <c r="L596" s="1" t="s">
         <v>2092</v>
       </c>
-      <c r="G596" s="1" t="s">
+      <c r="Q596" s="1" t="s">
         <v>2093</v>
-      </c>
-      <c r="L596" s="1" t="s">
-        <v>2094</v>
-      </c>
-      <c r="Q596" s="1" t="s">
-        <v>2095</v>
       </c>
     </row>
     <row r="597" spans="4:17" x14ac:dyDescent="0.45">
       <c r="D597" s="1" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G597" s="1" t="s">
+        <v>2099</v>
+      </c>
+      <c r="L597" s="1" t="s">
+        <v>2101</v>
+      </c>
+      <c r="Q597" s="1" t="s">
         <v>2102</v>
-      </c>
-      <c r="G597" s="1" t="s">
-        <v>2101</v>
-      </c>
-      <c r="L597" s="1" t="s">
-        <v>2103</v>
-      </c>
-      <c r="Q597" s="1" t="s">
-        <v>2104</v>
       </c>
     </row>
     <row r="598" spans="4:17" x14ac:dyDescent="0.45">
       <c r="D598" s="1" t="s">
+        <v>2103</v>
+      </c>
+      <c r="G598" s="1" t="s">
+        <v>2104</v>
+      </c>
+      <c r="L598" s="1" t="s">
         <v>2105</v>
       </c>
-      <c r="G598" s="1" t="s">
+      <c r="Q598" s="1" t="s">
         <v>2106</v>
-      </c>
-      <c r="L598" s="1" t="s">
-        <v>2107</v>
-      </c>
-      <c r="Q598" s="1" t="s">
-        <v>2108</v>
       </c>
     </row>
     <row r="599" spans="4:17" x14ac:dyDescent="0.45">
       <c r="D599" s="1" t="s">
+        <v>2107</v>
+      </c>
+      <c r="G599" s="1" t="s">
+        <v>2108</v>
+      </c>
+      <c r="L599" s="1" t="s">
         <v>2109</v>
       </c>
-      <c r="G599" s="1" t="s">
-        <v>2110</v>
-      </c>
-      <c r="L599" s="1" t="s">
-        <v>2111</v>
-      </c>
       <c r="Q599" s="1" t="s">
-        <v>2111</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="600" spans="4:17" x14ac:dyDescent="0.45">
       <c r="D600" s="1" t="s">
+        <v>2110</v>
+      </c>
+      <c r="G600" s="1" t="s">
+        <v>2111</v>
+      </c>
+      <c r="L600" s="1" t="s">
         <v>2112</v>
       </c>
-      <c r="G600" s="1" t="s">
+      <c r="Q600" s="1" t="s">
         <v>2113</v>
-      </c>
-      <c r="L600" s="1" t="s">
-        <v>2114</v>
-      </c>
-      <c r="Q600" s="1" t="s">
-        <v>2115</v>
       </c>
     </row>
     <row r="601" spans="4:17" x14ac:dyDescent="0.45">
       <c r="D601" s="1" t="s">
+        <v>2114</v>
+      </c>
+      <c r="G601" s="1" t="s">
+        <v>2115</v>
+      </c>
+      <c r="L601" s="1" t="s">
         <v>2116</v>
       </c>
-      <c r="G601" s="1" t="s">
+      <c r="Q601" s="1" t="s">
         <v>2117</v>
-      </c>
-      <c r="L601" s="1" t="s">
-        <v>2118</v>
-      </c>
-      <c r="Q601" s="1" t="s">
-        <v>2119</v>
       </c>
     </row>
     <row r="602" spans="4:17" x14ac:dyDescent="0.45">
       <c r="D602" s="1" t="s">
+        <v>2118</v>
+      </c>
+      <c r="G602" s="1" t="s">
+        <v>2119</v>
+      </c>
+      <c r="L602" s="1" t="s">
         <v>2120</v>
       </c>
-      <c r="G602" s="1" t="s">
+      <c r="Q602" s="1" t="s">
         <v>2121</v>
-      </c>
-      <c r="L602" s="1" t="s">
-        <v>2122</v>
-      </c>
-      <c r="Q602" s="1" t="s">
-        <v>2123</v>
       </c>
     </row>
     <row r="603" spans="4:17" x14ac:dyDescent="0.45">
       <c r="D603" s="1" t="s">
+        <v>2122</v>
+      </c>
+      <c r="G603" s="1" t="s">
+        <v>2123</v>
+      </c>
+      <c r="L603" s="1" t="s">
         <v>2124</v>
       </c>
-      <c r="G603" s="1" t="s">
+      <c r="Q603" s="1" t="s">
         <v>2125</v>
-      </c>
-      <c r="L603" s="1" t="s">
-        <v>2126</v>
-      </c>
-      <c r="Q603" s="1" t="s">
-        <v>2127</v>
       </c>
     </row>
     <row r="604" spans="4:17" x14ac:dyDescent="0.45">
       <c r="D604" s="1" t="s">
+        <v>2126</v>
+      </c>
+      <c r="G604" s="1" t="s">
+        <v>2127</v>
+      </c>
+      <c r="L604" s="1" t="s">
         <v>2128</v>
       </c>
-      <c r="G604" s="1" t="s">
+      <c r="Q604" s="1" t="s">
         <v>2129</v>
-      </c>
-      <c r="L604" s="1" t="s">
-        <v>2130</v>
-      </c>
-      <c r="Q604" s="1" t="s">
-        <v>2131</v>
       </c>
     </row>
     <row r="605" spans="4:17" x14ac:dyDescent="0.45">
       <c r="D605" s="1" t="s">
+        <v>2130</v>
+      </c>
+      <c r="G605" s="1" t="s">
+        <v>2131</v>
+      </c>
+      <c r="L605" s="1" t="s">
         <v>2132</v>
       </c>
-      <c r="G605" s="1" t="s">
+      <c r="Q605" s="1" t="s">
         <v>2133</v>
-      </c>
-      <c r="L605" s="1" t="s">
-        <v>2134</v>
-      </c>
-      <c r="Q605" s="1" t="s">
-        <v>2135</v>
       </c>
     </row>
     <row r="606" spans="4:17" x14ac:dyDescent="0.45">
       <c r="D606" s="1" t="s">
-        <v>2136</v>
+        <v>2134</v>
       </c>
       <c r="Q606" s="1" t="s">
-        <v>2137</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="607" spans="4:17" x14ac:dyDescent="0.45">
       <c r="D607" s="1" t="s">
+        <v>2136</v>
+      </c>
+      <c r="G607" s="1" t="s">
+        <v>2137</v>
+      </c>
+      <c r="L607" s="1" t="s">
         <v>2138</v>
       </c>
-      <c r="G607" s="1" t="s">
-        <v>2139</v>
-      </c>
-      <c r="L607" s="1" t="s">
-        <v>2140</v>
-      </c>
       <c r="Q607" s="1" t="s">
-        <v>2140</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="608" spans="4:17" x14ac:dyDescent="0.45">
       <c r="D608" s="1" t="s">
+        <v>2139</v>
+      </c>
+      <c r="G608" s="1" t="s">
+        <v>2140</v>
+      </c>
+      <c r="L608" s="1" t="s">
         <v>2141</v>
       </c>
-      <c r="G608" s="1" t="s">
+      <c r="Q608" s="1" t="s">
         <v>2142</v>
-      </c>
-      <c r="L608" s="1" t="s">
-        <v>2143</v>
-      </c>
-      <c r="Q608" s="1" t="s">
-        <v>2144</v>
       </c>
     </row>
     <row r="609" spans="4:17" x14ac:dyDescent="0.45">
       <c r="D609" s="1" t="s">
+        <v>2143</v>
+      </c>
+      <c r="G609" s="1" t="s">
+        <v>2144</v>
+      </c>
+      <c r="L609" s="1" t="s">
         <v>2145</v>
       </c>
-      <c r="G609" s="1" t="s">
+      <c r="Q609" s="1" t="s">
         <v>2146</v>
-      </c>
-      <c r="L609" s="1" t="s">
-        <v>2147</v>
-      </c>
-      <c r="Q609" s="1" t="s">
-        <v>2148</v>
       </c>
     </row>
     <row r="610" spans="4:17" x14ac:dyDescent="0.45">
       <c r="D610" s="1" t="s">
+        <v>2147</v>
+      </c>
+      <c r="G610" s="1" t="s">
+        <v>2148</v>
+      </c>
+      <c r="L610" s="1" t="s">
         <v>2149</v>
       </c>
-      <c r="G610" s="1" t="s">
+      <c r="Q610" s="1" t="s">
         <v>2150</v>
-      </c>
-      <c r="L610" s="1" t="s">
-        <v>2151</v>
-      </c>
-      <c r="Q610" s="1" t="s">
-        <v>2152</v>
       </c>
     </row>
     <row r="611" spans="4:17" x14ac:dyDescent="0.45">
       <c r="D611" s="1" t="s">
+        <v>2151</v>
+      </c>
+      <c r="G611" s="1" t="s">
+        <v>2152</v>
+      </c>
+      <c r="L611" s="1" t="s">
         <v>2153</v>
       </c>
-      <c r="G611" s="1" t="s">
+      <c r="Q611" s="1" t="s">
         <v>2154</v>
-      </c>
-      <c r="L611" s="1" t="s">
-        <v>2155</v>
-      </c>
-      <c r="Q611" s="1" t="s">
-        <v>2156</v>
       </c>
     </row>
     <row r="612" spans="4:17" x14ac:dyDescent="0.45">
       <c r="D612" s="1" t="s">
+        <v>2155</v>
+      </c>
+      <c r="G612" s="1" t="s">
+        <v>2156</v>
+      </c>
+      <c r="L612" s="1" t="s">
         <v>2157</v>
       </c>
-      <c r="G612" s="1" t="s">
+      <c r="Q612" s="1" t="s">
         <v>2158</v>
-      </c>
-      <c r="L612" s="1" t="s">
-        <v>2159</v>
-      </c>
-      <c r="Q612" s="1" t="s">
-        <v>2160</v>
       </c>
     </row>
     <row r="613" spans="4:17" x14ac:dyDescent="0.45">
       <c r="D613" s="1" t="s">
+        <v>2159</v>
+      </c>
+      <c r="G613" s="1" t="s">
+        <v>2160</v>
+      </c>
+      <c r="L613" s="1" t="s">
         <v>2161</v>
       </c>
-      <c r="G613" s="1" t="s">
+      <c r="Q613" s="1" t="s">
         <v>2162</v>
-      </c>
-      <c r="L613" s="1" t="s">
-        <v>2163</v>
-      </c>
-      <c r="Q613" s="1" t="s">
-        <v>2164</v>
       </c>
     </row>
     <row r="614" spans="4:17" x14ac:dyDescent="0.45">
       <c r="D614" s="1" t="s">
+        <v>2163</v>
+      </c>
+      <c r="G614" s="1" t="s">
+        <v>2164</v>
+      </c>
+      <c r="L614" s="1" t="s">
         <v>2165</v>
       </c>
-      <c r="G614" s="1" t="s">
+      <c r="Q614" s="1" t="s">
         <v>2166</v>
-      </c>
-      <c r="L614" s="1" t="s">
-        <v>2167</v>
-      </c>
-      <c r="Q614" s="1" t="s">
-        <v>2168</v>
       </c>
     </row>
     <row r="615" spans="4:17" x14ac:dyDescent="0.45">
       <c r="D615" s="1" t="s">
+        <v>2167</v>
+      </c>
+      <c r="G615" s="1" t="s">
+        <v>2168</v>
+      </c>
+      <c r="L615" s="1" t="s">
+        <v>2170</v>
+      </c>
+      <c r="Q615" s="1" t="s">
         <v>2169</v>
-      </c>
-      <c r="G615" s="1" t="s">
-        <v>2170</v>
-      </c>
-      <c r="L615" s="1" t="s">
-        <v>2172</v>
-      </c>
-      <c r="Q615" s="1" t="s">
-        <v>2171</v>
       </c>
     </row>
     <row r="616" spans="4:17" x14ac:dyDescent="0.45">
       <c r="D616" s="1" t="s">
+        <v>2171</v>
+      </c>
+      <c r="G616" s="1" t="s">
+        <v>2172</v>
+      </c>
+      <c r="L616" s="1" t="s">
         <v>2173</v>
-      </c>
-      <c r="G616" s="1" t="s">
-        <v>2174</v>
-      </c>
-      <c r="L616" s="1" t="s">
-        <v>2175</v>
       </c>
       <c r="Q616" s="1" t="s">
         <v>8</v>
@@ -14909,108 +15303,585 @@
     </row>
     <row r="617" spans="4:17" x14ac:dyDescent="0.45">
       <c r="D617" s="1" t="s">
+        <v>2174</v>
+      </c>
+      <c r="G617" s="1" t="s">
+        <v>2175</v>
+      </c>
+      <c r="L617" s="1" t="s">
         <v>2176</v>
       </c>
-      <c r="G617" s="1" t="s">
+      <c r="Q617" s="1" t="s">
         <v>2177</v>
-      </c>
-      <c r="L617" s="1" t="s">
-        <v>2178</v>
-      </c>
-      <c r="Q617" s="1" t="s">
-        <v>2179</v>
       </c>
     </row>
     <row r="618" spans="4:17" x14ac:dyDescent="0.45">
       <c r="D618" s="1" t="s">
+        <v>2178</v>
+      </c>
+      <c r="G618" s="1" t="s">
         <v>2180</v>
       </c>
-      <c r="G618" s="1" t="s">
-        <v>2182</v>
-      </c>
       <c r="L618" s="1" t="s">
+        <v>2179</v>
+      </c>
+      <c r="Q618" s="1" t="s">
         <v>2181</v>
-      </c>
-      <c r="Q618" s="1" t="s">
-        <v>2183</v>
       </c>
     </row>
     <row r="619" spans="4:17" x14ac:dyDescent="0.45">
       <c r="D619" s="1" t="s">
+        <v>2182</v>
+      </c>
+      <c r="G619" s="1" t="s">
+        <v>2183</v>
+      </c>
+      <c r="L619" s="1" t="s">
         <v>2184</v>
       </c>
-      <c r="G619" s="1" t="s">
+      <c r="Q619" s="1" t="s">
         <v>2185</v>
-      </c>
-      <c r="L619" s="1" t="s">
-        <v>2186</v>
-      </c>
-      <c r="Q619" s="1" t="s">
-        <v>2187</v>
       </c>
     </row>
     <row r="620" spans="4:17" x14ac:dyDescent="0.45">
       <c r="D620" s="1" t="s">
+        <v>2188</v>
+      </c>
+      <c r="G620" s="1" t="s">
+        <v>2189</v>
+      </c>
+      <c r="L620" s="1" t="s">
         <v>2190</v>
       </c>
-      <c r="G620" s="1" t="s">
+      <c r="Q620" s="1" t="s">
         <v>2191</v>
-      </c>
-      <c r="L620" s="1" t="s">
-        <v>2192</v>
-      </c>
-      <c r="Q620" s="1" t="s">
-        <v>2193</v>
       </c>
     </row>
     <row r="621" spans="4:17" x14ac:dyDescent="0.45">
       <c r="D621" s="1" t="s">
-        <v>2188</v>
+        <v>2186</v>
       </c>
       <c r="Q621" s="1" t="s">
-        <v>2189</v>
+        <v>2187</v>
       </c>
     </row>
     <row r="622" spans="4:17" x14ac:dyDescent="0.45">
       <c r="D622" s="1" t="s">
+        <v>2192</v>
+      </c>
+      <c r="G622" s="1" t="s">
+        <v>2193</v>
+      </c>
+      <c r="L622" s="1" t="s">
         <v>2194</v>
       </c>
-      <c r="G622" s="1" t="s">
+      <c r="Q622" s="1" t="s">
         <v>2195</v>
-      </c>
-      <c r="L622" s="1" t="s">
-        <v>2196</v>
-      </c>
-      <c r="Q622" s="1" t="s">
-        <v>2197</v>
       </c>
     </row>
     <row r="623" spans="4:17" x14ac:dyDescent="0.45">
       <c r="D623" s="1" t="s">
+        <v>2200</v>
+      </c>
+      <c r="G623" s="1" t="s">
+        <v>2201</v>
+      </c>
+      <c r="L623" s="1" t="s">
         <v>2202</v>
       </c>
-      <c r="G623" s="1" t="s">
+      <c r="Q623" s="1" t="s">
         <v>2203</v>
-      </c>
-      <c r="L623" s="1" t="s">
-        <v>2204</v>
-      </c>
-      <c r="Q623" s="1" t="s">
-        <v>2205</v>
       </c>
     </row>
     <row r="624" spans="4:17" x14ac:dyDescent="0.45">
       <c r="D624" s="1" t="s">
+        <v>2196</v>
+      </c>
+      <c r="G624" s="1" t="s">
+        <v>2197</v>
+      </c>
+      <c r="L624" s="1" t="s">
         <v>2198</v>
       </c>
-      <c r="G624" s="1" t="s">
+      <c r="Q624" s="1" t="s">
         <v>2199</v>
       </c>
-      <c r="L624" s="1" t="s">
-        <v>2200</v>
-      </c>
-      <c r="Q624" s="1" t="s">
-        <v>2201</v>
+    </row>
+    <row r="625" spans="4:17" x14ac:dyDescent="0.45">
+      <c r="D625" s="1" t="s">
+        <v>2206</v>
+      </c>
+      <c r="G625" s="1" t="s">
+        <v>2207</v>
+      </c>
+      <c r="L625" s="1" t="s">
+        <v>2208</v>
+      </c>
+      <c r="Q625" s="1" t="s">
+        <v>2209</v>
+      </c>
+    </row>
+    <row r="626" spans="4:17" x14ac:dyDescent="0.45">
+      <c r="D626" s="1" t="s">
+        <v>2210</v>
+      </c>
+      <c r="G626" s="1" t="s">
+        <v>2211</v>
+      </c>
+      <c r="L626" s="1" t="s">
+        <v>2212</v>
+      </c>
+      <c r="Q626" s="1" t="s">
+        <v>2213</v>
+      </c>
+    </row>
+    <row r="627" spans="4:17" x14ac:dyDescent="0.45">
+      <c r="D627" s="1" t="s">
+        <v>2214</v>
+      </c>
+      <c r="G627" s="1" t="s">
+        <v>2215</v>
+      </c>
+      <c r="L627" s="1" t="s">
+        <v>2216</v>
+      </c>
+      <c r="Q627" s="1" t="s">
+        <v>2217</v>
+      </c>
+    </row>
+    <row r="628" spans="4:17" x14ac:dyDescent="0.45">
+      <c r="D628" s="1" t="s">
+        <v>2218</v>
+      </c>
+      <c r="G628" s="1" t="s">
+        <v>2219</v>
+      </c>
+      <c r="L628" s="1" t="s">
+        <v>2220</v>
+      </c>
+      <c r="Q628" s="1" t="s">
+        <v>2221</v>
+      </c>
+    </row>
+    <row r="629" spans="4:17" x14ac:dyDescent="0.45">
+      <c r="D629" s="1" t="s">
+        <v>2222</v>
+      </c>
+      <c r="G629" s="1" t="s">
+        <v>2223</v>
+      </c>
+      <c r="L629" s="1" t="s">
+        <v>2224</v>
+      </c>
+      <c r="Q629" s="1" t="s">
+        <v>2225</v>
+      </c>
+    </row>
+    <row r="630" spans="4:17" x14ac:dyDescent="0.45">
+      <c r="D630" s="1" t="s">
+        <v>2226</v>
+      </c>
+      <c r="G630" s="1" t="s">
+        <v>2227</v>
+      </c>
+      <c r="L630" s="1" t="s">
+        <v>2228</v>
+      </c>
+      <c r="Q630" s="1" t="s">
+        <v>2236</v>
+      </c>
+    </row>
+    <row r="631" spans="4:17" x14ac:dyDescent="0.45">
+      <c r="D631" s="1" t="s">
+        <v>2229</v>
+      </c>
+      <c r="G631" s="1" t="s">
+        <v>2230</v>
+      </c>
+      <c r="L631" s="1" t="s">
+        <v>2231</v>
+      </c>
+      <c r="Q631" s="1" t="s">
+        <v>2232</v>
+      </c>
+    </row>
+    <row r="632" spans="4:17" x14ac:dyDescent="0.45">
+      <c r="D632" s="1" t="s">
+        <v>2233</v>
+      </c>
+      <c r="G632" s="1" t="s">
+        <v>2234</v>
+      </c>
+      <c r="Q632" s="1" t="s">
+        <v>2235</v>
+      </c>
+    </row>
+    <row r="633" spans="4:17" x14ac:dyDescent="0.45">
+      <c r="D633" s="1" t="s">
+        <v>2237</v>
+      </c>
+      <c r="G633" s="1" t="s">
+        <v>2238</v>
+      </c>
+      <c r="L633" s="1" t="s">
+        <v>2239</v>
+      </c>
+      <c r="Q633" s="1" t="s">
+        <v>2240</v>
+      </c>
+    </row>
+    <row r="634" spans="4:17" x14ac:dyDescent="0.45">
+      <c r="D634" s="1" t="s">
+        <v>2241</v>
+      </c>
+      <c r="Q634" s="1" t="s">
+        <v>2243</v>
+      </c>
+    </row>
+    <row r="635" spans="4:17" x14ac:dyDescent="0.45">
+      <c r="D635" s="1" t="s">
+        <v>2242</v>
+      </c>
+      <c r="Q635" s="1" t="s">
+        <v>2244</v>
+      </c>
+    </row>
+    <row r="636" spans="4:17" x14ac:dyDescent="0.45">
+      <c r="D636" s="1" t="s">
+        <v>2245</v>
+      </c>
+      <c r="G636" s="1" t="s">
+        <v>2246</v>
+      </c>
+      <c r="L636" s="1" t="s">
+        <v>2247</v>
+      </c>
+      <c r="Q636" s="1" t="s">
+        <v>2248</v>
+      </c>
+    </row>
+    <row r="637" spans="4:17" x14ac:dyDescent="0.45">
+      <c r="D637" s="1" t="s">
+        <v>2249</v>
+      </c>
+      <c r="G637" s="1" t="s">
+        <v>2250</v>
+      </c>
+      <c r="L637" s="1" t="s">
+        <v>2251</v>
+      </c>
+      <c r="Q637" s="1" t="s">
+        <v>2252</v>
+      </c>
+    </row>
+    <row r="638" spans="4:17" x14ac:dyDescent="0.45">
+      <c r="D638" s="1" t="s">
+        <v>2253</v>
+      </c>
+      <c r="G638" s="1" t="s">
+        <v>2254</v>
+      </c>
+      <c r="L638" s="1" t="s">
+        <v>2255</v>
+      </c>
+      <c r="Q638" s="1" t="s">
+        <v>2260</v>
+      </c>
+    </row>
+    <row r="639" spans="4:17" x14ac:dyDescent="0.45">
+      <c r="D639" s="1" t="s">
+        <v>2261</v>
+      </c>
+      <c r="G639" s="1" t="s">
+        <v>2262</v>
+      </c>
+      <c r="L639" s="1" t="s">
+        <v>2263</v>
+      </c>
+      <c r="Q639" s="1" t="s">
+        <v>2260</v>
+      </c>
+    </row>
+    <row r="640" spans="4:17" x14ac:dyDescent="0.45">
+      <c r="D640" s="1" t="s">
+        <v>2256</v>
+      </c>
+      <c r="G640" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="L640" s="1" t="s">
+        <v>2258</v>
+      </c>
+      <c r="Q640" s="1" t="s">
+        <v>2259</v>
+      </c>
+    </row>
+    <row r="641" spans="4:17" x14ac:dyDescent="0.45">
+      <c r="D641" s="1" t="s">
+        <v>2264</v>
+      </c>
+      <c r="G641" s="1" t="s">
+        <v>2265</v>
+      </c>
+      <c r="L641" s="1" t="s">
+        <v>2266</v>
+      </c>
+      <c r="Q641" s="1" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="642" spans="4:17" x14ac:dyDescent="0.45">
+      <c r="D642" s="1" t="s">
+        <v>2268</v>
+      </c>
+      <c r="Q642" s="1" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="643" spans="4:17" x14ac:dyDescent="0.45">
+      <c r="D643" s="1" t="s">
+        <v>2269</v>
+      </c>
+      <c r="G643" s="1" t="s">
+        <v>2270</v>
+      </c>
+      <c r="L643" s="1" t="s">
+        <v>2271</v>
+      </c>
+      <c r="Q643" s="1" t="s">
+        <v>2272</v>
+      </c>
+    </row>
+    <row r="644" spans="4:17" x14ac:dyDescent="0.45">
+      <c r="D644" s="1" t="s">
+        <v>2273</v>
+      </c>
+      <c r="G644" s="1" t="s">
+        <v>2274</v>
+      </c>
+      <c r="L644" s="1" t="s">
+        <v>2275</v>
+      </c>
+      <c r="Q644" s="1" t="s">
+        <v>2276</v>
+      </c>
+    </row>
+    <row r="645" spans="4:17" x14ac:dyDescent="0.45">
+      <c r="D645" s="1" t="s">
+        <v>2277</v>
+      </c>
+      <c r="G645" s="1" t="s">
+        <v>2278</v>
+      </c>
+      <c r="L645" s="1" t="s">
+        <v>2279</v>
+      </c>
+      <c r="Q645" s="1" t="s">
+        <v>2279</v>
+      </c>
+    </row>
+    <row r="646" spans="4:17" x14ac:dyDescent="0.45">
+      <c r="D646" s="2" t="s">
+        <v>2280</v>
+      </c>
+      <c r="G646" s="1" t="s">
+        <v>2281</v>
+      </c>
+    </row>
+    <row r="647" spans="4:17" x14ac:dyDescent="0.45">
+      <c r="D647" s="1" t="s">
+        <v>2282</v>
+      </c>
+      <c r="G647" s="1" t="s">
+        <v>2283</v>
+      </c>
+      <c r="L647" s="1" t="s">
+        <v>2284</v>
+      </c>
+      <c r="Q647" s="1" t="s">
+        <v>2285</v>
+      </c>
+    </row>
+    <row r="648" spans="4:17" x14ac:dyDescent="0.45">
+      <c r="D648" s="1" t="s">
+        <v>2286</v>
+      </c>
+      <c r="G648" s="1" t="s">
+        <v>2287</v>
+      </c>
+      <c r="L648" s="1" t="s">
+        <v>2288</v>
+      </c>
+      <c r="Q648" s="3">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="649" spans="4:17" x14ac:dyDescent="0.45">
+      <c r="D649" s="1" t="s">
+        <v>2289</v>
+      </c>
+      <c r="G649" s="1" t="s">
+        <v>2290</v>
+      </c>
+      <c r="L649" s="1" t="s">
+        <v>2291</v>
+      </c>
+      <c r="Q649" s="1" t="s">
+        <v>2292</v>
+      </c>
+    </row>
+    <row r="650" spans="4:17" x14ac:dyDescent="0.45">
+      <c r="D650" s="1" t="s">
+        <v>2293</v>
+      </c>
+      <c r="G650" s="1" t="s">
+        <v>2294</v>
+      </c>
+      <c r="L650" s="1" t="s">
+        <v>2295</v>
+      </c>
+      <c r="Q650" s="1" t="s">
+        <v>2296</v>
+      </c>
+    </row>
+    <row r="651" spans="4:17" x14ac:dyDescent="0.45">
+      <c r="D651" s="1" t="s">
+        <v>2297</v>
+      </c>
+      <c r="G651" s="1" t="s">
+        <v>2298</v>
+      </c>
+      <c r="L651" s="1" t="s">
+        <v>2299</v>
+      </c>
+      <c r="Q651" s="1" t="s">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="652" spans="4:17" x14ac:dyDescent="0.45">
+      <c r="D652" s="1" t="s">
+        <v>2317</v>
+      </c>
+      <c r="G652" s="1" t="s">
+        <v>2318</v>
+      </c>
+      <c r="L652" s="1" t="s">
+        <v>2319</v>
+      </c>
+      <c r="Q652" s="1" t="s">
+        <v>2320</v>
+      </c>
+    </row>
+    <row r="653" spans="4:17" x14ac:dyDescent="0.45">
+      <c r="D653" s="1" t="s">
+        <v>2301</v>
+      </c>
+      <c r="G653" s="1" t="s">
+        <v>2302</v>
+      </c>
+      <c r="L653" s="1" t="s">
+        <v>2303</v>
+      </c>
+      <c r="Q653" s="1" t="s">
+        <v>2304</v>
+      </c>
+    </row>
+    <row r="654" spans="4:17" x14ac:dyDescent="0.45">
+      <c r="D654" s="1" t="s">
+        <v>2305</v>
+      </c>
+      <c r="G654" s="1" t="s">
+        <v>2306</v>
+      </c>
+      <c r="L654" s="1" t="s">
+        <v>2307</v>
+      </c>
+      <c r="Q654" s="1" t="s">
+        <v>2308</v>
+      </c>
+    </row>
+    <row r="655" spans="4:17" x14ac:dyDescent="0.45">
+      <c r="D655" s="1" t="s">
+        <v>2309</v>
+      </c>
+      <c r="G655" s="1" t="s">
+        <v>2310</v>
+      </c>
+      <c r="L655" s="1" t="s">
+        <v>2311</v>
+      </c>
+      <c r="Q655" s="1" t="s">
+        <v>2312</v>
+      </c>
+    </row>
+    <row r="656" spans="4:17" x14ac:dyDescent="0.45">
+      <c r="D656" s="1" t="s">
+        <v>2313</v>
+      </c>
+      <c r="G656" s="1" t="s">
+        <v>2314</v>
+      </c>
+      <c r="L656" s="1" t="s">
+        <v>2315</v>
+      </c>
+      <c r="Q656" s="1" t="s">
+        <v>2316</v>
+      </c>
+    </row>
+    <row r="657" spans="4:17" x14ac:dyDescent="0.45">
+      <c r="D657" s="1" t="s">
+        <v>2321</v>
+      </c>
+      <c r="G657" s="1" t="s">
+        <v>2322</v>
+      </c>
+      <c r="L657" s="1" t="s">
+        <v>2323</v>
+      </c>
+      <c r="Q657" s="1" t="s">
+        <v>2324</v>
+      </c>
+    </row>
+    <row r="658" spans="4:17" x14ac:dyDescent="0.45">
+      <c r="D658" s="1" t="s">
+        <v>2325</v>
+      </c>
+      <c r="G658" s="1" t="s">
+        <v>2326</v>
+      </c>
+      <c r="L658" s="1" t="s">
+        <v>2327</v>
+      </c>
+      <c r="Q658" s="1" t="s">
+        <v>2327</v>
+      </c>
+    </row>
+    <row r="659" spans="4:17" x14ac:dyDescent="0.45">
+      <c r="D659" s="1" t="s">
+        <v>2328</v>
+      </c>
+      <c r="G659" s="1" t="s">
+        <v>2329</v>
+      </c>
+      <c r="L659" s="1" t="s">
+        <v>2330</v>
+      </c>
+      <c r="Q659" s="1" t="s">
+        <v>2331</v>
+      </c>
+    </row>
+    <row r="660" spans="4:17" x14ac:dyDescent="0.45">
+      <c r="D660" s="1" t="s">
+        <v>2332</v>
+      </c>
+      <c r="G660" s="1" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L660" s="1" t="s">
+        <v>2334</v>
+      </c>
+      <c r="Q660" s="1" t="s">
+        <v>2335</v>
       </c>
     </row>
   </sheetData>

--- a/Tiếng Trung/Từ mới.xlsx
+++ b/Tiếng Trung/Từ mới.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E2739B0-1B69-4D93-A4BA-FAE72DFDABBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1502C35A-BAB6-4288-A4A6-67B2436D6B86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11,7 +11,6 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -32,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2397" uniqueCount="2336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2596" uniqueCount="2531">
   <si>
     <t>带领</t>
   </si>
@@ -7040,6 +7039,591 @@
   </si>
   <si>
     <t>bất lực, bó tay, tiếc rằng, tiếc là</t>
+  </si>
+  <si>
+    <t>树立</t>
+  </si>
+  <si>
+    <t>shu` li`</t>
+  </si>
+  <si>
+    <t>thụ lập</t>
+  </si>
+  <si>
+    <t>xây, xây dựng, dựng nên</t>
+  </si>
+  <si>
+    <t>下来</t>
+  </si>
+  <si>
+    <t>xia` lai'</t>
+  </si>
+  <si>
+    <t>hạ lai</t>
+  </si>
+  <si>
+    <t>trôi qua, qua đi</t>
+  </si>
+  <si>
+    <t>依然</t>
+  </si>
+  <si>
+    <t>yi ran'</t>
+  </si>
+  <si>
+    <t>y nhiên</t>
+  </si>
+  <si>
+    <t>vẫn, vẫn cứ, vẫn vậy, y nguyên</t>
+  </si>
+  <si>
+    <t>智者</t>
+  </si>
+  <si>
+    <t>zhi` zhe?</t>
+  </si>
+  <si>
+    <t>trí giả</t>
+  </si>
+  <si>
+    <t>người trí thức, người thông minh</t>
+  </si>
+  <si>
+    <t>倾诉</t>
+  </si>
+  <si>
+    <t>qing su`</t>
+  </si>
+  <si>
+    <t>khuynh tố</t>
+  </si>
+  <si>
+    <t>giãi bày, thổ lộ, tâm sự</t>
+  </si>
+  <si>
+    <t>微笑</t>
+  </si>
+  <si>
+    <t>wei` xiao`</t>
+  </si>
+  <si>
+    <t>vi tiếu</t>
+  </si>
+  <si>
+    <t>mỉm cười</t>
+  </si>
+  <si>
+    <t>开水</t>
+  </si>
+  <si>
+    <t>kai shui?</t>
+  </si>
+  <si>
+    <t>khai thuỷ</t>
+  </si>
+  <si>
+    <t>nước sôi</t>
+  </si>
+  <si>
+    <t>烧</t>
+  </si>
+  <si>
+    <t>shao</t>
+  </si>
+  <si>
+    <t>thiêu</t>
+  </si>
+  <si>
+    <t>đốt, thiêu, cháy</t>
+  </si>
+  <si>
+    <t>壶</t>
+  </si>
+  <si>
+    <t>hu'</t>
+  </si>
+  <si>
+    <t>hồ</t>
+  </si>
+  <si>
+    <t>ấm, bình, hũ</t>
+  </si>
+  <si>
+    <t>墙角</t>
+  </si>
+  <si>
+    <t>qiang' jiao?</t>
+  </si>
+  <si>
+    <t>tường giác</t>
+  </si>
+  <si>
+    <t>góc tường</t>
+  </si>
+  <si>
+    <t>灶</t>
+  </si>
+  <si>
+    <t>zao`</t>
+  </si>
+  <si>
+    <t>táo</t>
+  </si>
+  <si>
+    <t>bếp, lò</t>
+  </si>
+  <si>
+    <t>柴火</t>
+  </si>
+  <si>
+    <t>sài hoả</t>
+  </si>
+  <si>
+    <t>拾</t>
+  </si>
+  <si>
+    <t>shi'</t>
+  </si>
+  <si>
+    <t>thập</t>
+  </si>
+  <si>
+    <t>nhặt, mót</t>
+  </si>
+  <si>
+    <t>枯枝</t>
+  </si>
+  <si>
+    <t>ku zhi</t>
+  </si>
+  <si>
+    <t>khô chi</t>
+  </si>
+  <si>
+    <t>cành khô, củi</t>
+  </si>
+  <si>
+    <t>灶台</t>
+  </si>
+  <si>
+    <t>zao` tai'</t>
+  </si>
+  <si>
+    <t>táo đài</t>
+  </si>
+  <si>
+    <t>cái bếp, kiềng</t>
+  </si>
+  <si>
+    <t>củi, rơm, củi đốt</t>
+  </si>
+  <si>
+    <t>尽</t>
+  </si>
+  <si>
+    <t>jin`</t>
+  </si>
+  <si>
+    <t>tận</t>
+  </si>
+  <si>
+    <t>hết, tận</t>
+  </si>
+  <si>
+    <t>凉</t>
+  </si>
+  <si>
+    <t>liang'</t>
+  </si>
+  <si>
+    <t>lương</t>
+  </si>
+  <si>
+    <t>mát, nguội, mát mẻ</t>
+  </si>
+  <si>
+    <t>充足</t>
+  </si>
+  <si>
+    <t>chong zu'</t>
+  </si>
+  <si>
+    <t>sung túc</t>
+  </si>
+  <si>
+    <t>đầy đủ, dồi dào</t>
+  </si>
+  <si>
+    <t>急于</t>
+  </si>
+  <si>
+    <t>ji' yu'</t>
+  </si>
+  <si>
+    <t>cấp vu</t>
+  </si>
+  <si>
+    <t>vội vàng, nóng lòng, nóng vội</t>
+  </si>
+  <si>
+    <t>不一会</t>
+  </si>
+  <si>
+    <t>chẳng mấy chốc, một lát sau, không lâu sau</t>
+  </si>
+  <si>
+    <t>若有所思</t>
+  </si>
+  <si>
+    <t>ruo` you? Suo? Si</t>
+  </si>
+  <si>
+    <t>nhược hữu sở tư</t>
+  </si>
+  <si>
+    <t>trầm ngâm, trầm tư</t>
+  </si>
+  <si>
+    <t>恍然</t>
+  </si>
+  <si>
+    <t>huang? Ran'</t>
+  </si>
+  <si>
+    <t>hoảng nhiên</t>
+  </si>
+  <si>
+    <t>chợt, đột nhiên</t>
+  </si>
+  <si>
+    <t>大悟</t>
+  </si>
+  <si>
+    <t>da` wu`</t>
+  </si>
+  <si>
+    <t>đại ngộ</t>
+  </si>
+  <si>
+    <t>ngộ ra, hiểu ra, vỡ lẽ</t>
+  </si>
+  <si>
+    <t>业余</t>
+  </si>
+  <si>
+    <t>ye` yu'</t>
+  </si>
+  <si>
+    <t>nghiệp dư</t>
+  </si>
+  <si>
+    <t>rảnh, rảnh rỗi, nghiệp dư, không chuyên</t>
+  </si>
+  <si>
+    <t>利用</t>
+  </si>
+  <si>
+    <t>li` yong`</t>
+  </si>
+  <si>
+    <t>lợi dụng</t>
+  </si>
+  <si>
+    <t>dùng, sử dụng, tận dụng, lợi dụng</t>
+  </si>
+  <si>
+    <t>知识</t>
+  </si>
+  <si>
+    <t>zhi shi</t>
+  </si>
+  <si>
+    <t>tri thức</t>
+  </si>
+  <si>
+    <t>tri thức, kiến thức</t>
+  </si>
+  <si>
+    <t>删繁就简</t>
+  </si>
+  <si>
+    <t>shan fan' jiu` jian?</t>
+  </si>
+  <si>
+    <t>san phồn tựu giản</t>
+  </si>
+  <si>
+    <t>đơn giản hoá, bỏ cái rườm rà giữ đơn giản</t>
+  </si>
+  <si>
+    <t>挂怀</t>
+  </si>
+  <si>
+    <t>gua` huai'</t>
+  </si>
+  <si>
+    <t>quải hoài</t>
+  </si>
+  <si>
+    <t>lo lắng, để trong lòng, đoái hoài</t>
+  </si>
+  <si>
+    <t>半途而废</t>
+  </si>
+  <si>
+    <t>ban` tu' er' fei`</t>
+  </si>
+  <si>
+    <t>Bán đồ nhi phế</t>
+  </si>
+  <si>
+    <t>bỏ dở giữa chừng</t>
+  </si>
+  <si>
+    <t>只会</t>
+  </si>
+  <si>
+    <t>chỉ có thể</t>
+  </si>
+  <si>
+    <t>捡拾</t>
+  </si>
+  <si>
+    <t>jian? Shi'</t>
+  </si>
+  <si>
+    <t>kiểm thập</t>
+  </si>
+  <si>
+    <t>lục tìm, tìm kiếm, góp nhặt</t>
+  </si>
+  <si>
+    <t>zhi? Hui`</t>
+  </si>
+  <si>
+    <t>沸腾</t>
+  </si>
+  <si>
+    <t>fei` teng'</t>
+  </si>
+  <si>
+    <t>phí đằng</t>
+  </si>
+  <si>
+    <t>sôi, sôi sục</t>
+  </si>
+  <si>
+    <t>祝贺</t>
+  </si>
+  <si>
+    <t>zhu` he`</t>
+  </si>
+  <si>
+    <t>chúc hạ</t>
+  </si>
+  <si>
+    <t>chúc mừng</t>
+  </si>
+  <si>
+    <t>敢于</t>
+  </si>
+  <si>
+    <t>gan? Yu'</t>
+  </si>
+  <si>
+    <t>cảm vu</t>
+  </si>
+  <si>
+    <t>dám, có dũng khí</t>
+  </si>
+  <si>
+    <t>珍惜</t>
+  </si>
+  <si>
+    <t>zhen xi</t>
+  </si>
+  <si>
+    <t>trân tích</t>
+  </si>
+  <si>
+    <t>trân trọng</t>
+  </si>
+  <si>
+    <t>chai' huo?</t>
+  </si>
+  <si>
+    <t>丰富</t>
+  </si>
+  <si>
+    <t>feng fu`</t>
+  </si>
+  <si>
+    <t>phong phú</t>
+  </si>
+  <si>
+    <t>phong phú, dồi dào</t>
+  </si>
+  <si>
+    <t>过多</t>
+  </si>
+  <si>
+    <t>guo` duo`</t>
+  </si>
+  <si>
+    <t>quá nhiều</t>
+  </si>
+  <si>
+    <t>quá đa</t>
+  </si>
+  <si>
+    <t>忽视</t>
+  </si>
+  <si>
+    <t>hu shi`</t>
+  </si>
+  <si>
+    <t>hốt thị</t>
+  </si>
+  <si>
+    <t>xem nhẹ, coi nhẹ, bỏ qua</t>
+  </si>
+  <si>
+    <t>成员</t>
+  </si>
+  <si>
+    <t>cheng' yuan'</t>
+  </si>
+  <si>
+    <t>thành viên</t>
+  </si>
+  <si>
+    <t>chi gian</t>
+  </si>
+  <si>
+    <t>giữa</t>
+  </si>
+  <si>
+    <t>花去</t>
+  </si>
+  <si>
+    <t>hua qu`</t>
+  </si>
+  <si>
+    <t>hoa khứ</t>
+  </si>
+  <si>
+    <t>tiêu</t>
+  </si>
+  <si>
+    <t>导致</t>
+  </si>
+  <si>
+    <t>dao? Zhi`</t>
+  </si>
+  <si>
+    <t>đạo trí</t>
+  </si>
+  <si>
+    <t>dẫn đến, gây ra, làm cho</t>
+  </si>
+  <si>
+    <t>度过</t>
+  </si>
+  <si>
+    <t>du` guo`</t>
+  </si>
+  <si>
+    <t>độ quá</t>
+  </si>
+  <si>
+    <t>trải qua, trôi qua</t>
+  </si>
+  <si>
+    <t>靠 A 来 B</t>
+  </si>
+  <si>
+    <t>kao`…lai'</t>
+  </si>
+  <si>
+    <t>kháo….lai</t>
+  </si>
+  <si>
+    <t>dựa vào A để B</t>
+  </si>
+  <si>
+    <t>度过时间</t>
+  </si>
+  <si>
+    <t>giết thời gian</t>
+  </si>
+  <si>
+    <t>总之</t>
+  </si>
+  <si>
+    <t>zong? Zhi</t>
+  </si>
+  <si>
+    <t>tổng chi</t>
+  </si>
+  <si>
+    <t>nói chung, nói tóm lại</t>
+  </si>
+  <si>
+    <t>危害</t>
+  </si>
+  <si>
+    <t>wei hai`</t>
+  </si>
+  <si>
+    <t>nguy hại</t>
+  </si>
+  <si>
+    <t>tác hại, nguy cơ, nguy hại</t>
+  </si>
+  <si>
+    <t>充分</t>
+  </si>
+  <si>
+    <t>chong fen`</t>
+  </si>
+  <si>
+    <t>sung phận</t>
+  </si>
+  <si>
+    <t>đầy đủ(dùng cho sự vật trìu tượng), hết mức</t>
+  </si>
+  <si>
+    <t>引起</t>
+  </si>
+  <si>
+    <t>yin' qi?</t>
+  </si>
+  <si>
+    <t>dẫn khởi</t>
+  </si>
+  <si>
+    <t>dẫn tới</t>
+  </si>
+  <si>
+    <t>占用</t>
+  </si>
+  <si>
+    <t>zhan` yong`</t>
+  </si>
+  <si>
+    <t>chiếm dụng</t>
+  </si>
+  <si>
+    <t>培养</t>
+  </si>
+  <si>
+    <t>pei' yang?</t>
+  </si>
+  <si>
+    <t>bồi dưỡng</t>
+  </si>
+  <si>
+    <t>bồi dưỡng, gây, nuôi cấy</t>
   </si>
 </sst>
 </file>
@@ -7366,17 +7950,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:W660"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="30.75" x14ac:dyDescent="0.45"/>
+  <dimension ref="A2:W711"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="30.6" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="3" width="9.140625" style="1"/>
-    <col min="4" max="4" width="11.28515625" style="1" customWidth="1"/>
-    <col min="5" max="16" width="9.140625" style="1"/>
-    <col min="17" max="17" width="10.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="3" width="9.109375" style="1"/>
+    <col min="4" max="4" width="11.33203125" style="1" customWidth="1"/>
+    <col min="5" max="16" width="9.109375" style="1"/>
+    <col min="17" max="17" width="10.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="2" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D2" s="1" t="s">
         <v>0</v>
       </c>
@@ -7387,7 +7971,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="3" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D3" s="1" t="s">
         <v>3</v>
       </c>
@@ -7398,7 +7982,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="4" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D4" s="1" t="s">
         <v>6</v>
       </c>
@@ -7409,7 +7993,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="5" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D5" s="1" t="s">
         <v>9</v>
       </c>
@@ -7420,7 +8004,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="6" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D6" s="1" t="s">
         <v>12</v>
       </c>
@@ -7431,7 +8015,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="7" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D7" s="1" t="s">
         <v>15</v>
       </c>
@@ -7442,7 +8026,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="8" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D8" s="1" t="s">
         <v>18</v>
       </c>
@@ -7450,7 +8034,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="9" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D9" s="1" t="s">
         <v>20</v>
       </c>
@@ -7461,7 +8045,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="10" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="10" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D10" s="1" t="s">
         <v>22</v>
       </c>
@@ -7472,7 +8056,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="11" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="11" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D11" s="1" t="s">
         <v>493</v>
       </c>
@@ -7483,7 +8067,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="12" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="12" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D12" s="1" t="s">
         <v>24</v>
       </c>
@@ -7494,7 +8078,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="13" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="13" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D13" s="1" t="s">
         <v>26</v>
       </c>
@@ -7505,7 +8089,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="14" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D14" s="1" t="s">
         <v>29</v>
       </c>
@@ -7513,7 +8097,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="15" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D15" s="1" t="s">
         <v>31</v>
       </c>
@@ -7524,7 +8108,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="16" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D16" s="1" t="s">
         <v>34</v>
       </c>
@@ -7535,7 +8119,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="17" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D17" s="1" t="s">
         <v>37</v>
       </c>
@@ -7546,7 +8130,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="18" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="18" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D18" s="1" t="s">
         <v>39</v>
       </c>
@@ -7557,7 +8141,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="19" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D19" s="1" t="s">
         <v>42</v>
       </c>
@@ -7568,7 +8152,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="20" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D20" s="1" t="s">
         <v>45</v>
       </c>
@@ -7579,7 +8163,7 @@
         <v>2073</v>
       </c>
     </row>
-    <row r="21" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="21" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D21" s="1" t="s">
         <v>47</v>
       </c>
@@ -7590,7 +8174,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="22" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="22" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D22" s="1" t="s">
         <v>50</v>
       </c>
@@ -7601,7 +8185,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="23" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="23" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D23" s="1" t="s">
         <v>53</v>
       </c>
@@ -7612,7 +8196,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="24" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="24" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D24" s="1" t="s">
         <v>56</v>
       </c>
@@ -7620,7 +8204,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="25" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="25" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D25" s="1" t="s">
         <v>58</v>
       </c>
@@ -7631,12 +8215,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="26" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D26" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="27" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="27" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D27" s="1" t="s">
         <v>62</v>
       </c>
@@ -7647,7 +8231,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="28" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="28" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D28" s="1" t="s">
         <v>65</v>
       </c>
@@ -7658,7 +8242,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="29" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D29" s="1" t="s">
         <v>68</v>
       </c>
@@ -7666,7 +8250,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="30" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="30" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D30" s="1" t="s">
         <v>70</v>
       </c>
@@ -7677,7 +8261,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="31" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="31" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D31" s="1" t="s">
         <v>73</v>
       </c>
@@ -7685,7 +8269,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="32" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="32" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D32" s="1" t="s">
         <v>75</v>
       </c>
@@ -7696,7 +8280,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="33" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="33" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D33" s="1" t="s">
         <v>78</v>
       </c>
@@ -7707,7 +8291,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="34" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="34" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D34" s="1" t="s">
         <v>80</v>
       </c>
@@ -7718,7 +8302,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="35" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="35" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D35" s="1" t="s">
         <v>83</v>
       </c>
@@ -7729,7 +8313,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="36" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="36" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D36" s="1" t="s">
         <v>86</v>
       </c>
@@ -7740,7 +8324,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="37" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="37" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D37" s="1" t="s">
         <v>89</v>
       </c>
@@ -7751,7 +8335,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="38" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="38" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D38" s="1" t="s">
         <v>92</v>
       </c>
@@ -7762,7 +8346,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="39" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="39" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D39" s="1" t="s">
         <v>95</v>
       </c>
@@ -7773,7 +8357,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="40" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="40" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D40" s="1" t="s">
         <v>98</v>
       </c>
@@ -7784,7 +8368,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="41" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="41" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D41" s="1" t="s">
         <v>24</v>
       </c>
@@ -7795,7 +8379,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="42" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="42" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D42" s="1" t="s">
         <v>101</v>
       </c>
@@ -7806,7 +8390,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="43" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="43" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D43" s="1" t="s">
         <v>105</v>
       </c>
@@ -7817,7 +8401,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="44" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="44" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D44" s="1" t="s">
         <v>108</v>
       </c>
@@ -7828,7 +8412,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="45" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="45" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D45" s="1" t="s">
         <v>111</v>
       </c>
@@ -7839,7 +8423,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="46" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="46" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D46" s="1" t="s">
         <v>114</v>
       </c>
@@ -7850,7 +8434,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="47" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="47" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D47" s="1" t="s">
         <v>117</v>
       </c>
@@ -7861,7 +8445,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="48" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="48" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D48" s="1" t="s">
         <v>120</v>
       </c>
@@ -7872,7 +8456,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="49" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="49" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D49" s="1" t="s">
         <v>123</v>
       </c>
@@ -7883,7 +8467,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="50" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="50" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D50" s="1" t="s">
         <v>126</v>
       </c>
@@ -7894,7 +8478,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="51" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="51" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D51" s="1" t="s">
         <v>129</v>
       </c>
@@ -7902,7 +8486,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="52" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="52" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D52" s="1" t="s">
         <v>131</v>
       </c>
@@ -7913,7 +8497,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="53" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="53" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D53" s="1" t="s">
         <v>134</v>
       </c>
@@ -7924,7 +8508,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="54" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="54" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D54" s="1" t="s">
         <v>137</v>
       </c>
@@ -7932,7 +8516,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="55" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="55" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D55" s="1" t="s">
         <v>138</v>
       </c>
@@ -7943,7 +8527,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="56" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="56" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D56" s="1" t="s">
         <v>141</v>
       </c>
@@ -7954,7 +8538,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="57" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="57" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D57" s="1" t="s">
         <v>144</v>
       </c>
@@ -7965,7 +8549,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="58" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="58" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D58" s="1" t="s">
         <v>147</v>
       </c>
@@ -7976,7 +8560,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="59" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="59" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D59" s="1" t="s">
         <v>152</v>
       </c>
@@ -7987,7 +8571,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="60" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="60" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D60" s="1" t="s">
         <v>155</v>
       </c>
@@ -7998,7 +8582,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="61" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="61" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D61" s="1" t="s">
         <v>158</v>
       </c>
@@ -8009,7 +8593,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="62" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="62" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D62" s="1" t="s">
         <v>161</v>
       </c>
@@ -8020,7 +8604,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="63" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="63" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D63" s="1" t="s">
         <v>164</v>
       </c>
@@ -8031,7 +8615,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="64" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="64" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D64" s="1" t="s">
         <v>167</v>
       </c>
@@ -8042,7 +8626,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="65" spans="4:23" x14ac:dyDescent="0.45">
+    <row r="65" spans="4:23" x14ac:dyDescent="0.55000000000000004">
       <c r="D65" s="1" t="s">
         <v>170</v>
       </c>
@@ -8053,7 +8637,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="66" spans="4:23" x14ac:dyDescent="0.45">
+    <row r="66" spans="4:23" x14ac:dyDescent="0.55000000000000004">
       <c r="D66" s="1" t="s">
         <v>173</v>
       </c>
@@ -8064,7 +8648,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="67" spans="4:23" x14ac:dyDescent="0.45">
+    <row r="67" spans="4:23" x14ac:dyDescent="0.55000000000000004">
       <c r="D67" s="1" t="s">
         <v>176</v>
       </c>
@@ -8075,7 +8659,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="68" spans="4:23" x14ac:dyDescent="0.45">
+    <row r="68" spans="4:23" x14ac:dyDescent="0.55000000000000004">
       <c r="D68" s="1" t="s">
         <v>179</v>
       </c>
@@ -8086,7 +8670,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="69" spans="4:23" x14ac:dyDescent="0.45">
+    <row r="69" spans="4:23" x14ac:dyDescent="0.55000000000000004">
       <c r="D69" s="1" t="s">
         <v>182</v>
       </c>
@@ -8097,7 +8681,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="70" spans="4:23" x14ac:dyDescent="0.45">
+    <row r="70" spans="4:23" x14ac:dyDescent="0.55000000000000004">
       <c r="D70" s="1" t="s">
         <v>185</v>
       </c>
@@ -8108,7 +8692,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="71" spans="4:23" x14ac:dyDescent="0.45">
+    <row r="71" spans="4:23" x14ac:dyDescent="0.55000000000000004">
       <c r="D71" s="1" t="s">
         <v>188</v>
       </c>
@@ -8119,7 +8703,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="72" spans="4:23" x14ac:dyDescent="0.45">
+    <row r="72" spans="4:23" x14ac:dyDescent="0.55000000000000004">
       <c r="D72" s="1" t="s">
         <v>191</v>
       </c>
@@ -8130,7 +8714,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="73" spans="4:23" x14ac:dyDescent="0.45">
+    <row r="73" spans="4:23" x14ac:dyDescent="0.55000000000000004">
       <c r="D73" s="1" t="s">
         <v>194</v>
       </c>
@@ -8138,7 +8722,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="74" spans="4:23" x14ac:dyDescent="0.45">
+    <row r="74" spans="4:23" x14ac:dyDescent="0.55000000000000004">
       <c r="D74" s="1" t="s">
         <v>196</v>
       </c>
@@ -8149,7 +8733,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="75" spans="4:23" x14ac:dyDescent="0.45">
+    <row r="75" spans="4:23" x14ac:dyDescent="0.55000000000000004">
       <c r="D75" s="1" t="s">
         <v>199</v>
       </c>
@@ -8160,7 +8744,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="76" spans="4:23" x14ac:dyDescent="0.45">
+    <row r="76" spans="4:23" x14ac:dyDescent="0.55000000000000004">
       <c r="D76" s="1" t="s">
         <v>204</v>
       </c>
@@ -8171,7 +8755,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="77" spans="4:23" x14ac:dyDescent="0.45">
+    <row r="77" spans="4:23" x14ac:dyDescent="0.55000000000000004">
       <c r="D77" s="1" t="s">
         <v>205</v>
       </c>
@@ -8185,7 +8769,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="78" spans="4:23" x14ac:dyDescent="0.45">
+    <row r="78" spans="4:23" x14ac:dyDescent="0.55000000000000004">
       <c r="D78" s="1" t="s">
         <v>209</v>
       </c>
@@ -8196,7 +8780,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="79" spans="4:23" x14ac:dyDescent="0.45">
+    <row r="79" spans="4:23" x14ac:dyDescent="0.55000000000000004">
       <c r="D79" s="1" t="s">
         <v>212</v>
       </c>
@@ -8207,7 +8791,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="80" spans="4:23" x14ac:dyDescent="0.45">
+    <row r="80" spans="4:23" x14ac:dyDescent="0.55000000000000004">
       <c r="D80" s="1" t="s">
         <v>214</v>
       </c>
@@ -8215,12 +8799,12 @@
         <v>216</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" s="1" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D82" s="1" t="s">
         <v>217</v>
       </c>
@@ -8231,7 +8815,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D83" s="1" t="s">
         <v>220</v>
       </c>
@@ -8242,7 +8826,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D84" s="1" t="s">
         <v>223</v>
       </c>
@@ -8253,7 +8837,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D85" s="1" t="s">
         <v>226</v>
       </c>
@@ -8264,7 +8848,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D86" s="1" t="s">
         <v>229</v>
       </c>
@@ -8275,7 +8859,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D87" s="1" t="s">
         <v>232</v>
       </c>
@@ -8286,7 +8870,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D88" s="1" t="s">
         <v>235</v>
       </c>
@@ -8297,7 +8881,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D89" s="1" t="s">
         <v>238</v>
       </c>
@@ -8308,7 +8892,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D90" s="1" t="s">
         <v>241</v>
       </c>
@@ -8319,7 +8903,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D91" s="1" t="s">
         <v>244</v>
       </c>
@@ -8330,7 +8914,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D92" s="1" t="s">
         <v>247</v>
       </c>
@@ -8338,7 +8922,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D93" s="1" t="s">
         <v>249</v>
       </c>
@@ -8349,7 +8933,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D94" s="1" t="s">
         <v>252</v>
       </c>
@@ -8360,7 +8944,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D95" s="1" t="s">
         <v>255</v>
       </c>
@@ -8371,7 +8955,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D96" s="1" t="s">
         <v>259</v>
       </c>
@@ -8382,7 +8966,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="97" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="97" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D97" s="1" t="s">
         <v>261</v>
       </c>
@@ -8393,7 +8977,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="98" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="98" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D98" s="1" t="s">
         <v>264</v>
       </c>
@@ -8404,7 +8988,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="99" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="99" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D99" s="1" t="s">
         <v>267</v>
       </c>
@@ -8415,7 +8999,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="100" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="100" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D100" s="1" t="s">
         <v>270</v>
       </c>
@@ -8426,7 +9010,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="101" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="101" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D101" s="1" t="s">
         <v>273</v>
       </c>
@@ -8437,7 +9021,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="102" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="102" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D102" s="1" t="s">
         <v>276</v>
       </c>
@@ -8448,7 +9032,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="103" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="103" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D103" s="1" t="s">
         <v>279</v>
       </c>
@@ -8459,7 +9043,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="104" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="104" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D104" s="1" t="s">
         <v>282</v>
       </c>
@@ -8467,7 +9051,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="105" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="105" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D105" s="1" t="s">
         <v>284</v>
       </c>
@@ -8478,7 +9062,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="106" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="106" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D106" s="1" t="s">
         <v>313</v>
       </c>
@@ -8486,7 +9070,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="107" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="107" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D107" s="1" t="s">
         <v>287</v>
       </c>
@@ -8497,7 +9081,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="108" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="108" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D108" s="1" t="s">
         <v>290</v>
       </c>
@@ -8508,7 +9092,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="109" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="109" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D109" s="1" t="s">
         <v>293</v>
       </c>
@@ -8519,7 +9103,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="110" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="110" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D110" s="1" t="s">
         <v>296</v>
       </c>
@@ -8530,7 +9114,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="111" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="111" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D111" s="1" t="s">
         <v>299</v>
       </c>
@@ -8541,7 +9125,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="112" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="112" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D112" s="1" t="s">
         <v>302</v>
       </c>
@@ -8552,7 +9136,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="113" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="113" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D113" s="1" t="s">
         <v>305</v>
       </c>
@@ -8563,7 +9147,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="114" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="114" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D114" s="1" t="s">
         <v>307</v>
       </c>
@@ -8574,7 +9158,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="115" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="115" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D115" s="1" t="s">
         <v>310</v>
       </c>
@@ -8585,7 +9169,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="116" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="116" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D116" s="1" t="s">
         <v>315</v>
       </c>
@@ -8596,7 +9180,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="117" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="117" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D117" s="1" t="s">
         <v>318</v>
       </c>
@@ -8607,7 +9191,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="118" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="118" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D118" s="1" t="s">
         <v>321</v>
       </c>
@@ -8618,7 +9202,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="119" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="119" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D119" s="1" t="s">
         <v>324</v>
       </c>
@@ -8629,7 +9213,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="120" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="120" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D120" s="1" t="s">
         <v>327</v>
       </c>
@@ -8640,7 +9224,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="121" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="121" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D121" s="1" t="s">
         <v>330</v>
       </c>
@@ -8651,7 +9235,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="122" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="122" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D122" s="1" t="s">
         <v>333</v>
       </c>
@@ -8662,7 +9246,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="123" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="123" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D123" s="1" t="s">
         <v>336</v>
       </c>
@@ -8673,7 +9257,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="124" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="124" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D124" s="1" t="s">
         <v>339</v>
       </c>
@@ -8684,7 +9268,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="125" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="125" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D125" s="1" t="s">
         <v>341</v>
       </c>
@@ -8695,7 +9279,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="126" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="126" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D126" s="1" t="s">
         <v>345</v>
       </c>
@@ -8706,7 +9290,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="127" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="127" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D127" s="1" t="s">
         <v>348</v>
       </c>
@@ -8717,7 +9301,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="128" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="128" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D128" s="1" t="s">
         <v>351</v>
       </c>
@@ -8728,7 +9312,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="129" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="129" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D129" s="1" t="s">
         <v>354</v>
       </c>
@@ -8736,7 +9320,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="130" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="130" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D130" s="1" t="s">
         <v>356</v>
       </c>
@@ -8747,7 +9331,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="131" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="131" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D131" s="1" t="s">
         <v>359</v>
       </c>
@@ -8758,7 +9342,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="132" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="132" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D132" s="1" t="s">
         <v>362</v>
       </c>
@@ -8769,7 +9353,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="133" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="133" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D133" s="1" t="s">
         <v>365</v>
       </c>
@@ -8780,7 +9364,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="134" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="134" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D134" s="1" t="s">
         <v>368</v>
       </c>
@@ -8791,7 +9375,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="135" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="135" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D135" s="1" t="s">
         <v>370</v>
       </c>
@@ -8802,7 +9386,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="136" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="136" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D136" s="1" t="s">
         <v>373</v>
       </c>
@@ -8813,7 +9397,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="137" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="137" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D137" s="1" t="s">
         <v>375</v>
       </c>
@@ -8824,7 +9408,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="138" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="138" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D138" s="1" t="s">
         <v>378</v>
       </c>
@@ -8835,7 +9419,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="139" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="139" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D139" s="1" t="s">
         <v>381</v>
       </c>
@@ -8846,7 +9430,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="140" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="140" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D140" s="1" t="s">
         <v>384</v>
       </c>
@@ -8857,7 +9441,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="141" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="141" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D141" s="1" t="s">
         <v>387</v>
       </c>
@@ -8868,7 +9452,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="142" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="142" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D142" s="1" t="s">
         <v>390</v>
       </c>
@@ -8879,7 +9463,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="143" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="143" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D143" s="1" t="s">
         <v>393</v>
       </c>
@@ -8890,7 +9474,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="144" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="144" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D144" s="1" t="s">
         <v>396</v>
       </c>
@@ -8901,7 +9485,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="145" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="145" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D145" s="1" t="s">
         <v>399</v>
       </c>
@@ -8909,7 +9493,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="146" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="146" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D146" s="1" t="s">
         <v>400</v>
       </c>
@@ -8920,7 +9504,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="147" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="147" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D147" s="1" t="s">
         <v>403</v>
       </c>
@@ -8931,7 +9515,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="148" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="148" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D148" s="1" t="s">
         <v>406</v>
       </c>
@@ -8942,7 +9526,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="149" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="149" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D149" s="1" t="s">
         <v>409</v>
       </c>
@@ -8950,7 +9534,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="150" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="150" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D150" s="1" t="s">
         <v>411</v>
       </c>
@@ -8961,7 +9545,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="151" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="151" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D151" s="1" t="s">
         <v>414</v>
       </c>
@@ -8972,7 +9556,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="152" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="152" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D152" s="1" t="s">
         <v>417</v>
       </c>
@@ -8983,7 +9567,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="153" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="153" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D153" s="1" t="s">
         <v>420</v>
       </c>
@@ -8994,7 +9578,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="154" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="154" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D154" s="1" t="s">
         <v>498</v>
       </c>
@@ -9005,7 +9589,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="155" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="155" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D155" s="1" t="s">
         <v>423</v>
       </c>
@@ -9016,7 +9600,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="156" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="156" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D156" s="1" t="s">
         <v>425</v>
       </c>
@@ -9027,7 +9611,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="157" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="157" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D157" s="1" t="s">
         <v>428</v>
       </c>
@@ -9038,7 +9622,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="158" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="158" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D158" s="1" t="s">
         <v>431</v>
       </c>
@@ -9046,7 +9630,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="159" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="159" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D159" s="1" t="s">
         <v>433</v>
       </c>
@@ -9057,7 +9641,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="160" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="160" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D160" s="1" t="s">
         <v>436</v>
       </c>
@@ -9068,7 +9652,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="161" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="161" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D161" s="1" t="s">
         <v>439</v>
       </c>
@@ -9079,7 +9663,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="162" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="162" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D162" s="1" t="s">
         <v>442</v>
       </c>
@@ -9093,7 +9677,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="163" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="163" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D163" s="1" t="s">
         <v>444</v>
       </c>
@@ -9107,7 +9691,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="164" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="164" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D164" s="1" t="s">
         <v>447</v>
       </c>
@@ -9121,7 +9705,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="165" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="165" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D165" s="1" t="s">
         <v>449</v>
       </c>
@@ -9135,7 +9719,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="166" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="166" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D166" s="1" t="s">
         <v>452</v>
       </c>
@@ -9149,7 +9733,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="167" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="167" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D167" s="1" t="s">
         <v>455</v>
       </c>
@@ -9163,7 +9747,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="168" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="168" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D168" s="1" t="s">
         <v>458</v>
       </c>
@@ -9177,7 +9761,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="169" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="169" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D169" s="1" t="s">
         <v>460</v>
       </c>
@@ -9191,7 +9775,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="170" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="170" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D170" s="1" t="s">
         <v>463</v>
       </c>
@@ -9205,7 +9789,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="171" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="171" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D171" s="1" t="s">
         <v>466</v>
       </c>
@@ -9219,7 +9803,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="172" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="172" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D172" s="1" t="s">
         <v>468</v>
       </c>
@@ -9230,7 +9814,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="173" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="173" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D173" s="1" t="s">
         <v>517</v>
       </c>
@@ -9244,7 +9828,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="174" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="174" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D174" s="1" t="s">
         <v>518</v>
       </c>
@@ -9258,7 +9842,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="175" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="175" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D175" s="1" t="s">
         <v>501</v>
       </c>
@@ -9269,7 +9853,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="176" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="176" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D176" s="1" t="s">
         <v>504</v>
       </c>
@@ -9283,7 +9867,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="177" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="177" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D177" s="1" t="s">
         <v>507</v>
       </c>
@@ -9297,7 +9881,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="178" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="178" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D178" s="1" t="s">
         <v>511</v>
       </c>
@@ -9311,7 +9895,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="179" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="179" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D179" s="1" t="s">
         <v>514</v>
       </c>
@@ -9325,7 +9909,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="180" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="180" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D180" s="1" t="s">
         <v>523</v>
       </c>
@@ -9339,7 +9923,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="181" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="181" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D181" s="1" t="s">
         <v>526</v>
       </c>
@@ -9353,7 +9937,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="182" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="182" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D182" s="1" t="s">
         <v>530</v>
       </c>
@@ -9367,7 +9951,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="183" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="183" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D183" s="1" t="s">
         <v>533</v>
       </c>
@@ -9381,7 +9965,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="184" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="184" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D184" s="1" t="s">
         <v>536</v>
       </c>
@@ -9395,7 +9979,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="185" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="185" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D185" s="1" t="s">
         <v>540</v>
       </c>
@@ -9409,7 +9993,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="186" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="186" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D186" s="1" t="s">
         <v>543</v>
       </c>
@@ -9423,7 +10007,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="187" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="187" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D187" s="1" t="s">
         <v>545</v>
       </c>
@@ -9437,7 +10021,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="188" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="188" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D188" s="1" t="s">
         <v>548</v>
       </c>
@@ -9451,7 +10035,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="189" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="189" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D189" s="1" t="s">
         <v>551</v>
       </c>
@@ -9465,7 +10049,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="190" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="190" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D190" s="1" t="s">
         <v>559</v>
       </c>
@@ -9479,7 +10063,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="191" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="191" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D191" s="1" t="s">
         <v>562</v>
       </c>
@@ -9490,7 +10074,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="192" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="192" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D192" s="1" t="s">
         <v>565</v>
       </c>
@@ -9504,7 +10088,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="193" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="193" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D193" s="1" t="s">
         <v>569</v>
       </c>
@@ -9518,7 +10102,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="194" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="194" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D194" s="1" t="s">
         <v>576</v>
       </c>
@@ -9532,7 +10116,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="195" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="195" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D195" s="1" t="s">
         <v>574</v>
       </c>
@@ -9543,7 +10127,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="196" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="196" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D196" s="1" t="s">
         <v>580</v>
       </c>
@@ -9557,7 +10141,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="197" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="197" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D197" s="1" t="s">
         <v>584</v>
       </c>
@@ -9568,7 +10152,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="198" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="198" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D198" s="1" t="s">
         <v>587</v>
       </c>
@@ -9582,7 +10166,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="199" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="199" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D199" s="1" t="s">
         <v>590</v>
       </c>
@@ -9593,7 +10177,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="200" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="200" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D200" s="1" t="s">
         <v>593</v>
       </c>
@@ -9607,7 +10191,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="201" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="201" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D201" s="1" t="s">
         <v>487</v>
       </c>
@@ -9621,7 +10205,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="202" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="202" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D202" s="1" t="s">
         <v>600</v>
       </c>
@@ -9635,7 +10219,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="203" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="203" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D203" s="1" t="s">
         <v>604</v>
       </c>
@@ -9649,7 +10233,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="204" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="204" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D204" s="1" t="s">
         <v>606</v>
       </c>
@@ -9660,7 +10244,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="205" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="205" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D205" s="1" t="s">
         <v>611</v>
       </c>
@@ -9668,7 +10252,7 @@
         <v>1597</v>
       </c>
     </row>
-    <row r="206" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="206" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D206" s="1" t="s">
         <v>612</v>
       </c>
@@ -9679,7 +10263,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="207" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="207" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D207" s="1" t="s">
         <v>615</v>
       </c>
@@ -9693,7 +10277,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="208" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="208" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D208" s="1" t="s">
         <v>619</v>
       </c>
@@ -9707,7 +10291,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="209" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="209" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D209" s="1" t="s">
         <v>623</v>
       </c>
@@ -9721,7 +10305,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="210" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="210" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D210" s="1" t="s">
         <v>627</v>
       </c>
@@ -9735,7 +10319,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="211" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="211" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D211" s="1" t="s">
         <v>631</v>
       </c>
@@ -9749,7 +10333,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="212" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="212" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D212" s="1" t="s">
         <v>472</v>
       </c>
@@ -9763,7 +10347,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="213" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="213" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D213" s="1" t="s">
         <v>636</v>
       </c>
@@ -9777,7 +10361,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="214" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="214" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D214" s="1" t="s">
         <v>640</v>
       </c>
@@ -9791,7 +10375,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="215" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="215" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D215" s="1" t="s">
         <v>644</v>
       </c>
@@ -9805,7 +10389,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="216" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="216" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D216" s="1" t="s">
         <v>648</v>
       </c>
@@ -9819,7 +10403,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="217" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="217" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D217" s="1" t="s">
         <v>652</v>
       </c>
@@ -9833,7 +10417,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="218" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="218" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D218" s="1" t="s">
         <v>656</v>
       </c>
@@ -9847,7 +10431,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="219" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="219" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D219" s="1" t="s">
         <v>660</v>
       </c>
@@ -9861,7 +10445,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="220" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="220" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D220" s="1" t="s">
         <v>663</v>
       </c>
@@ -9875,7 +10459,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="221" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="221" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D221" s="1" t="s">
         <v>667</v>
       </c>
@@ -9889,7 +10473,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="222" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="222" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D222" s="1" t="s">
         <v>671</v>
       </c>
@@ -9903,7 +10487,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="223" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="223" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D223" s="1" t="s">
         <v>675</v>
       </c>
@@ -9917,7 +10501,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="224" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="224" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D224" s="1" t="s">
         <v>679</v>
       </c>
@@ -9931,7 +10515,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="225" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="225" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D225" s="1" t="s">
         <v>683</v>
       </c>
@@ -9945,7 +10529,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="226" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="226" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D226" s="1" t="s">
         <v>687</v>
       </c>
@@ -9959,7 +10543,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="227" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="227" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D227" s="1" t="s">
         <v>691</v>
       </c>
@@ -9973,7 +10557,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="228" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="228" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D228" s="1" t="s">
         <v>695</v>
       </c>
@@ -9987,7 +10571,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="229" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="229" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D229" s="1" t="s">
         <v>699</v>
       </c>
@@ -10001,7 +10585,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="230" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="230" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D230" s="1" t="s">
         <v>703</v>
       </c>
@@ -10015,7 +10599,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="231" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="231" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D231" s="1" t="s">
         <v>707</v>
       </c>
@@ -10029,7 +10613,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="232" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="232" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D232" s="1" t="s">
         <v>711</v>
       </c>
@@ -10043,7 +10627,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="233" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="233" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D233" s="1" t="s">
         <v>715</v>
       </c>
@@ -10057,7 +10641,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="234" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="234" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D234" s="1" t="s">
         <v>718</v>
       </c>
@@ -10071,7 +10655,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="235" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="235" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D235" s="1" t="s">
         <v>722</v>
       </c>
@@ -10085,7 +10669,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="236" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="236" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D236" s="1" t="s">
         <v>726</v>
       </c>
@@ -10099,7 +10683,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="237" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="237" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D237" s="1" t="s">
         <v>730</v>
       </c>
@@ -10113,7 +10697,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="238" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="238" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D238" s="1" t="s">
         <v>734</v>
       </c>
@@ -10127,7 +10711,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="239" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="239" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D239" s="1" t="s">
         <v>738</v>
       </c>
@@ -10141,7 +10725,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="240" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="240" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D240" s="1" t="s">
         <v>742</v>
       </c>
@@ -10155,7 +10739,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="241" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="241" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D241" s="1" t="s">
         <v>746</v>
       </c>
@@ -10169,7 +10753,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="242" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="242" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D242" s="1" t="s">
         <v>750</v>
       </c>
@@ -10183,7 +10767,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="243" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="243" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D243" s="1" t="s">
         <v>754</v>
       </c>
@@ -10197,7 +10781,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="244" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="244" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D244" s="1" t="s">
         <v>758</v>
       </c>
@@ -10211,7 +10795,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="245" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="245" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D245" s="1" t="s">
         <v>763</v>
       </c>
@@ -10225,7 +10809,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="246" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="246" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D246" s="1" t="s">
         <v>767</v>
       </c>
@@ -10239,7 +10823,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="247" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="247" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D247" s="1" t="s">
         <v>771</v>
       </c>
@@ -10253,7 +10837,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="248" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="248" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D248" s="1" t="s">
         <v>775</v>
       </c>
@@ -10267,7 +10851,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="249" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="249" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D249" s="1" t="s">
         <v>779</v>
       </c>
@@ -10281,7 +10865,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="250" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="250" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D250" s="1" t="s">
         <v>782</v>
       </c>
@@ -10295,7 +10879,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="251" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="251" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D251" s="1" t="s">
         <v>786</v>
       </c>
@@ -10309,7 +10893,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="252" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="252" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D252" s="1" t="s">
         <v>480</v>
       </c>
@@ -10323,7 +10907,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="253" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="253" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D253" s="1" t="s">
         <v>792</v>
       </c>
@@ -10337,7 +10921,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="254" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="254" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D254" s="1" t="s">
         <v>796</v>
       </c>
@@ -10351,7 +10935,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="255" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="255" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D255" s="1" t="s">
         <v>800</v>
       </c>
@@ -10362,7 +10946,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="256" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="256" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D256" s="1" t="s">
         <v>803</v>
       </c>
@@ -10376,7 +10960,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="257" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="257" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D257" s="1" t="s">
         <v>807</v>
       </c>
@@ -10390,7 +10974,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="258" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="258" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D258" s="1" t="s">
         <v>830</v>
       </c>
@@ -10404,7 +10988,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="259" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="259" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D259" s="1" t="s">
         <v>811</v>
       </c>
@@ -10418,7 +11002,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="260" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="260" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D260" s="1" t="s">
         <v>815</v>
       </c>
@@ -10432,7 +11016,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="261" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="261" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D261" s="1" t="s">
         <v>819</v>
       </c>
@@ -10446,7 +11030,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="262" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="262" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D262" s="1" t="s">
         <v>823</v>
       </c>
@@ -10460,7 +11044,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="263" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="263" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D263" s="1" t="s">
         <v>826</v>
       </c>
@@ -10474,7 +11058,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="264" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="264" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D264" s="1" t="s">
         <v>909</v>
       </c>
@@ -10488,7 +11072,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="265" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="265" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D265" s="1" t="s">
         <v>834</v>
       </c>
@@ -10502,7 +11086,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="266" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="266" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D266" s="1" t="s">
         <v>838</v>
       </c>
@@ -10516,7 +11100,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="267" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="267" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D267" s="1" t="s">
         <v>905</v>
       </c>
@@ -10530,7 +11114,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="268" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="268" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D268" s="1" t="s">
         <v>842</v>
       </c>
@@ -10544,7 +11128,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="269" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="269" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D269" s="1" t="s">
         <v>877</v>
       </c>
@@ -10558,7 +11142,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="270" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="270" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D270" s="1" t="s">
         <v>845</v>
       </c>
@@ -10572,7 +11156,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="271" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="271" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D271" s="1" t="s">
         <v>849</v>
       </c>
@@ -10586,7 +11170,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="272" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="272" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D272" s="1" t="s">
         <v>853</v>
       </c>
@@ -10600,7 +11184,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="273" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="273" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D273" s="1" t="s">
         <v>913</v>
       </c>
@@ -10614,7 +11198,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="274" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="274" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D274" s="1" t="s">
         <v>857</v>
       </c>
@@ -10628,7 +11212,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="275" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="275" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D275" s="1" t="s">
         <v>861</v>
       </c>
@@ -10642,7 +11226,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="276" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="276" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D276" s="1" t="s">
         <v>917</v>
       </c>
@@ -10656,7 +11240,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="277" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="277" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D277" s="1" t="s">
         <v>865</v>
       </c>
@@ -10670,7 +11254,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="278" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="278" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D278" s="1" t="s">
         <v>869</v>
       </c>
@@ -10684,7 +11268,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="279" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="279" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D279" s="1" t="s">
         <v>873</v>
       </c>
@@ -10698,7 +11282,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="280" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="280" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D280" s="1" t="s">
         <v>921</v>
       </c>
@@ -10712,7 +11296,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="281" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="281" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D281" s="1" t="s">
         <v>925</v>
       </c>
@@ -10726,7 +11310,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="282" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="282" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D282" s="1" t="s">
         <v>929</v>
       </c>
@@ -10740,7 +11324,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="283" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="283" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D283" s="1" t="s">
         <v>933</v>
       </c>
@@ -10754,7 +11338,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="284" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="284" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D284" s="1" t="s">
         <v>937</v>
       </c>
@@ -10768,7 +11352,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="285" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="285" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D285" s="1" t="s">
         <v>941</v>
       </c>
@@ -10782,7 +11366,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="286" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="286" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D286" s="1" t="s">
         <v>945</v>
       </c>
@@ -10796,7 +11380,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="287" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="287" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D287" s="1" t="s">
         <v>949</v>
       </c>
@@ -10810,7 +11394,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="288" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="288" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D288" s="1" t="s">
         <v>952</v>
       </c>
@@ -10824,7 +11408,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="289" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="289" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D289" s="1" t="s">
         <v>956</v>
       </c>
@@ -10838,7 +11422,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="290" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="290" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D290" s="1" t="s">
         <v>960</v>
       </c>
@@ -10852,7 +11436,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="291" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="291" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D291" s="1" t="s">
         <v>964</v>
       </c>
@@ -10866,7 +11450,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="292" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="292" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D292" s="1" t="s">
         <v>486</v>
       </c>
@@ -10880,7 +11464,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="293" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="293" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D293" s="1" t="s">
         <v>968</v>
       </c>
@@ -10894,7 +11478,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="294" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="294" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D294" s="1" t="s">
         <v>972</v>
       </c>
@@ -10908,7 +11492,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="295" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="295" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D295" s="1" t="s">
         <v>975</v>
       </c>
@@ -10922,7 +11506,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="296" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="296" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D296" s="1" t="s">
         <v>979</v>
       </c>
@@ -10936,7 +11520,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="297" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="297" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D297" s="1" t="s">
         <v>983</v>
       </c>
@@ -10950,7 +11534,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="298" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="298" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D298" s="1" t="s">
         <v>987</v>
       </c>
@@ -10964,7 +11548,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="299" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="299" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D299" s="1" t="s">
         <v>991</v>
       </c>
@@ -10978,7 +11562,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="300" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="300" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D300" s="1" t="s">
         <v>995</v>
       </c>
@@ -10992,7 +11576,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="301" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="301" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D301" s="1" t="s">
         <v>999</v>
       </c>
@@ -11006,7 +11590,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="302" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="302" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D302" s="1" t="s">
         <v>1002</v>
       </c>
@@ -11020,7 +11604,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="303" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="303" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D303" s="1" t="s">
         <v>1006</v>
       </c>
@@ -11034,7 +11618,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="304" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="304" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D304" s="1" t="s">
         <v>1010</v>
       </c>
@@ -11048,7 +11632,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="305" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="305" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D305" s="1" t="s">
         <v>1014</v>
       </c>
@@ -11062,7 +11646,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="306" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="306" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D306" s="1" t="s">
         <v>1017</v>
       </c>
@@ -11076,7 +11660,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="307" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="307" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D307" s="1" t="s">
         <v>1022</v>
       </c>
@@ -11090,7 +11674,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="308" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="308" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D308" s="1" t="s">
         <v>1026</v>
       </c>
@@ -11104,7 +11688,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="309" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="309" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D309" s="1" t="s">
         <v>1029</v>
       </c>
@@ -11118,7 +11702,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="310" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="310" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D310" s="1" t="s">
         <v>1033</v>
       </c>
@@ -11132,7 +11716,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="311" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="311" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D311" s="1" t="s">
         <v>1037</v>
       </c>
@@ -11146,7 +11730,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="312" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="312" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D312" s="1" t="s">
         <v>1041</v>
       </c>
@@ -11160,7 +11744,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="313" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="313" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D313" s="1" t="s">
         <v>1045</v>
       </c>
@@ -11174,7 +11758,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="314" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="314" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D314" s="1" t="s">
         <v>1079</v>
       </c>
@@ -11188,7 +11772,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="315" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="315" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D315" s="1" t="s">
         <v>1083</v>
       </c>
@@ -11202,7 +11786,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="316" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="316" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D316" s="1" t="s">
         <v>1048</v>
       </c>
@@ -11216,7 +11800,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="317" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="317" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D317" s="1" t="s">
         <v>1052</v>
       </c>
@@ -11230,7 +11814,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="318" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="318" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D318" s="1" t="s">
         <v>1057</v>
       </c>
@@ -11244,7 +11828,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="319" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="319" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D319" s="1" t="s">
         <v>1061</v>
       </c>
@@ -11258,7 +11842,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="320" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="320" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D320" s="1" t="s">
         <v>1065</v>
       </c>
@@ -11272,7 +11856,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="321" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="321" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D321" s="1" t="s">
         <v>1068</v>
       </c>
@@ -11280,7 +11864,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="322" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="322" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D322" s="1" t="s">
         <v>1070</v>
       </c>
@@ -11294,7 +11878,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="323" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="323" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D323" s="1" t="s">
         <v>1074</v>
       </c>
@@ -11308,7 +11892,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="324" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="324" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D324" s="1" t="s">
         <v>1087</v>
       </c>
@@ -11322,7 +11906,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="325" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="325" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D325" s="1" t="s">
         <v>483</v>
       </c>
@@ -11333,7 +11917,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="326" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="326" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D326" s="1" t="s">
         <v>1100</v>
       </c>
@@ -11347,7 +11931,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="327" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="327" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D327" s="1" t="s">
         <v>1092</v>
       </c>
@@ -11361,7 +11945,7 @@
         <v>1095</v>
       </c>
     </row>
-    <row r="328" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="328" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D328" s="1" t="s">
         <v>1096</v>
       </c>
@@ -11375,7 +11959,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="329" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="329" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D329" s="1" t="s">
         <v>1104</v>
       </c>
@@ -11389,7 +11973,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="330" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="330" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D330" s="1" t="s">
         <v>1107</v>
       </c>
@@ -11403,7 +11987,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="331" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="331" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D331" s="1" t="s">
         <v>1110</v>
       </c>
@@ -11417,7 +12001,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="332" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="332" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D332" s="1" t="s">
         <v>1115</v>
       </c>
@@ -11431,7 +12015,7 @@
         <v>1118</v>
       </c>
     </row>
-    <row r="333" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="333" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D333" s="1" t="s">
         <v>1119</v>
       </c>
@@ -11445,7 +12029,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="334" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="334" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D334" s="1" t="s">
         <v>1123</v>
       </c>
@@ -11459,7 +12043,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="335" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="335" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D335" s="1" t="s">
         <v>1127</v>
       </c>
@@ -11473,7 +12057,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="336" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="336" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D336" s="1" t="s">
         <v>1131</v>
       </c>
@@ -11487,7 +12071,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="337" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="337" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D337" s="1" t="s">
         <v>1135</v>
       </c>
@@ -11501,7 +12085,7 @@
         <v>1138</v>
       </c>
     </row>
-    <row r="338" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="338" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D338" s="1" t="s">
         <v>1139</v>
       </c>
@@ -11515,7 +12099,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="339" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="339" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D339" s="1" t="s">
         <v>1143</v>
       </c>
@@ -11529,7 +12113,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="340" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="340" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D340" s="1" t="s">
         <v>1147</v>
       </c>
@@ -11543,7 +12127,7 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="341" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="341" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D341" s="1" t="s">
         <v>1151</v>
       </c>
@@ -11557,7 +12141,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="342" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="342" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D342" s="1" t="s">
         <v>1154</v>
       </c>
@@ -11571,7 +12155,7 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="343" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="343" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D343" s="1" t="s">
         <v>1158</v>
       </c>
@@ -11585,7 +12169,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="344" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="344" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D344" s="1" t="s">
         <v>1162</v>
       </c>
@@ -11599,7 +12183,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="345" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="345" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D345" s="1" t="s">
         <v>1166</v>
       </c>
@@ -11613,7 +12197,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="346" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="346" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D346" s="1" t="s">
         <v>1169</v>
       </c>
@@ -11627,7 +12211,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="347" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="347" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D347" s="1" t="s">
         <v>1173</v>
       </c>
@@ -11641,7 +12225,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="348" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="348" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D348" s="1" t="s">
         <v>1204</v>
       </c>
@@ -11655,7 +12239,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="349" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="349" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D349" s="1" t="s">
         <v>1208</v>
       </c>
@@ -11669,7 +12253,7 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="350" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="350" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D350" s="1" t="s">
         <v>1177</v>
       </c>
@@ -11683,7 +12267,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="351" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="351" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D351" s="1" t="s">
         <v>1181</v>
       </c>
@@ -11697,7 +12281,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="352" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="352" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D352" s="1" t="s">
         <v>1185</v>
       </c>
@@ -11711,7 +12295,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="353" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="353" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D353" s="1" t="s">
         <v>1231</v>
       </c>
@@ -11725,7 +12309,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="354" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="354" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D354" s="1" t="s">
         <v>1212</v>
       </c>
@@ -11739,7 +12323,7 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="355" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="355" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D355" s="1" t="s">
         <v>1188</v>
       </c>
@@ -11753,7 +12337,7 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="356" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="356" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D356" s="1" t="s">
         <v>1192</v>
       </c>
@@ -11767,7 +12351,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="357" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="357" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D357" s="1" t="s">
         <v>1196</v>
       </c>
@@ -11781,7 +12365,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="358" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="358" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D358" s="1" t="s">
         <v>1216</v>
       </c>
@@ -11792,7 +12376,7 @@
         <v>1218</v>
       </c>
     </row>
-    <row r="359" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="359" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D359" s="1" t="s">
         <v>1200</v>
       </c>
@@ -11806,7 +12390,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="360" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="360" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D360" s="1" t="s">
         <v>1219</v>
       </c>
@@ -11820,7 +12404,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="361" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="361" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D361" s="1" t="s">
         <v>1223</v>
       </c>
@@ -11834,7 +12418,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="362" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="362" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D362" s="1" t="s">
         <v>1227</v>
       </c>
@@ -11848,7 +12432,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="363" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="363" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D363" s="1" t="s">
         <v>1235</v>
       </c>
@@ -11862,7 +12446,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="364" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="364" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D364" s="1" t="s">
         <v>475</v>
       </c>
@@ -11876,7 +12460,7 @@
         <v>1241</v>
       </c>
     </row>
-    <row r="365" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="365" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D365" s="1" t="s">
         <v>1242</v>
       </c>
@@ -11890,7 +12474,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="366" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="366" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D366" s="1" t="s">
         <v>1246</v>
       </c>
@@ -11904,7 +12488,7 @@
         <v>1249</v>
       </c>
     </row>
-    <row r="367" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="367" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D367" s="1" t="s">
         <v>1250</v>
       </c>
@@ -11918,7 +12502,7 @@
         <v>1253</v>
       </c>
     </row>
-    <row r="368" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="368" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D368" s="1" t="s">
         <v>1254</v>
       </c>
@@ -11932,7 +12516,7 @@
         <v>1257</v>
       </c>
     </row>
-    <row r="369" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="369" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D369" s="1" t="s">
         <v>1258</v>
       </c>
@@ -11946,7 +12530,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="370" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="370" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D370" s="1" t="s">
         <v>1262</v>
       </c>
@@ -11960,7 +12544,7 @@
         <v>1265</v>
       </c>
     </row>
-    <row r="371" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="371" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D371" s="1" t="s">
         <v>1266</v>
       </c>
@@ -11974,7 +12558,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="372" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="372" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D372" s="1" t="s">
         <v>1270</v>
       </c>
@@ -11988,7 +12572,7 @@
         <v>1273</v>
       </c>
     </row>
-    <row r="373" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="373" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D373" s="1" t="s">
         <v>1274</v>
       </c>
@@ -12002,7 +12586,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="374" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="374" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D374" s="1" t="s">
         <v>1278</v>
       </c>
@@ -12016,7 +12600,7 @@
         <v>1281</v>
       </c>
     </row>
-    <row r="375" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="375" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D375" s="1" t="s">
         <v>1282</v>
       </c>
@@ -12030,7 +12614,7 @@
         <v>1284</v>
       </c>
     </row>
-    <row r="376" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="376" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D376" s="1" t="s">
         <v>1300</v>
       </c>
@@ -12041,7 +12625,7 @@
         <v>1334</v>
       </c>
     </row>
-    <row r="377" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="377" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D377" s="1" t="s">
         <v>1285</v>
       </c>
@@ -12055,7 +12639,7 @@
         <v>1287</v>
       </c>
     </row>
-    <row r="378" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="378" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D378" s="1" t="s">
         <v>1288</v>
       </c>
@@ -12069,7 +12653,7 @@
         <v>1291</v>
       </c>
     </row>
-    <row r="379" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="379" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D379" s="1" t="s">
         <v>1292</v>
       </c>
@@ -12083,7 +12667,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="380" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="380" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D380" s="1" t="s">
         <v>1296</v>
       </c>
@@ -12097,7 +12681,7 @@
         <v>1299</v>
       </c>
     </row>
-    <row r="381" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="381" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D381" s="1" t="s">
         <v>1301</v>
       </c>
@@ -12111,7 +12695,7 @@
         <v>1304</v>
       </c>
     </row>
-    <row r="382" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="382" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D382" s="1" t="s">
         <v>1305</v>
       </c>
@@ -12119,7 +12703,7 @@
         <v>1306</v>
       </c>
     </row>
-    <row r="383" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="383" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D383" s="1" t="s">
         <v>1308</v>
       </c>
@@ -12133,7 +12717,7 @@
         <v>1310</v>
       </c>
     </row>
-    <row r="384" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="384" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D384" s="1" t="s">
         <v>1311</v>
       </c>
@@ -12147,7 +12731,7 @@
         <v>1314</v>
       </c>
     </row>
-    <row r="385" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="385" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D385" s="1" t="s">
         <v>1315</v>
       </c>
@@ -12161,7 +12745,7 @@
         <v>1318</v>
       </c>
     </row>
-    <row r="386" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="386" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D386" s="1" t="s">
         <v>1319</v>
       </c>
@@ -12175,7 +12759,7 @@
         <v>1321</v>
       </c>
     </row>
-    <row r="387" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="387" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D387" s="1" t="s">
         <v>1322</v>
       </c>
@@ -12189,7 +12773,7 @@
         <v>1325</v>
       </c>
     </row>
-    <row r="388" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="388" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D388" s="1" t="s">
         <v>1326</v>
       </c>
@@ -12203,7 +12787,7 @@
         <v>1329</v>
       </c>
     </row>
-    <row r="389" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="389" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D389" s="1" t="s">
         <v>1330</v>
       </c>
@@ -12217,7 +12801,7 @@
         <v>1333</v>
       </c>
     </row>
-    <row r="390" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="390" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D390" s="1" t="s">
         <v>1335</v>
       </c>
@@ -12231,7 +12815,7 @@
         <v>1338</v>
       </c>
     </row>
-    <row r="391" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="391" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D391" s="1" t="s">
         <v>1339</v>
       </c>
@@ -12245,7 +12829,7 @@
         <v>1342</v>
       </c>
     </row>
-    <row r="392" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="392" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D392" s="1" t="s">
         <v>1378</v>
       </c>
@@ -12256,7 +12840,7 @@
         <v>1383</v>
       </c>
     </row>
-    <row r="393" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="393" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D393" s="1" t="s">
         <v>1377</v>
       </c>
@@ -12270,7 +12854,7 @@
         <v>1382</v>
       </c>
     </row>
-    <row r="394" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="394" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D394" s="1" t="s">
         <v>1343</v>
       </c>
@@ -12284,12 +12868,12 @@
         <v>1346</v>
       </c>
     </row>
-    <row r="395" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="395" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="Q395" s="1" t="s">
         <v>1347</v>
       </c>
     </row>
-    <row r="396" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="396" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D396" s="1" t="s">
         <v>1348</v>
       </c>
@@ -12303,7 +12887,7 @@
         <v>1351</v>
       </c>
     </row>
-    <row r="397" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="397" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D397" s="1" t="s">
         <v>1352</v>
       </c>
@@ -12317,7 +12901,7 @@
         <v>1355</v>
       </c>
     </row>
-    <row r="398" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="398" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D398" s="1" t="s">
         <v>1356</v>
       </c>
@@ -12331,7 +12915,7 @@
         <v>1359</v>
       </c>
     </row>
-    <row r="399" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="399" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D399" s="1" t="s">
         <v>1356</v>
       </c>
@@ -12345,7 +12929,7 @@
         <v>1362</v>
       </c>
     </row>
-    <row r="400" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="400" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D400" s="1" t="s">
         <v>123</v>
       </c>
@@ -12359,7 +12943,7 @@
         <v>1364</v>
       </c>
     </row>
-    <row r="401" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="401" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D401" s="1" t="s">
         <v>1365</v>
       </c>
@@ -12373,7 +12957,7 @@
         <v>1368</v>
       </c>
     </row>
-    <row r="402" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="402" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D402" s="1" t="s">
         <v>1369</v>
       </c>
@@ -12387,7 +12971,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="403" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="403" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D403" s="1" t="s">
         <v>1384</v>
       </c>
@@ -12401,7 +12985,7 @@
         <v>1387</v>
       </c>
     </row>
-    <row r="404" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="404" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D404" s="1" t="s">
         <v>1373</v>
       </c>
@@ -12415,7 +12999,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="405" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="405" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D405" s="1" t="s">
         <v>1388</v>
       </c>
@@ -12429,7 +13013,7 @@
         <v>1390</v>
       </c>
     </row>
-    <row r="406" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="406" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D406" s="1" t="s">
         <v>1391</v>
       </c>
@@ -12443,7 +13027,7 @@
         <v>1394</v>
       </c>
     </row>
-    <row r="407" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="407" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D407" s="1" t="s">
         <v>1395</v>
       </c>
@@ -12457,7 +13041,7 @@
         <v>1398</v>
       </c>
     </row>
-    <row r="408" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="408" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D408" s="1" t="s">
         <v>1399</v>
       </c>
@@ -12471,7 +13055,7 @@
         <v>1402</v>
       </c>
     </row>
-    <row r="409" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="409" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D409" s="1" t="s">
         <v>1403</v>
       </c>
@@ -12485,7 +13069,7 @@
         <v>1406</v>
       </c>
     </row>
-    <row r="410" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="410" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D410" s="1" t="s">
         <v>1429</v>
       </c>
@@ -12496,7 +13080,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="411" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="411" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D411" s="1" t="s">
         <v>1407</v>
       </c>
@@ -12510,7 +13094,7 @@
         <v>1410</v>
       </c>
     </row>
-    <row r="412" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="412" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D412" s="1" t="s">
         <v>1411</v>
       </c>
@@ -12524,7 +13108,7 @@
         <v>1414</v>
       </c>
     </row>
-    <row r="413" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="413" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D413" s="1" t="s">
         <v>1415</v>
       </c>
@@ -12538,7 +13122,7 @@
         <v>1418</v>
       </c>
     </row>
-    <row r="414" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="414" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D414" s="1" t="s">
         <v>1419</v>
       </c>
@@ -12552,7 +13136,7 @@
         <v>1422</v>
       </c>
     </row>
-    <row r="415" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="415" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D415" s="1" t="s">
         <v>1423</v>
       </c>
@@ -12560,7 +13144,7 @@
         <v>1424</v>
       </c>
     </row>
-    <row r="416" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="416" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D416" s="1" t="s">
         <v>1425</v>
       </c>
@@ -12574,7 +13158,7 @@
         <v>1428</v>
       </c>
     </row>
-    <row r="417" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="417" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D417" s="1" t="s">
         <v>1431</v>
       </c>
@@ -12588,7 +13172,7 @@
         <v>1434</v>
       </c>
     </row>
-    <row r="418" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="418" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D418" s="1" t="s">
         <v>1435</v>
       </c>
@@ -12602,7 +13186,7 @@
         <v>1438</v>
       </c>
     </row>
-    <row r="419" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="419" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D419" s="1" t="s">
         <v>1439</v>
       </c>
@@ -12616,7 +13200,7 @@
         <v>1442</v>
       </c>
     </row>
-    <row r="420" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="420" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D420" s="1" t="s">
         <v>477</v>
       </c>
@@ -12630,7 +13214,7 @@
         <v>1444</v>
       </c>
     </row>
-    <row r="421" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="421" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D421" s="1" t="s">
         <v>1445</v>
       </c>
@@ -12644,7 +13228,7 @@
         <v>1448</v>
       </c>
     </row>
-    <row r="422" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="422" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D422" s="1" t="s">
         <v>1449</v>
       </c>
@@ -12658,7 +13242,7 @@
         <v>1455</v>
       </c>
     </row>
-    <row r="423" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="423" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D423" s="1" t="s">
         <v>1452</v>
       </c>
@@ -12672,7 +13256,7 @@
         <v>1456</v>
       </c>
     </row>
-    <row r="424" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="424" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D424" s="1" t="s">
         <v>1457</v>
       </c>
@@ -12686,7 +13270,7 @@
         <v>1460</v>
       </c>
     </row>
-    <row r="425" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="425" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D425" s="1" t="s">
         <v>1461</v>
       </c>
@@ -12700,7 +13284,7 @@
         <v>1464</v>
       </c>
     </row>
-    <row r="426" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="426" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D426" s="1" t="s">
         <v>1465</v>
       </c>
@@ -12714,7 +13298,7 @@
         <v>1468</v>
       </c>
     </row>
-    <row r="427" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="427" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D427" s="1" t="s">
         <v>1469</v>
       </c>
@@ -12728,7 +13312,7 @@
         <v>1472</v>
       </c>
     </row>
-    <row r="428" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="428" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D428" s="1" t="s">
         <v>1473</v>
       </c>
@@ -12742,7 +13326,7 @@
         <v>1476</v>
       </c>
     </row>
-    <row r="429" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="429" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D429" s="1" t="s">
         <v>1477</v>
       </c>
@@ -12756,7 +13340,7 @@
         <v>1480</v>
       </c>
     </row>
-    <row r="430" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="430" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D430" s="1" t="s">
         <v>1481</v>
       </c>
@@ -12770,7 +13354,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="431" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="431" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D431" s="1" t="s">
         <v>1485</v>
       </c>
@@ -12784,7 +13368,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="432" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="432" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D432" s="1" t="s">
         <v>1489</v>
       </c>
@@ -12798,7 +13382,7 @@
         <v>1492</v>
       </c>
     </row>
-    <row r="433" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="433" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D433" s="1" t="s">
         <v>1493</v>
       </c>
@@ -12812,7 +13396,7 @@
         <v>1494</v>
       </c>
     </row>
-    <row r="434" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="434" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D434" s="1" t="s">
         <v>1496</v>
       </c>
@@ -12826,7 +13410,7 @@
         <v>1499</v>
       </c>
     </row>
-    <row r="435" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="435" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D435" s="1" t="s">
         <v>1500</v>
       </c>
@@ -12840,7 +13424,7 @@
         <v>1503</v>
       </c>
     </row>
-    <row r="436" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="436" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D436" s="1" t="s">
         <v>1504</v>
       </c>
@@ -12854,7 +13438,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="437" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="437" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D437" s="1" t="s">
         <v>1508</v>
       </c>
@@ -12868,7 +13452,7 @@
         <v>1511</v>
       </c>
     </row>
-    <row r="438" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="438" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D438" s="1" t="s">
         <v>1512</v>
       </c>
@@ -12882,7 +13466,7 @@
         <v>1515</v>
       </c>
     </row>
-    <row r="439" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="439" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D439" s="1" t="s">
         <v>1516</v>
       </c>
@@ -12896,7 +13480,7 @@
         <v>1519</v>
       </c>
     </row>
-    <row r="440" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="440" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D440" s="1" t="s">
         <v>1520</v>
       </c>
@@ -12910,7 +13494,7 @@
         <v>1522</v>
       </c>
     </row>
-    <row r="441" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="441" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D441" s="1" t="s">
         <v>1524</v>
       </c>
@@ -12918,7 +13502,7 @@
         <v>1529</v>
       </c>
     </row>
-    <row r="442" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="442" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D442" s="1" t="s">
         <v>1525</v>
       </c>
@@ -12932,7 +13516,7 @@
         <v>1528</v>
       </c>
     </row>
-    <row r="443" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="443" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D443" s="1" t="s">
         <v>1530</v>
       </c>
@@ -12946,7 +13530,7 @@
         <v>1533</v>
       </c>
     </row>
-    <row r="444" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="444" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D444" s="1" t="s">
         <v>1534</v>
       </c>
@@ -12960,7 +13544,7 @@
         <v>1537</v>
       </c>
     </row>
-    <row r="445" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="445" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D445" s="1" t="s">
         <v>1538</v>
       </c>
@@ -12974,7 +13558,7 @@
         <v>1541</v>
       </c>
     </row>
-    <row r="446" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="446" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D446" s="1" t="s">
         <v>1542</v>
       </c>
@@ -12988,7 +13572,7 @@
         <v>1545</v>
       </c>
     </row>
-    <row r="447" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="447" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D447" s="1" t="s">
         <v>1546</v>
       </c>
@@ -13002,7 +13586,7 @@
         <v>1548</v>
       </c>
     </row>
-    <row r="448" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="448" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D448" s="1" t="s">
         <v>1550</v>
       </c>
@@ -13016,7 +13600,7 @@
         <v>1552</v>
       </c>
     </row>
-    <row r="449" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="449" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D449" s="1" t="s">
         <v>1553</v>
       </c>
@@ -13030,7 +13614,7 @@
         <v>1555</v>
       </c>
     </row>
-    <row r="450" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="450" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D450" s="1" t="s">
         <v>1680</v>
       </c>
@@ -13044,7 +13628,7 @@
         <v>1683</v>
       </c>
     </row>
-    <row r="451" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="451" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D451" s="1" t="s">
         <v>1556</v>
       </c>
@@ -13058,7 +13642,7 @@
         <v>1559</v>
       </c>
     </row>
-    <row r="452" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="452" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D452" s="1" t="s">
         <v>1560</v>
       </c>
@@ -13072,7 +13656,7 @@
         <v>1563</v>
       </c>
     </row>
-    <row r="453" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="453" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D453" s="1" t="s">
         <v>1565</v>
       </c>
@@ -13086,7 +13670,7 @@
         <v>1568</v>
       </c>
     </row>
-    <row r="454" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="454" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D454" s="1" t="s">
         <v>1569</v>
       </c>
@@ -13100,7 +13684,7 @@
         <v>1572</v>
       </c>
     </row>
-    <row r="455" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="455" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D455" s="1" t="s">
         <v>1573</v>
       </c>
@@ -13114,7 +13698,7 @@
         <v>1575</v>
       </c>
     </row>
-    <row r="456" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="456" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D456" s="1" t="s">
         <v>1576</v>
       </c>
@@ -13128,7 +13712,7 @@
         <v>1579</v>
       </c>
     </row>
-    <row r="457" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="457" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D457" s="1" t="s">
         <v>1580</v>
       </c>
@@ -13142,7 +13726,7 @@
         <v>1583</v>
       </c>
     </row>
-    <row r="458" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="458" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D458" s="1" t="s">
         <v>1584</v>
       </c>
@@ -13156,7 +13740,7 @@
         <v>1587</v>
       </c>
     </row>
-    <row r="459" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="459" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D459" s="1" t="s">
         <v>1588</v>
       </c>
@@ -13170,7 +13754,7 @@
         <v>1590</v>
       </c>
     </row>
-    <row r="460" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="460" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D460" s="1" t="s">
         <v>1591</v>
       </c>
@@ -13184,7 +13768,7 @@
         <v>1593</v>
       </c>
     </row>
-    <row r="461" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="461" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D461" s="1" t="s">
         <v>1594</v>
       </c>
@@ -13198,12 +13782,12 @@
         <v>1596</v>
       </c>
     </row>
-    <row r="464" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="464" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A464" s="1" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="465" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="465" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D465" s="1" t="s">
         <v>1598</v>
       </c>
@@ -13217,7 +13801,7 @@
         <v>1601</v>
       </c>
     </row>
-    <row r="466" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="466" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D466" s="1" t="s">
         <v>1602</v>
       </c>
@@ -13231,7 +13815,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="467" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="467" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D467" s="1" t="s">
         <v>1606</v>
       </c>
@@ -13245,7 +13829,7 @@
         <v>1609</v>
       </c>
     </row>
-    <row r="468" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="468" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D468" s="1" t="s">
         <v>1629</v>
       </c>
@@ -13259,7 +13843,7 @@
         <v>1632</v>
       </c>
     </row>
-    <row r="469" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="469" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D469" s="1" t="s">
         <v>489</v>
       </c>
@@ -13273,7 +13857,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="470" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="470" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D470" s="1" t="s">
         <v>1612</v>
       </c>
@@ -13287,7 +13871,7 @@
         <v>1615</v>
       </c>
     </row>
-    <row r="471" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="471" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D471" s="1" t="s">
         <v>1616</v>
       </c>
@@ -13301,7 +13885,7 @@
         <v>1619</v>
       </c>
     </row>
-    <row r="472" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="472" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D472" s="1" t="s">
         <v>1620</v>
       </c>
@@ -13315,7 +13899,7 @@
         <v>1622</v>
       </c>
     </row>
-    <row r="473" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="473" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D473" s="1" t="s">
         <v>482</v>
       </c>
@@ -13329,7 +13913,7 @@
         <v>1624</v>
       </c>
     </row>
-    <row r="474" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="474" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D474" s="1" t="s">
         <v>1625</v>
       </c>
@@ -13343,7 +13927,7 @@
         <v>1628</v>
       </c>
     </row>
-    <row r="475" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="475" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D475" s="1" t="s">
         <v>1633</v>
       </c>
@@ -13357,7 +13941,7 @@
         <v>1638</v>
       </c>
     </row>
-    <row r="476" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="476" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D476" s="1" t="s">
         <v>1635</v>
       </c>
@@ -13371,7 +13955,7 @@
         <v>1640</v>
       </c>
     </row>
-    <row r="477" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="477" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D477" s="1" t="s">
         <v>1391</v>
       </c>
@@ -13385,7 +13969,7 @@
         <v>1394</v>
       </c>
     </row>
-    <row r="478" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="478" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D478" s="1" t="s">
         <v>1641</v>
       </c>
@@ -13399,7 +13983,7 @@
         <v>1644</v>
       </c>
     </row>
-    <row r="479" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="479" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D479" s="1" t="s">
         <v>1645</v>
       </c>
@@ -13413,7 +13997,7 @@
         <v>1648</v>
       </c>
     </row>
-    <row r="480" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="480" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D480" s="1" t="s">
         <v>1649</v>
       </c>
@@ -13427,7 +14011,7 @@
         <v>1652</v>
       </c>
     </row>
-    <row r="481" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="481" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D481" s="1" t="s">
         <v>1665</v>
       </c>
@@ -13441,7 +14025,7 @@
         <v>1668</v>
       </c>
     </row>
-    <row r="482" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="482" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D482" s="1" t="s">
         <v>1653</v>
       </c>
@@ -13455,7 +14039,7 @@
         <v>1656</v>
       </c>
     </row>
-    <row r="483" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="483" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D483" s="1" t="s">
         <v>1657</v>
       </c>
@@ -13469,7 +14053,7 @@
         <v>1660</v>
       </c>
     </row>
-    <row r="484" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="484" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D484" s="1" t="s">
         <v>1661</v>
       </c>
@@ -13483,7 +14067,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="485" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="485" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D485" s="1" t="s">
         <v>1669</v>
       </c>
@@ -13494,7 +14078,7 @@
         <v>1671</v>
       </c>
     </row>
-    <row r="486" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="486" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D486" s="1" t="s">
         <v>1672</v>
       </c>
@@ -13508,7 +14092,7 @@
         <v>1675</v>
       </c>
     </row>
-    <row r="487" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="487" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D487" s="1" t="s">
         <v>1676</v>
       </c>
@@ -13522,7 +14106,7 @@
         <v>1679</v>
       </c>
     </row>
-    <row r="488" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="488" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D488" s="1" t="s">
         <v>1684</v>
       </c>
@@ -13536,7 +14120,7 @@
         <v>1687</v>
       </c>
     </row>
-    <row r="489" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="489" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D489" s="1" t="s">
         <v>1688</v>
       </c>
@@ -13550,7 +14134,7 @@
         <v>1691</v>
       </c>
     </row>
-    <row r="490" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="490" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D490" s="1" t="s">
         <v>1692</v>
       </c>
@@ -13564,7 +14148,7 @@
         <v>1695</v>
       </c>
     </row>
-    <row r="491" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="491" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D491" s="1" t="s">
         <v>1700</v>
       </c>
@@ -13578,7 +14162,7 @@
         <v>1703</v>
       </c>
     </row>
-    <row r="492" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="492" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D492" s="1" t="s">
         <v>1696</v>
       </c>
@@ -13592,7 +14176,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="493" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="493" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D493" s="1" t="s">
         <v>1849</v>
       </c>
@@ -13606,7 +14190,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="494" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="494" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D494" s="1" t="s">
         <v>1704</v>
       </c>
@@ -13620,7 +14204,7 @@
         <v>1707</v>
       </c>
     </row>
-    <row r="495" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="495" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D495" s="1" t="s">
         <v>1708</v>
       </c>
@@ -13634,7 +14218,7 @@
         <v>1711</v>
       </c>
     </row>
-    <row r="496" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="496" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D496" s="1" t="s">
         <v>1712</v>
       </c>
@@ -13648,7 +14232,7 @@
         <v>1715</v>
       </c>
     </row>
-    <row r="497" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="497" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D497" s="1" t="s">
         <v>1716</v>
       </c>
@@ -13662,7 +14246,7 @@
         <v>1719</v>
       </c>
     </row>
-    <row r="498" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="498" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D498" s="1" t="s">
         <v>1720</v>
       </c>
@@ -13676,7 +14260,7 @@
         <v>1723</v>
       </c>
     </row>
-    <row r="499" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="499" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D499" s="1" t="s">
         <v>1724</v>
       </c>
@@ -13690,7 +14274,7 @@
         <v>1727</v>
       </c>
     </row>
-    <row r="500" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="500" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D500" s="1" t="s">
         <v>1728</v>
       </c>
@@ -13704,7 +14288,7 @@
         <v>1731</v>
       </c>
     </row>
-    <row r="501" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="501" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D501" s="1" t="s">
         <v>1732</v>
       </c>
@@ -13718,7 +14302,7 @@
         <v>1735</v>
       </c>
     </row>
-    <row r="502" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="502" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D502" s="1" t="s">
         <v>1845</v>
       </c>
@@ -13732,7 +14316,7 @@
         <v>1848</v>
       </c>
     </row>
-    <row r="503" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="503" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D503" s="1" t="s">
         <v>1736</v>
       </c>
@@ -13746,7 +14330,7 @@
         <v>1739</v>
       </c>
     </row>
-    <row r="504" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="504" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D504" s="1" t="s">
         <v>1740</v>
       </c>
@@ -13760,7 +14344,7 @@
         <v>1743</v>
       </c>
     </row>
-    <row r="505" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="505" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D505" s="1" t="s">
         <v>1744</v>
       </c>
@@ -13774,7 +14358,7 @@
         <v>1747</v>
       </c>
     </row>
-    <row r="506" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="506" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D506" s="1" t="s">
         <v>1748</v>
       </c>
@@ -13788,7 +14372,7 @@
         <v>1750</v>
       </c>
     </row>
-    <row r="507" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="507" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D507" s="1" t="s">
         <v>1751</v>
       </c>
@@ -13802,7 +14386,7 @@
         <v>1753</v>
       </c>
     </row>
-    <row r="508" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="508" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D508" s="1" t="s">
         <v>1754</v>
       </c>
@@ -13816,7 +14400,7 @@
         <v>1757</v>
       </c>
     </row>
-    <row r="509" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="509" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D509" s="1" t="s">
         <v>1758</v>
       </c>
@@ -13830,7 +14414,7 @@
         <v>1761</v>
       </c>
     </row>
-    <row r="510" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="510" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D510" s="1" t="s">
         <v>1762</v>
       </c>
@@ -13844,7 +14428,7 @@
         <v>1765</v>
       </c>
     </row>
-    <row r="511" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="511" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D511" s="1" t="s">
         <v>1766</v>
       </c>
@@ -13858,7 +14442,7 @@
         <v>1769</v>
       </c>
     </row>
-    <row r="512" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="512" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D512" s="1" t="s">
         <v>1770</v>
       </c>
@@ -13872,7 +14456,7 @@
         <v>1773</v>
       </c>
     </row>
-    <row r="513" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="513" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D513" s="1" t="s">
         <v>1774</v>
       </c>
@@ -13886,7 +14470,7 @@
         <v>1777</v>
       </c>
     </row>
-    <row r="514" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="514" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D514" s="1" t="s">
         <v>1778</v>
       </c>
@@ -13900,7 +14484,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="515" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="515" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D515" s="1" t="s">
         <v>1782</v>
       </c>
@@ -13914,7 +14498,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="516" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="516" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D516" s="1" t="s">
         <v>1786</v>
       </c>
@@ -13928,7 +14512,7 @@
         <v>1789</v>
       </c>
     </row>
-    <row r="517" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="517" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D517" s="1" t="s">
         <v>1790</v>
       </c>
@@ -13942,7 +14526,7 @@
         <v>1793</v>
       </c>
     </row>
-    <row r="518" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="518" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D518" s="1" t="s">
         <v>1794</v>
       </c>
@@ -13956,7 +14540,7 @@
         <v>1797</v>
       </c>
     </row>
-    <row r="519" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="519" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D519" s="1" t="s">
         <v>1798</v>
       </c>
@@ -13970,7 +14554,7 @@
         <v>1801</v>
       </c>
     </row>
-    <row r="520" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="520" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D520" s="1" t="s">
         <v>1802</v>
       </c>
@@ -13984,7 +14568,7 @@
         <v>1805</v>
       </c>
     </row>
-    <row r="521" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="521" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D521" s="1" t="s">
         <v>1806</v>
       </c>
@@ -13998,7 +14582,7 @@
         <v>1808</v>
       </c>
     </row>
-    <row r="522" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="522" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D522" s="1" t="s">
         <v>1809</v>
       </c>
@@ -14012,7 +14596,7 @@
         <v>1812</v>
       </c>
     </row>
-    <row r="523" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="523" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D523" s="1" t="s">
         <v>1813</v>
       </c>
@@ -14026,7 +14610,7 @@
         <v>1816</v>
       </c>
     </row>
-    <row r="524" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="524" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D524" s="1" t="s">
         <v>1817</v>
       </c>
@@ -14040,7 +14624,7 @@
         <v>1820</v>
       </c>
     </row>
-    <row r="525" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="525" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D525" s="1" t="s">
         <v>1821</v>
       </c>
@@ -14054,7 +14638,7 @@
         <v>1824</v>
       </c>
     </row>
-    <row r="526" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="526" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D526" s="1" t="s">
         <v>1825</v>
       </c>
@@ -14068,7 +14652,7 @@
         <v>1828</v>
       </c>
     </row>
-    <row r="527" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="527" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D527" s="1" t="s">
         <v>1829</v>
       </c>
@@ -14082,7 +14666,7 @@
         <v>1832</v>
       </c>
     </row>
-    <row r="528" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="528" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D528" s="1" t="s">
         <v>1833</v>
       </c>
@@ -14096,7 +14680,7 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="529" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="529" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D529" s="1" t="s">
         <v>1837</v>
       </c>
@@ -14110,7 +14694,7 @@
         <v>1840</v>
       </c>
     </row>
-    <row r="530" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="530" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D530" s="1" t="s">
         <v>1841</v>
       </c>
@@ -14124,7 +14708,7 @@
         <v>1844</v>
       </c>
     </row>
-    <row r="531" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="531" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D531" s="1" t="s">
         <v>1853</v>
       </c>
@@ -14138,7 +14722,7 @@
         <v>1856</v>
       </c>
     </row>
-    <row r="532" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="532" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D532" s="1" t="s">
         <v>1857</v>
       </c>
@@ -14152,7 +14736,7 @@
         <v>1860</v>
       </c>
     </row>
-    <row r="533" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="533" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D533" s="1" t="s">
         <v>1861</v>
       </c>
@@ -14166,7 +14750,7 @@
         <v>1864</v>
       </c>
     </row>
-    <row r="534" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="534" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D534" s="1" t="s">
         <v>1127</v>
       </c>
@@ -14180,7 +14764,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="535" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="535" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D535" s="1" t="s">
         <v>1866</v>
       </c>
@@ -14194,7 +14778,7 @@
         <v>1880</v>
       </c>
     </row>
-    <row r="536" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="536" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D536" s="1" t="s">
         <v>1868</v>
       </c>
@@ -14208,7 +14792,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="537" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="537" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D537" s="1" t="s">
         <v>1872</v>
       </c>
@@ -14222,7 +14806,7 @@
         <v>1875</v>
       </c>
     </row>
-    <row r="538" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="538" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D538" s="1" t="s">
         <v>1876</v>
       </c>
@@ -14236,7 +14820,7 @@
         <v>1879</v>
       </c>
     </row>
-    <row r="539" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="539" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D539" s="1" t="s">
         <v>1885</v>
       </c>
@@ -14250,7 +14834,7 @@
         <v>1888</v>
       </c>
     </row>
-    <row r="540" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="540" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D540" s="1" t="s">
         <v>1881</v>
       </c>
@@ -14264,7 +14848,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="541" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="541" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D541" s="1" t="s">
         <v>1889</v>
       </c>
@@ -14278,7 +14862,7 @@
         <v>1891</v>
       </c>
     </row>
-    <row r="542" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="542" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D542" s="1" t="s">
         <v>1892</v>
       </c>
@@ -14292,7 +14876,7 @@
         <v>1894</v>
       </c>
     </row>
-    <row r="543" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="543" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D543" s="1" t="s">
         <v>1895</v>
       </c>
@@ -14306,7 +14890,7 @@
         <v>1898</v>
       </c>
     </row>
-    <row r="544" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="544" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D544" s="1" t="s">
         <v>1899</v>
       </c>
@@ -14320,7 +14904,7 @@
         <v>1902</v>
       </c>
     </row>
-    <row r="545" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="545" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D545" s="1" t="s">
         <v>1903</v>
       </c>
@@ -14334,7 +14918,7 @@
         <v>1906</v>
       </c>
     </row>
-    <row r="546" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="546" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D546" s="1" t="s">
         <v>1907</v>
       </c>
@@ -14348,7 +14932,7 @@
         <v>1910</v>
       </c>
     </row>
-    <row r="547" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="547" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D547" s="1" t="s">
         <v>1911</v>
       </c>
@@ -14362,7 +14946,7 @@
         <v>1914</v>
       </c>
     </row>
-    <row r="548" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="548" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D548" s="1" t="s">
         <v>1915</v>
       </c>
@@ -14376,7 +14960,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="549" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="549" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D549" s="1" t="s">
         <v>1919</v>
       </c>
@@ -14390,7 +14974,7 @@
         <v>1922</v>
       </c>
     </row>
-    <row r="550" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="550" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D550" s="1" t="s">
         <v>1923</v>
       </c>
@@ -14404,7 +14988,7 @@
         <v>1926</v>
       </c>
     </row>
-    <row r="551" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="551" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D551" s="1" t="s">
         <v>1927</v>
       </c>
@@ -14418,7 +15002,7 @@
         <v>1930</v>
       </c>
     </row>
-    <row r="552" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="552" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D552" s="1" t="s">
         <v>1931</v>
       </c>
@@ -14432,7 +15016,7 @@
         <v>1934</v>
       </c>
     </row>
-    <row r="553" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="553" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D553" s="1" t="s">
         <v>1935</v>
       </c>
@@ -14446,7 +15030,7 @@
         <v>1938</v>
       </c>
     </row>
-    <row r="554" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="554" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D554" s="1" t="s">
         <v>1939</v>
       </c>
@@ -14460,7 +15044,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="555" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="555" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D555" s="1" t="s">
         <v>1943</v>
       </c>
@@ -14474,7 +15058,7 @@
         <v>1946</v>
       </c>
     </row>
-    <row r="556" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="556" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D556" s="1" t="s">
         <v>1947</v>
       </c>
@@ -14488,7 +15072,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="557" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="557" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D557" s="1" t="s">
         <v>1951</v>
       </c>
@@ -14502,7 +15086,7 @@
         <v>1954</v>
       </c>
     </row>
-    <row r="558" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="558" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D558" s="1" t="s">
         <v>1955</v>
       </c>
@@ -14516,7 +15100,7 @@
         <v>1958</v>
       </c>
     </row>
-    <row r="559" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="559" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D559" s="1" t="s">
         <v>1959</v>
       </c>
@@ -14530,7 +15114,7 @@
         <v>1962</v>
       </c>
     </row>
-    <row r="560" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="560" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D560" s="1" t="s">
         <v>1963</v>
       </c>
@@ -14544,7 +15128,7 @@
         <v>1966</v>
       </c>
     </row>
-    <row r="561" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="561" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D561" s="1" t="s">
         <v>1967</v>
       </c>
@@ -14558,7 +15142,7 @@
         <v>1970</v>
       </c>
     </row>
-    <row r="562" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="562" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D562" s="1" t="s">
         <v>1975</v>
       </c>
@@ -14572,7 +15156,7 @@
         <v>1978</v>
       </c>
     </row>
-    <row r="563" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="563" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D563" s="1" t="s">
         <v>1971</v>
       </c>
@@ -14586,7 +15170,7 @@
         <v>1974</v>
       </c>
     </row>
-    <row r="564" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="564" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D564" s="1" t="s">
         <v>1979</v>
       </c>
@@ -14600,7 +15184,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="565" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="565" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D565" s="1" t="s">
         <v>1983</v>
       </c>
@@ -14614,7 +15198,7 @@
         <v>1986</v>
       </c>
     </row>
-    <row r="566" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="566" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D566" s="1" t="s">
         <v>1987</v>
       </c>
@@ -14628,7 +15212,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="567" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="567" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D567" s="1" t="s">
         <v>1991</v>
       </c>
@@ -14642,7 +15226,7 @@
         <v>1993</v>
       </c>
     </row>
-    <row r="568" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="568" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D568" s="1" t="s">
         <v>1994</v>
       </c>
@@ -14656,7 +15240,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="569" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="569" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D569" s="1" t="s">
         <v>1998</v>
       </c>
@@ -14670,7 +15254,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="570" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="570" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D570" s="1" t="s">
         <v>2002</v>
       </c>
@@ -14684,7 +15268,7 @@
         <v>2204</v>
       </c>
     </row>
-    <row r="571" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="571" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D571" s="1" t="s">
         <v>2005</v>
       </c>
@@ -14698,7 +15282,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="572" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="572" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D572" s="1" t="s">
         <v>2009</v>
       </c>
@@ -14712,7 +15296,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="573" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="573" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D573" s="1" t="s">
         <v>2012</v>
       </c>
@@ -14726,7 +15310,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="574" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="574" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D574" s="1" t="s">
         <v>2016</v>
       </c>
@@ -14740,7 +15324,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="575" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="575" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D575" s="1" t="s">
         <v>2020</v>
       </c>
@@ -14751,7 +15335,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="576" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="576" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D576" s="1" t="s">
         <v>2023</v>
       </c>
@@ -14762,7 +15346,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="577" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="577" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D577" s="1" t="s">
         <v>2026</v>
       </c>
@@ -14770,7 +15354,7 @@
         <v>2205</v>
       </c>
     </row>
-    <row r="578" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="578" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D578" s="1" t="s">
         <v>2027</v>
       </c>
@@ -14784,7 +15368,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="579" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="579" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D579" s="1" t="s">
         <v>2031</v>
       </c>
@@ -14798,7 +15382,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="580" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="580" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D580" s="1" t="s">
         <v>2031</v>
       </c>
@@ -14809,7 +15393,7 @@
         <v>2041</v>
       </c>
     </row>
-    <row r="581" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="581" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D581" s="1" t="s">
         <v>2034</v>
       </c>
@@ -14820,7 +15404,7 @@
         <v>2036</v>
       </c>
     </row>
-    <row r="582" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="582" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D582" s="1" t="s">
         <v>2037</v>
       </c>
@@ -14834,7 +15418,7 @@
         <v>2039</v>
       </c>
     </row>
-    <row r="583" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="583" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D583" s="1" t="s">
         <v>2042</v>
       </c>
@@ -14848,7 +15432,7 @@
         <v>2045</v>
       </c>
     </row>
-    <row r="584" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="584" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D584" s="1" t="s">
         <v>2046</v>
       </c>
@@ -14862,7 +15446,7 @@
         <v>2049</v>
       </c>
     </row>
-    <row r="585" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="585" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D585" s="1" t="s">
         <v>2051</v>
       </c>
@@ -14873,7 +15457,7 @@
         <v>2053</v>
       </c>
     </row>
-    <row r="586" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="586" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D586" s="1" t="s">
         <v>2094</v>
       </c>
@@ -14887,7 +15471,7 @@
         <v>2097</v>
       </c>
     </row>
-    <row r="587" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="587" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D587" s="1" t="s">
         <v>2054</v>
       </c>
@@ -14901,7 +15485,7 @@
         <v>2057</v>
       </c>
     </row>
-    <row r="588" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="588" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D588" s="1" t="s">
         <v>2058</v>
       </c>
@@ -14915,7 +15499,7 @@
         <v>2061</v>
       </c>
     </row>
-    <row r="589" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="589" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D589" s="1" t="s">
         <v>2062</v>
       </c>
@@ -14929,7 +15513,7 @@
         <v>2065</v>
       </c>
     </row>
-    <row r="590" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="590" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D590" s="1" t="s">
         <v>2066</v>
       </c>
@@ -14943,7 +15527,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="591" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="591" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D591" s="1" t="s">
         <v>2070</v>
       </c>
@@ -14957,7 +15541,7 @@
         <v>2098</v>
       </c>
     </row>
-    <row r="592" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="592" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D592" s="1" t="s">
         <v>2074</v>
       </c>
@@ -14971,7 +15555,7 @@
         <v>2077</v>
       </c>
     </row>
-    <row r="593" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="593" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D593" s="1" t="s">
         <v>2078</v>
       </c>
@@ -14985,7 +15569,7 @@
         <v>2081</v>
       </c>
     </row>
-    <row r="594" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="594" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D594" s="1" t="s">
         <v>2082</v>
       </c>
@@ -14999,7 +15583,7 @@
         <v>2085</v>
       </c>
     </row>
-    <row r="595" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="595" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D595" s="1" t="s">
         <v>2086</v>
       </c>
@@ -15013,7 +15597,7 @@
         <v>2089</v>
       </c>
     </row>
-    <row r="596" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="596" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D596" s="1" t="s">
         <v>2090</v>
       </c>
@@ -15027,7 +15611,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="597" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="597" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D597" s="1" t="s">
         <v>2100</v>
       </c>
@@ -15041,7 +15625,7 @@
         <v>2102</v>
       </c>
     </row>
-    <row r="598" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="598" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D598" s="1" t="s">
         <v>2103</v>
       </c>
@@ -15055,7 +15639,7 @@
         <v>2106</v>
       </c>
     </row>
-    <row r="599" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="599" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D599" s="1" t="s">
         <v>2107</v>
       </c>
@@ -15069,7 +15653,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="600" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="600" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D600" s="1" t="s">
         <v>2110</v>
       </c>
@@ -15083,7 +15667,7 @@
         <v>2113</v>
       </c>
     </row>
-    <row r="601" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="601" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D601" s="1" t="s">
         <v>2114</v>
       </c>
@@ -15097,7 +15681,7 @@
         <v>2117</v>
       </c>
     </row>
-    <row r="602" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="602" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D602" s="1" t="s">
         <v>2118</v>
       </c>
@@ -15111,7 +15695,7 @@
         <v>2121</v>
       </c>
     </row>
-    <row r="603" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="603" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D603" s="1" t="s">
         <v>2122</v>
       </c>
@@ -15125,7 +15709,7 @@
         <v>2125</v>
       </c>
     </row>
-    <row r="604" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="604" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D604" s="1" t="s">
         <v>2126</v>
       </c>
@@ -15139,7 +15723,7 @@
         <v>2129</v>
       </c>
     </row>
-    <row r="605" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="605" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D605" s="1" t="s">
         <v>2130</v>
       </c>
@@ -15153,7 +15737,7 @@
         <v>2133</v>
       </c>
     </row>
-    <row r="606" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="606" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D606" s="1" t="s">
         <v>2134</v>
       </c>
@@ -15161,7 +15745,7 @@
         <v>2135</v>
       </c>
     </row>
-    <row r="607" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="607" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D607" s="1" t="s">
         <v>2136</v>
       </c>
@@ -15175,7 +15759,7 @@
         <v>2138</v>
       </c>
     </row>
-    <row r="608" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="608" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D608" s="1" t="s">
         <v>2139</v>
       </c>
@@ -15189,7 +15773,7 @@
         <v>2142</v>
       </c>
     </row>
-    <row r="609" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="609" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D609" s="1" t="s">
         <v>2143</v>
       </c>
@@ -15203,7 +15787,7 @@
         <v>2146</v>
       </c>
     </row>
-    <row r="610" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="610" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D610" s="1" t="s">
         <v>2147</v>
       </c>
@@ -15217,7 +15801,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="611" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="611" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D611" s="1" t="s">
         <v>2151</v>
       </c>
@@ -15231,7 +15815,7 @@
         <v>2154</v>
       </c>
     </row>
-    <row r="612" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="612" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D612" s="1" t="s">
         <v>2155</v>
       </c>
@@ -15245,7 +15829,7 @@
         <v>2158</v>
       </c>
     </row>
-    <row r="613" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="613" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D613" s="1" t="s">
         <v>2159</v>
       </c>
@@ -15259,7 +15843,7 @@
         <v>2162</v>
       </c>
     </row>
-    <row r="614" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="614" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D614" s="1" t="s">
         <v>2163</v>
       </c>
@@ -15273,7 +15857,7 @@
         <v>2166</v>
       </c>
     </row>
-    <row r="615" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="615" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D615" s="1" t="s">
         <v>2167</v>
       </c>
@@ -15287,7 +15871,7 @@
         <v>2169</v>
       </c>
     </row>
-    <row r="616" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="616" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D616" s="1" t="s">
         <v>2171</v>
       </c>
@@ -15301,7 +15885,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="617" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="617" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D617" s="1" t="s">
         <v>2174</v>
       </c>
@@ -15315,7 +15899,7 @@
         <v>2177</v>
       </c>
     </row>
-    <row r="618" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="618" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D618" s="1" t="s">
         <v>2178</v>
       </c>
@@ -15329,7 +15913,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="619" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="619" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D619" s="1" t="s">
         <v>2182</v>
       </c>
@@ -15343,7 +15927,7 @@
         <v>2185</v>
       </c>
     </row>
-    <row r="620" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="620" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D620" s="1" t="s">
         <v>2188</v>
       </c>
@@ -15357,7 +15941,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="621" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="621" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D621" s="1" t="s">
         <v>2186</v>
       </c>
@@ -15365,7 +15949,7 @@
         <v>2187</v>
       </c>
     </row>
-    <row r="622" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="622" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D622" s="1" t="s">
         <v>2192</v>
       </c>
@@ -15379,7 +15963,7 @@
         <v>2195</v>
       </c>
     </row>
-    <row r="623" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="623" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D623" s="1" t="s">
         <v>2200</v>
       </c>
@@ -15393,7 +15977,7 @@
         <v>2203</v>
       </c>
     </row>
-    <row r="624" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="624" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D624" s="1" t="s">
         <v>2196</v>
       </c>
@@ -15407,7 +15991,7 @@
         <v>2199</v>
       </c>
     </row>
-    <row r="625" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="625" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D625" s="1" t="s">
         <v>2206</v>
       </c>
@@ -15421,7 +16005,7 @@
         <v>2209</v>
       </c>
     </row>
-    <row r="626" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="626" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D626" s="1" t="s">
         <v>2210</v>
       </c>
@@ -15435,7 +16019,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="627" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="627" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D627" s="1" t="s">
         <v>2214</v>
       </c>
@@ -15449,7 +16033,7 @@
         <v>2217</v>
       </c>
     </row>
-    <row r="628" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="628" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D628" s="1" t="s">
         <v>2218</v>
       </c>
@@ -15463,7 +16047,7 @@
         <v>2221</v>
       </c>
     </row>
-    <row r="629" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="629" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D629" s="1" t="s">
         <v>2222</v>
       </c>
@@ -15477,7 +16061,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="630" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="630" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D630" s="1" t="s">
         <v>2226</v>
       </c>
@@ -15491,7 +16075,7 @@
         <v>2236</v>
       </c>
     </row>
-    <row r="631" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="631" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D631" s="1" t="s">
         <v>2229</v>
       </c>
@@ -15505,7 +16089,7 @@
         <v>2232</v>
       </c>
     </row>
-    <row r="632" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="632" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D632" s="1" t="s">
         <v>2233</v>
       </c>
@@ -15516,7 +16100,7 @@
         <v>2235</v>
       </c>
     </row>
-    <row r="633" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="633" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D633" s="1" t="s">
         <v>2237</v>
       </c>
@@ -15530,7 +16114,7 @@
         <v>2240</v>
       </c>
     </row>
-    <row r="634" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="634" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D634" s="1" t="s">
         <v>2241</v>
       </c>
@@ -15538,7 +16122,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="635" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="635" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D635" s="1" t="s">
         <v>2242</v>
       </c>
@@ -15546,7 +16130,7 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="636" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="636" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D636" s="1" t="s">
         <v>2245</v>
       </c>
@@ -15560,7 +16144,7 @@
         <v>2248</v>
       </c>
     </row>
-    <row r="637" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="637" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D637" s="1" t="s">
         <v>2249</v>
       </c>
@@ -15574,7 +16158,7 @@
         <v>2252</v>
       </c>
     </row>
-    <row r="638" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="638" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D638" s="1" t="s">
         <v>2253</v>
       </c>
@@ -15588,7 +16172,7 @@
         <v>2260</v>
       </c>
     </row>
-    <row r="639" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="639" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D639" s="1" t="s">
         <v>2261</v>
       </c>
@@ -15602,7 +16186,7 @@
         <v>2260</v>
       </c>
     </row>
-    <row r="640" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="640" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D640" s="1" t="s">
         <v>2256</v>
       </c>
@@ -15616,7 +16200,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="641" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="641" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D641" s="1" t="s">
         <v>2264</v>
       </c>
@@ -15630,7 +16214,7 @@
         <v>2267</v>
       </c>
     </row>
-    <row r="642" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="642" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D642" s="1" t="s">
         <v>2268</v>
       </c>
@@ -15638,7 +16222,7 @@
         <v>2267</v>
       </c>
     </row>
-    <row r="643" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="643" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D643" s="1" t="s">
         <v>2269</v>
       </c>
@@ -15652,7 +16236,7 @@
         <v>2272</v>
       </c>
     </row>
-    <row r="644" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="644" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D644" s="1" t="s">
         <v>2273</v>
       </c>
@@ -15666,7 +16250,7 @@
         <v>2276</v>
       </c>
     </row>
-    <row r="645" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="645" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D645" s="1" t="s">
         <v>2277</v>
       </c>
@@ -15680,7 +16264,7 @@
         <v>2279</v>
       </c>
     </row>
-    <row r="646" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="646" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D646" s="2" t="s">
         <v>2280</v>
       </c>
@@ -15688,7 +16272,7 @@
         <v>2281</v>
       </c>
     </row>
-    <row r="647" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="647" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D647" s="1" t="s">
         <v>2282</v>
       </c>
@@ -15702,7 +16286,7 @@
         <v>2285</v>
       </c>
     </row>
-    <row r="648" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="648" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D648" s="1" t="s">
         <v>2286</v>
       </c>
@@ -15716,7 +16300,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="649" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="649" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D649" s="1" t="s">
         <v>2289</v>
       </c>
@@ -15730,7 +16314,7 @@
         <v>2292</v>
       </c>
     </row>
-    <row r="650" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="650" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D650" s="1" t="s">
         <v>2293</v>
       </c>
@@ -15744,7 +16328,7 @@
         <v>2296</v>
       </c>
     </row>
-    <row r="651" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="651" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D651" s="1" t="s">
         <v>2297</v>
       </c>
@@ -15758,7 +16342,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="652" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="652" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D652" s="1" t="s">
         <v>2317</v>
       </c>
@@ -15772,7 +16356,7 @@
         <v>2320</v>
       </c>
     </row>
-    <row r="653" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="653" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D653" s="1" t="s">
         <v>2301</v>
       </c>
@@ -15786,7 +16370,7 @@
         <v>2304</v>
       </c>
     </row>
-    <row r="654" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="654" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D654" s="1" t="s">
         <v>2305</v>
       </c>
@@ -15800,7 +16384,7 @@
         <v>2308</v>
       </c>
     </row>
-    <row r="655" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="655" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D655" s="1" t="s">
         <v>2309</v>
       </c>
@@ -15814,7 +16398,7 @@
         <v>2312</v>
       </c>
     </row>
-    <row r="656" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="656" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D656" s="1" t="s">
         <v>2313</v>
       </c>
@@ -15828,7 +16412,7 @@
         <v>2316</v>
       </c>
     </row>
-    <row r="657" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="657" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D657" s="1" t="s">
         <v>2321</v>
       </c>
@@ -15842,7 +16426,7 @@
         <v>2324</v>
       </c>
     </row>
-    <row r="658" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="658" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D658" s="1" t="s">
         <v>2325</v>
       </c>
@@ -15856,7 +16440,7 @@
         <v>2327</v>
       </c>
     </row>
-    <row r="659" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="659" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D659" s="1" t="s">
         <v>2328</v>
       </c>
@@ -15870,7 +16454,7 @@
         <v>2331</v>
       </c>
     </row>
-    <row r="660" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="660" spans="4:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D660" s="1" t="s">
         <v>2332</v>
       </c>
@@ -15882,6 +16466,705 @@
       </c>
       <c r="Q660" s="1" t="s">
         <v>2335</v>
+      </c>
+    </row>
+    <row r="661" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D661" s="1" t="s">
+        <v>2336</v>
+      </c>
+      <c r="G661" s="1" t="s">
+        <v>2337</v>
+      </c>
+      <c r="L661" s="1" t="s">
+        <v>2338</v>
+      </c>
+      <c r="Q661" s="1" t="s">
+        <v>2339</v>
+      </c>
+    </row>
+    <row r="662" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D662" s="1" t="s">
+        <v>2340</v>
+      </c>
+      <c r="G662" s="1" t="s">
+        <v>2341</v>
+      </c>
+      <c r="L662" s="1" t="s">
+        <v>2342</v>
+      </c>
+      <c r="Q662" s="1" t="s">
+        <v>2343</v>
+      </c>
+    </row>
+    <row r="663" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D663" s="1" t="s">
+        <v>2344</v>
+      </c>
+      <c r="G663" s="1" t="s">
+        <v>2345</v>
+      </c>
+      <c r="L663" s="1" t="s">
+        <v>2346</v>
+      </c>
+      <c r="Q663" s="1" t="s">
+        <v>2347</v>
+      </c>
+    </row>
+    <row r="664" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D664" s="1" t="s">
+        <v>2348</v>
+      </c>
+      <c r="G664" s="1" t="s">
+        <v>2349</v>
+      </c>
+      <c r="L664" s="1" t="s">
+        <v>2350</v>
+      </c>
+      <c r="Q664" s="1" t="s">
+        <v>2351</v>
+      </c>
+    </row>
+    <row r="665" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D665" s="1" t="s">
+        <v>2352</v>
+      </c>
+      <c r="G665" s="1" t="s">
+        <v>2353</v>
+      </c>
+      <c r="L665" s="1" t="s">
+        <v>2354</v>
+      </c>
+      <c r="Q665" s="1" t="s">
+        <v>2355</v>
+      </c>
+    </row>
+    <row r="666" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D666" s="1" t="s">
+        <v>2356</v>
+      </c>
+      <c r="G666" s="1" t="s">
+        <v>2357</v>
+      </c>
+      <c r="L666" s="1" t="s">
+        <v>2358</v>
+      </c>
+      <c r="Q666" s="1" t="s">
+        <v>2359</v>
+      </c>
+    </row>
+    <row r="667" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D667" s="1" t="s">
+        <v>2360</v>
+      </c>
+      <c r="G667" s="1" t="s">
+        <v>2361</v>
+      </c>
+      <c r="L667" s="1" t="s">
+        <v>2362</v>
+      </c>
+      <c r="Q667" s="1" t="s">
+        <v>2363</v>
+      </c>
+    </row>
+    <row r="668" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D668" s="1" t="s">
+        <v>2364</v>
+      </c>
+      <c r="G668" s="1" t="s">
+        <v>2365</v>
+      </c>
+      <c r="L668" s="1" t="s">
+        <v>2366</v>
+      </c>
+      <c r="Q668" s="1" t="s">
+        <v>2367</v>
+      </c>
+    </row>
+    <row r="669" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D669" s="1" t="s">
+        <v>2368</v>
+      </c>
+      <c r="G669" s="1" t="s">
+        <v>2369</v>
+      </c>
+      <c r="L669" s="1" t="s">
+        <v>2370</v>
+      </c>
+      <c r="Q669" s="1" t="s">
+        <v>2371</v>
+      </c>
+    </row>
+    <row r="670" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D670" s="1" t="s">
+        <v>2372</v>
+      </c>
+      <c r="G670" s="1" t="s">
+        <v>2373</v>
+      </c>
+      <c r="L670" s="1" t="s">
+        <v>2374</v>
+      </c>
+      <c r="Q670" s="1" t="s">
+        <v>2375</v>
+      </c>
+    </row>
+    <row r="671" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D671" s="1" t="s">
+        <v>2376</v>
+      </c>
+      <c r="G671" s="1" t="s">
+        <v>2377</v>
+      </c>
+      <c r="L671" s="1" t="s">
+        <v>2378</v>
+      </c>
+      <c r="Q671" s="1" t="s">
+        <v>2379</v>
+      </c>
+    </row>
+    <row r="672" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D672" s="1" t="s">
+        <v>2380</v>
+      </c>
+      <c r="G672" s="1" t="s">
+        <v>2472</v>
+      </c>
+      <c r="L672" s="1" t="s">
+        <v>2381</v>
+      </c>
+      <c r="Q672" s="1" t="s">
+        <v>2394</v>
+      </c>
+    </row>
+    <row r="673" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D673" s="1" t="s">
+        <v>2382</v>
+      </c>
+      <c r="G673" s="1" t="s">
+        <v>2383</v>
+      </c>
+      <c r="L673" s="1" t="s">
+        <v>2384</v>
+      </c>
+      <c r="Q673" s="1" t="s">
+        <v>2385</v>
+      </c>
+    </row>
+    <row r="674" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D674" s="1" t="s">
+        <v>2386</v>
+      </c>
+      <c r="G674" s="1" t="s">
+        <v>2387</v>
+      </c>
+      <c r="L674" s="1" t="s">
+        <v>2388</v>
+      </c>
+      <c r="Q674" s="1" t="s">
+        <v>2389</v>
+      </c>
+    </row>
+    <row r="675" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D675" s="1" t="s">
+        <v>2390</v>
+      </c>
+      <c r="G675" s="1" t="s">
+        <v>2391</v>
+      </c>
+      <c r="L675" s="1" t="s">
+        <v>2392</v>
+      </c>
+      <c r="Q675" s="1" t="s">
+        <v>2393</v>
+      </c>
+    </row>
+    <row r="676" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D676" s="1" t="s">
+        <v>2395</v>
+      </c>
+      <c r="G676" s="1" t="s">
+        <v>2396</v>
+      </c>
+      <c r="L676" s="1" t="s">
+        <v>2397</v>
+      </c>
+      <c r="Q676" s="1" t="s">
+        <v>2398</v>
+      </c>
+    </row>
+    <row r="677" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D677" s="1" t="s">
+        <v>2399</v>
+      </c>
+      <c r="G677" s="1" t="s">
+        <v>2400</v>
+      </c>
+      <c r="L677" s="1" t="s">
+        <v>2401</v>
+      </c>
+      <c r="Q677" s="1" t="s">
+        <v>2402</v>
+      </c>
+    </row>
+    <row r="678" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D678" s="1" t="s">
+        <v>2403</v>
+      </c>
+      <c r="G678" s="1" t="s">
+        <v>2404</v>
+      </c>
+      <c r="L678" s="1" t="s">
+        <v>2405</v>
+      </c>
+      <c r="Q678" s="1" t="s">
+        <v>2406</v>
+      </c>
+    </row>
+    <row r="679" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D679" s="1" t="s">
+        <v>2407</v>
+      </c>
+      <c r="G679" s="1" t="s">
+        <v>2408</v>
+      </c>
+      <c r="L679" s="1" t="s">
+        <v>2409</v>
+      </c>
+      <c r="Q679" s="1" t="s">
+        <v>2410</v>
+      </c>
+    </row>
+    <row r="680" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D680" s="1" t="s">
+        <v>2411</v>
+      </c>
+      <c r="Q680" s="1" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="681" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D681" s="1" t="s">
+        <v>2413</v>
+      </c>
+      <c r="G681" s="1" t="s">
+        <v>2414</v>
+      </c>
+      <c r="L681" s="1" t="s">
+        <v>2415</v>
+      </c>
+      <c r="Q681" s="1" t="s">
+        <v>2416</v>
+      </c>
+    </row>
+    <row r="682" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D682" s="1" t="s">
+        <v>2417</v>
+      </c>
+      <c r="G682" s="1" t="s">
+        <v>2418</v>
+      </c>
+      <c r="L682" s="1" t="s">
+        <v>2419</v>
+      </c>
+      <c r="Q682" s="1" t="s">
+        <v>2420</v>
+      </c>
+    </row>
+    <row r="683" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D683" s="1" t="s">
+        <v>2421</v>
+      </c>
+      <c r="G683" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="L683" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="Q683" s="1" t="s">
+        <v>2424</v>
+      </c>
+    </row>
+    <row r="684" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D684" s="1" t="s">
+        <v>2425</v>
+      </c>
+      <c r="G684" s="1" t="s">
+        <v>2426</v>
+      </c>
+      <c r="L684" s="1" t="s">
+        <v>2427</v>
+      </c>
+      <c r="Q684" s="1" t="s">
+        <v>2428</v>
+      </c>
+    </row>
+    <row r="685" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D685" s="1" t="s">
+        <v>2429</v>
+      </c>
+      <c r="G685" s="1" t="s">
+        <v>2430</v>
+      </c>
+      <c r="L685" s="1" t="s">
+        <v>2431</v>
+      </c>
+      <c r="Q685" s="1" t="s">
+        <v>2432</v>
+      </c>
+    </row>
+    <row r="686" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D686" s="1" t="s">
+        <v>2433</v>
+      </c>
+      <c r="G686" s="1" t="s">
+        <v>2434</v>
+      </c>
+      <c r="L686" s="1" t="s">
+        <v>2435</v>
+      </c>
+      <c r="Q686" s="1" t="s">
+        <v>2436</v>
+      </c>
+    </row>
+    <row r="687" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D687" s="1" t="s">
+        <v>2437</v>
+      </c>
+      <c r="G687" s="1" t="s">
+        <v>2438</v>
+      </c>
+      <c r="L687" s="1" t="s">
+        <v>2439</v>
+      </c>
+      <c r="Q687" s="1" t="s">
+        <v>2440</v>
+      </c>
+    </row>
+    <row r="688" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D688" s="1" t="s">
+        <v>2441</v>
+      </c>
+      <c r="G688" s="1" t="s">
+        <v>2442</v>
+      </c>
+      <c r="L688" s="1" t="s">
+        <v>2443</v>
+      </c>
+      <c r="Q688" s="1" t="s">
+        <v>2444</v>
+      </c>
+    </row>
+    <row r="689" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D689" s="1" t="s">
+        <v>2445</v>
+      </c>
+      <c r="G689" s="1" t="s">
+        <v>2446</v>
+      </c>
+      <c r="L689" s="1" t="s">
+        <v>2447</v>
+      </c>
+      <c r="Q689" s="1" t="s">
+        <v>2448</v>
+      </c>
+    </row>
+    <row r="690" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D690" s="1" t="s">
+        <v>2449</v>
+      </c>
+      <c r="G690" s="1" t="s">
+        <v>2455</v>
+      </c>
+      <c r="Q690" s="1" t="s">
+        <v>2450</v>
+      </c>
+    </row>
+    <row r="691" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D691" s="1" t="s">
+        <v>2451</v>
+      </c>
+      <c r="G691" s="1" t="s">
+        <v>2452</v>
+      </c>
+      <c r="L691" s="1" t="s">
+        <v>2453</v>
+      </c>
+      <c r="Q691" s="1" t="s">
+        <v>2454</v>
+      </c>
+    </row>
+    <row r="692" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D692" s="1" t="s">
+        <v>2456</v>
+      </c>
+      <c r="G692" s="1" t="s">
+        <v>2457</v>
+      </c>
+      <c r="L692" s="1" t="s">
+        <v>2458</v>
+      </c>
+      <c r="Q692" s="1" t="s">
+        <v>2459</v>
+      </c>
+    </row>
+    <row r="693" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D693" s="1" t="s">
+        <v>2460</v>
+      </c>
+      <c r="G693" s="1" t="s">
+        <v>2461</v>
+      </c>
+      <c r="L693" s="1" t="s">
+        <v>2462</v>
+      </c>
+      <c r="Q693" s="1" t="s">
+        <v>2463</v>
+      </c>
+    </row>
+    <row r="694" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D694" s="1" t="s">
+        <v>2464</v>
+      </c>
+      <c r="G694" s="1" t="s">
+        <v>2465</v>
+      </c>
+      <c r="L694" s="1" t="s">
+        <v>2466</v>
+      </c>
+      <c r="Q694" s="1" t="s">
+        <v>2467</v>
+      </c>
+    </row>
+    <row r="695" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D695" s="1" t="s">
+        <v>2468</v>
+      </c>
+      <c r="G695" s="1" t="s">
+        <v>2469</v>
+      </c>
+      <c r="L695" s="1" t="s">
+        <v>2470</v>
+      </c>
+      <c r="Q695" s="1" t="s">
+        <v>2471</v>
+      </c>
+    </row>
+    <row r="696" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D696" s="1" t="s">
+        <v>2473</v>
+      </c>
+      <c r="G696" s="1" t="s">
+        <v>2474</v>
+      </c>
+      <c r="L696" s="1" t="s">
+        <v>2475</v>
+      </c>
+      <c r="Q696" s="1" t="s">
+        <v>2476</v>
+      </c>
+    </row>
+    <row r="697" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D697" s="1" t="s">
+        <v>2477</v>
+      </c>
+      <c r="G697" s="1" t="s">
+        <v>2478</v>
+      </c>
+      <c r="L697" s="1" t="s">
+        <v>2480</v>
+      </c>
+      <c r="Q697" s="1" t="s">
+        <v>2479</v>
+      </c>
+    </row>
+    <row r="698" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D698" s="1" t="s">
+        <v>2481</v>
+      </c>
+      <c r="G698" s="1" t="s">
+        <v>2482</v>
+      </c>
+      <c r="L698" s="1" t="s">
+        <v>2483</v>
+      </c>
+      <c r="Q698" s="1" t="s">
+        <v>2484</v>
+      </c>
+    </row>
+    <row r="699" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D699" s="1" t="s">
+        <v>2485</v>
+      </c>
+      <c r="G699" s="1" t="s">
+        <v>2486</v>
+      </c>
+      <c r="L699" s="1" t="s">
+        <v>2487</v>
+      </c>
+      <c r="Q699" s="1" t="s">
+        <v>2487</v>
+      </c>
+    </row>
+    <row r="700" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D700" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="G700" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="L700" s="1" t="s">
+        <v>2488</v>
+      </c>
+      <c r="Q700" s="1" t="s">
+        <v>2489</v>
+      </c>
+    </row>
+    <row r="701" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D701" s="1" t="s">
+        <v>2490</v>
+      </c>
+      <c r="G701" s="1" t="s">
+        <v>2491</v>
+      </c>
+      <c r="L701" s="1" t="s">
+        <v>2492</v>
+      </c>
+      <c r="Q701" s="1" t="s">
+        <v>2493</v>
+      </c>
+    </row>
+    <row r="702" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D702" s="1" t="s">
+        <v>2494</v>
+      </c>
+      <c r="G702" s="1" t="s">
+        <v>2495</v>
+      </c>
+      <c r="L702" s="1" t="s">
+        <v>2496</v>
+      </c>
+      <c r="Q702" s="1" t="s">
+        <v>2497</v>
+      </c>
+    </row>
+    <row r="703" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D703" s="1" t="s">
+        <v>2498</v>
+      </c>
+      <c r="G703" s="1" t="s">
+        <v>2499</v>
+      </c>
+      <c r="L703" s="1" t="s">
+        <v>2500</v>
+      </c>
+      <c r="Q703" s="1" t="s">
+        <v>2501</v>
+      </c>
+    </row>
+    <row r="704" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D704" s="1" t="s">
+        <v>2506</v>
+      </c>
+      <c r="Q704" s="1" t="s">
+        <v>2507</v>
+      </c>
+    </row>
+    <row r="705" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D705" s="1" t="s">
+        <v>2502</v>
+      </c>
+      <c r="G705" s="1" t="s">
+        <v>2503</v>
+      </c>
+      <c r="L705" s="1" t="s">
+        <v>2504</v>
+      </c>
+      <c r="Q705" s="1" t="s">
+        <v>2505</v>
+      </c>
+    </row>
+    <row r="706" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D706" s="1" t="s">
+        <v>2508</v>
+      </c>
+      <c r="G706" s="1" t="s">
+        <v>2509</v>
+      </c>
+      <c r="L706" s="1" t="s">
+        <v>2510</v>
+      </c>
+      <c r="Q706" s="1" t="s">
+        <v>2511</v>
+      </c>
+    </row>
+    <row r="707" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D707" s="1" t="s">
+        <v>2512</v>
+      </c>
+      <c r="G707" s="1" t="s">
+        <v>2513</v>
+      </c>
+      <c r="L707" s="1" t="s">
+        <v>2514</v>
+      </c>
+      <c r="Q707" s="1" t="s">
+        <v>2515</v>
+      </c>
+    </row>
+    <row r="708" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D708" s="1" t="s">
+        <v>2516</v>
+      </c>
+      <c r="G708" s="1" t="s">
+        <v>2517</v>
+      </c>
+      <c r="L708" s="1" t="s">
+        <v>2518</v>
+      </c>
+      <c r="Q708" s="1" t="s">
+        <v>2519</v>
+      </c>
+    </row>
+    <row r="709" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D709" s="1" t="s">
+        <v>2520</v>
+      </c>
+      <c r="G709" s="1" t="s">
+        <v>2521</v>
+      </c>
+      <c r="L709" s="1" t="s">
+        <v>2522</v>
+      </c>
+      <c r="Q709" s="1" t="s">
+        <v>2523</v>
+      </c>
+    </row>
+    <row r="710" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D710" s="1" t="s">
+        <v>2524</v>
+      </c>
+      <c r="G710" s="1" t="s">
+        <v>2525</v>
+      </c>
+      <c r="L710" s="1" t="s">
+        <v>2526</v>
+      </c>
+      <c r="Q710" s="1" t="s">
+        <v>2526</v>
+      </c>
+    </row>
+    <row r="711" spans="4:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D711" s="1" t="s">
+        <v>2527</v>
+      </c>
+      <c r="G711" s="1" t="s">
+        <v>2528</v>
+      </c>
+      <c r="L711" s="1" t="s">
+        <v>2529</v>
+      </c>
+      <c r="Q711" s="1" t="s">
+        <v>2530</v>
       </c>
     </row>
   </sheetData>
